--- a/research/traditional_assets/database/data/bangladesh/bangladesh_machinery.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_machinery.xlsx
@@ -611,7 +611,7 @@
         <v>0.041</v>
       </c>
       <c r="N2">
-        <v>0.002303370786516854</v>
+        <v>0.001880733944954129</v>
       </c>
       <c r="O2">
         <v>0.9111111111111112</v>
@@ -620,7 +620,7 @@
         <v>0.041</v>
       </c>
       <c r="Q2">
-        <v>0.002303370786516854</v>
+        <v>0.001880733944954129</v>
       </c>
       <c r="R2">
         <v>0.9111111111111112</v>
@@ -635,16 +635,16 @@
         <v>0.031</v>
       </c>
       <c r="V2">
-        <v>0.001741573033707865</v>
+        <v>0.001422018348623853</v>
       </c>
       <c r="W2">
         <v>0.1036866359447005</v>
       </c>
       <c r="X2">
-        <v>0.1013663750168247</v>
+        <v>0.1694179678224205</v>
       </c>
       <c r="Y2">
-        <v>0.002320260927875781</v>
+        <v>-0.06573133187772004</v>
       </c>
       <c r="Z2">
         <v>0.9281678773204195</v>
@@ -653,10 +653,10 @@
         <v>0.05825053574907461</v>
       </c>
       <c r="AB2">
-        <v>0.1000301081262519</v>
+        <v>0.1676876306646993</v>
       </c>
       <c r="AC2">
-        <v>-0.04177957237717725</v>
+        <v>-0.1094370949156247</v>
       </c>
       <c r="AD2">
         <v>0.374</v>
@@ -671,13 +671,13 @@
         <v>0.343</v>
       </c>
       <c r="AH2">
-        <v>0.02057884890502916</v>
+        <v>0.0168666005231352</v>
       </c>
       <c r="AI2">
         <v>0.453883495145631</v>
       </c>
       <c r="AJ2">
-        <v>0.01890536294989803</v>
+        <v>0.01549022264372488</v>
       </c>
       <c r="AK2">
         <v>0.4325346784363178</v>
@@ -739,7 +739,7 @@
         <v>0.041</v>
       </c>
       <c r="N3">
-        <v>0.002303370786516854</v>
+        <v>0.001880733944954129</v>
       </c>
       <c r="O3">
         <v>0.9111111111111112</v>
@@ -748,7 +748,7 @@
         <v>0.041</v>
       </c>
       <c r="Q3">
-        <v>0.002303370786516854</v>
+        <v>0.001880733944954129</v>
       </c>
       <c r="R3">
         <v>0.9111111111111112</v>
@@ -763,16 +763,16 @@
         <v>0.031</v>
       </c>
       <c r="V3">
-        <v>0.001741573033707865</v>
+        <v>0.001422018348623853</v>
       </c>
       <c r="W3">
         <v>0.1036866359447005</v>
       </c>
       <c r="X3">
-        <v>0.1013663750168247</v>
+        <v>0.1694179678224205</v>
       </c>
       <c r="Y3">
-        <v>0.002320260927875781</v>
+        <v>-0.06573133187772004</v>
       </c>
       <c r="Z3">
         <v>0.9281678773204195</v>
@@ -781,10 +781,10 @@
         <v>0.05825053574907461</v>
       </c>
       <c r="AB3">
-        <v>0.1000301081262519</v>
+        <v>0.1676876306646993</v>
       </c>
       <c r="AC3">
-        <v>-0.04177957237717725</v>
+        <v>-0.1094370949156247</v>
       </c>
       <c r="AD3">
         <v>0.374</v>
@@ -799,13 +799,13 @@
         <v>0.343</v>
       </c>
       <c r="AH3">
-        <v>0.02057884890502916</v>
+        <v>0.0168666005231352</v>
       </c>
       <c r="AI3">
         <v>0.453883495145631</v>
       </c>
       <c r="AJ3">
-        <v>0.01890536294989803</v>
+        <v>0.01549022264372488</v>
       </c>
       <c r="AK3">
         <v>0.4325346784363178</v>
@@ -1078,40 +1078,40 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.0205788489050292</v>
+        <v>0.0168666005231352</v>
       </c>
       <c r="F2">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G2">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="H2">
-        <v>17.6070746692522</v>
+        <v>21.9914418806548</v>
       </c>
       <c r="I2">
-        <v>18.143</v>
+        <v>22.143</v>
       </c>
       <c r="J2">
-        <v>18.3030346692522</v>
+        <v>22.1821818806548</v>
       </c>
       <c r="K2">
         <v>0.374</v>
       </c>
       <c r="L2">
-        <v>0.7269600000000001</v>
+        <v>0.22174</v>
       </c>
       <c r="M2">
-        <v>0.100030108126252</v>
+        <v>0.167687630664699</v>
       </c>
       <c r="N2">
-        <v>0.0992875120481068</v>
+        <v>0.167459967768878</v>
       </c>
       <c r="O2">
-        <v>0.0364323791096843</v>
+        <v>0.06682840596330281</v>
       </c>
       <c r="P2">
-        <v>0.0209321941789906</v>
+        <v>0.0344925</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1120,23 +1120,23 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="S2">
-        <v>0.101366375016825</v>
+        <v>0.16941796782242</v>
       </c>
       <c r="T2">
-        <v>0.10255231695932</v>
+        <v>0.168803073503917</v>
       </c>
       <c r="U2">
-        <v>1.14112979766983</v>
+        <v>1.07755483357949</v>
       </c>
       <c r="V2">
-        <v>1.15681741278781</v>
+        <v>1.07248215976523</v>
       </c>
       <c r="W2">
-        <v>4.03663884597984</v>
+        <v>8.031126173934425</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -1145,16 +1145,16 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>0.0151</v>
+        <v>0.0388</v>
       </c>
       <c r="AA2">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="AB2">
-        <v>0.07559733800044451</v>
+        <v>0.1212170033041622</v>
       </c>
       <c r="AC2">
-        <v>0.05397389497731009</v>
+        <v>0.09900504587155964</v>
       </c>
       <c r="AD2">
         <v>0.325</v>
@@ -1346,13 +1346,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1001600043373325</v>
+        <v>0.1679226915163062</v>
       </c>
       <c r="C2">
-        <v>18.14629359466888</v>
+        <v>22.13368987033953</v>
       </c>
       <c r="D2">
-        <v>18.11529359466888</v>
+        <v>22.10268987033953</v>
       </c>
       <c r="E2">
         <v>-0.374</v>
@@ -1364,7 +1364,7 @@
         <v>0.031</v>
       </c>
       <c r="H2">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1385,10 +1385,10 @@
         <v>0.091</v>
       </c>
       <c r="O2">
-        <v>0.029575</v>
+        <v>0.02957499999999999</v>
       </c>
       <c r="P2">
-        <v>0.06142499999999999</v>
+        <v>0.06142500000000001</v>
       </c>
       <c r="Q2">
         <v>0.117425</v>
@@ -1397,19 +1397,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1001600043373325</v>
+        <v>0.1679226915163062</v>
       </c>
       <c r="T2">
-        <v>1.125171951647721</v>
+        <v>1.065219300895492</v>
       </c>
       <c r="U2">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V2">
         <v>0.325</v>
       </c>
       <c r="W2">
-        <v>0.01468821721016348</v>
+        <v>0.0308475</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1428,25 +1428,25 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09987944149533785</v>
+        <v>0.1674599677688782</v>
       </c>
       <c r="C3">
-        <v>18.02450301359455</v>
+        <v>21.99144188065477</v>
       </c>
       <c r="D3">
-        <v>18.17524301359455</v>
+        <v>22.18218188065477</v>
       </c>
       <c r="E3">
-        <v>-0.19226</v>
+        <v>-0.15226</v>
       </c>
       <c r="F3">
-        <v>0.18174</v>
+        <v>0.22174</v>
       </c>
       <c r="G3">
         <v>0.031</v>
       </c>
       <c r="H3">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1461,45 +1461,45 @@
         <v>0.091</v>
       </c>
       <c r="M3">
-        <v>0.003954720882629792</v>
+        <v>0.011330914</v>
       </c>
       <c r="N3">
-        <v>0.0870452791173702</v>
+        <v>0.079669086</v>
       </c>
       <c r="O3">
-        <v>0.02828971571314532</v>
+        <v>0.02589245295</v>
       </c>
       <c r="P3">
-        <v>0.05875556340422489</v>
+        <v>0.05377663305000001</v>
       </c>
       <c r="Q3">
-        <v>0.1147555634042249</v>
+        <v>0.10977663305</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1007399589123598</v>
+        <v>0.1688030735039174</v>
       </c>
       <c r="T3">
-        <v>1.132843578590773</v>
+        <v>1.072482159765234</v>
       </c>
       <c r="U3">
-        <v>0.02176032179283478</v>
+        <v>0.0511</v>
       </c>
       <c r="V3">
         <v>0.325</v>
       </c>
       <c r="W3">
-        <v>0.01468821721016348</v>
+        <v>0.0344925</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>23.01047348238827</v>
+        <v>8.031126173934425</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09962028683053442</v>
+        <v>0.1675412940214502</v>
       </c>
       <c r="C4">
-        <v>17.89849163434987</v>
+        <v>21.7556893313796</v>
       </c>
       <c r="D4">
-        <v>18.23097163434987</v>
+        <v>22.16816933137961</v>
       </c>
       <c r="E4">
-        <v>-0.01052000000000003</v>
+        <v>0.06947999999999999</v>
       </c>
       <c r="F4">
-        <v>0.36348</v>
+        <v>0.44348</v>
       </c>
       <c r="G4">
         <v>0.031</v>
       </c>
       <c r="H4">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1543,45 +1543,45 @@
         <v>0.091</v>
       </c>
       <c r="M4">
-        <v>0.008485845042702344</v>
+        <v>0.040534072</v>
       </c>
       <c r="N4">
-        <v>0.08251415495729765</v>
+        <v>0.05046592799999999</v>
       </c>
       <c r="O4">
-        <v>0.02681710036112174</v>
+        <v>0.01640142659999999</v>
       </c>
       <c r="P4">
-        <v>0.05569705459617591</v>
+        <v>0.0340645014</v>
       </c>
       <c r="Q4">
-        <v>0.1116970545961759</v>
+        <v>0.0900645014</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1013317492950407</v>
+        <v>0.1697014224708676</v>
       </c>
       <c r="T4">
-        <v>1.140671769348991</v>
+        <v>1.079893240244563</v>
       </c>
       <c r="U4">
-        <v>0.02334611269589068</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V4">
         <v>0.325</v>
       </c>
       <c r="W4">
-        <v>0.01575862606972621</v>
+        <v>0.06169500000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y4">
-        <v>10.72374048100939</v>
+        <v>2.245024876849284</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1592,25 +1592,25 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09944393899510673</v>
+        <v>0.1710334036251382</v>
       </c>
       <c r="C5">
-        <v>17.75486928007243</v>
+        <v>20.94851724768501</v>
       </c>
       <c r="D5">
-        <v>18.26908928007244</v>
+        <v>21.58273724768502</v>
       </c>
       <c r="E5">
-        <v>0.1712199999999999</v>
+        <v>0.2912199999999999</v>
       </c>
       <c r="F5">
-        <v>0.5452199999999999</v>
+        <v>0.6652199999999999</v>
       </c>
       <c r="G5">
         <v>0.031</v>
       </c>
       <c r="H5">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1625,45 +1625,45 @@
         <v>0.091</v>
       </c>
       <c r="M5">
-        <v>0.0152464970799235</v>
+        <v>0.142224036</v>
       </c>
       <c r="N5">
-        <v>0.07575350292007649</v>
+        <v>-0.05122403599999997</v>
       </c>
       <c r="O5">
-        <v>0.02461988844902486</v>
+        <v>-0.01664781169999999</v>
       </c>
       <c r="P5">
-        <v>0.05113361447105163</v>
+        <v>-0.03457622429999999</v>
       </c>
       <c r="Q5">
-        <v>0.1071336144710516</v>
+        <v>0.02142377570000001</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.101935741541282</v>
+        <v>0.1710857452623447</v>
       </c>
       <c r="T5">
-        <v>1.148661366102222</v>
+        <v>1.091313443299769</v>
       </c>
       <c r="U5">
-        <v>0.0279639358055895</v>
+        <v>0.2138</v>
       </c>
       <c r="V5">
-        <v>0.325</v>
+        <v>0.2079465667814405</v>
       </c>
       <c r="W5">
-        <v>0.01887565666877291</v>
+        <v>0.169341024022128</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.968584096594111</v>
+        <v>0.6398355900967402</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1674,25 +1674,25 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09928751204810683</v>
+        <v>0.1738677334630603</v>
       </c>
       <c r="C6">
-        <v>17.60707466925221</v>
+        <v>20.27387414050526</v>
       </c>
       <c r="D6">
-        <v>18.30303466925221</v>
+        <v>21.12983414050526</v>
       </c>
       <c r="E6">
-        <v>0.3529599999999999</v>
+        <v>0.51296</v>
       </c>
       <c r="F6">
-        <v>0.7269599999999999</v>
+        <v>0.88696</v>
       </c>
       <c r="G6">
         <v>0.031</v>
       </c>
       <c r="H6">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1707,45 +1707,45 @@
         <v>0.091</v>
       </c>
       <c r="M6">
-        <v>0.0225435079709022</v>
+        <v>0.211806048</v>
       </c>
       <c r="N6">
-        <v>0.06845649202909779</v>
+        <v>-0.120806048</v>
       </c>
       <c r="O6">
-        <v>0.02224835990945678</v>
+        <v>-0.0392619656</v>
       </c>
       <c r="P6">
-        <v>0.046208132119641</v>
+        <v>-0.0815440824</v>
       </c>
       <c r="Q6">
-        <v>0.102208132119641</v>
+        <v>-0.0255440824</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.10255231695932</v>
+        <v>0.172551565356663</v>
       </c>
       <c r="T6">
-        <v>1.156817412787813</v>
+        <v>1.103405972023979</v>
       </c>
       <c r="U6">
-        <v>0.031010658042949</v>
+        <v>0.2388</v>
       </c>
       <c r="V6">
-        <v>0.325</v>
+        <v>0.1396324622420602</v>
       </c>
       <c r="W6">
-        <v>0.02093219417899058</v>
+        <v>0.205455768016596</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.03663884597984</v>
+        <v>0.4296383453601854</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1756,25 +1756,25 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1000903012031405</v>
+        <v>0.1758677334630603</v>
       </c>
       <c r="C7">
-        <v>17.25245049860359</v>
+        <v>19.74382183962083</v>
       </c>
       <c r="D7">
-        <v>18.13015049860359</v>
+        <v>20.82152183962083</v>
       </c>
       <c r="E7">
-        <v>0.5347000000000001</v>
+        <v>0.7347</v>
       </c>
       <c r="F7">
-        <v>0.9087000000000001</v>
+        <v>1.1087</v>
       </c>
       <c r="G7">
         <v>0.031</v>
       </c>
       <c r="H7">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1789,45 +1789,45 @@
         <v>0.091</v>
       </c>
       <c r="M7">
-        <v>0.05566687951130014</v>
+        <v>0.26475756</v>
       </c>
       <c r="N7">
-        <v>0.03533312048869986</v>
+        <v>-0.17375756</v>
       </c>
       <c r="O7">
-        <v>0.01148326415882745</v>
+        <v>-0.056471207</v>
       </c>
       <c r="P7">
-        <v>0.02384985632987241</v>
+        <v>-0.117286353</v>
       </c>
       <c r="Q7">
-        <v>0.0798498563298724</v>
+        <v>-0.06128635300000002</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1031818729124746</v>
+        <v>0.1739594765709436</v>
       </c>
       <c r="T7">
-        <v>1.165145165719416</v>
+        <v>1.115020771729495</v>
       </c>
       <c r="U7">
-        <v>0.06125990922339621</v>
+        <v>0.2388</v>
       </c>
       <c r="V7">
-        <v>0.325</v>
+        <v>0.1117059697936482</v>
       </c>
       <c r="W7">
-        <v>0.04135043872579244</v>
+        <v>0.2121246144132768</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y7">
-        <v>1.63472428846182</v>
+        <v>0.3437106762881483</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1838,25 +1838,25 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.102470097140912</v>
+        <v>0.1778677334630602</v>
       </c>
       <c r="C8">
-        <v>16.57687954362392</v>
+        <v>19.22263751387936</v>
       </c>
       <c r="D8">
-        <v>17.63631954362392</v>
+        <v>20.52207751387936</v>
       </c>
       <c r="E8">
-        <v>0.7164399999999999</v>
+        <v>0.9564399999999998</v>
       </c>
       <c r="F8">
-        <v>1.09044</v>
+        <v>1.33044</v>
       </c>
       <c r="G8">
         <v>0.031</v>
       </c>
       <c r="H8">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1871,45 +1871,45 @@
         <v>0.091</v>
       </c>
       <c r="M8">
-        <v>0.112424364</v>
+        <v>0.317709072</v>
       </c>
       <c r="N8">
-        <v>-0.02142436399999999</v>
+        <v>-0.226709072</v>
       </c>
       <c r="O8">
-        <v>-0.006962918299999996</v>
+        <v>-0.07368044839999999</v>
       </c>
       <c r="P8">
-        <v>-0.01446144569999999</v>
+        <v>-0.1530286236</v>
       </c>
       <c r="Q8">
-        <v>0.0415385543</v>
+        <v>-0.0970286236</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1041610871176111</v>
+        <v>0.1753973433429749</v>
       </c>
       <c r="T8">
-        <v>1.178098190667605</v>
+        <v>1.126882694833</v>
       </c>
       <c r="U8">
-        <v>0.1031</v>
+        <v>0.2388</v>
       </c>
       <c r="V8">
-        <v>0.2630657532561181</v>
+        <v>0.09308830816137349</v>
       </c>
       <c r="W8">
-        <v>0.07597792083929424</v>
+        <v>0.216570512011064</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y8">
-        <v>0.8094330869419017</v>
+        <v>0.2864255635734569</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1920,25 +1920,25 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1049329201355914</v>
+        <v>0.1798677334630603</v>
       </c>
       <c r="C9">
-        <v>15.91162934215223</v>
+        <v>18.7099439838256</v>
       </c>
       <c r="D9">
-        <v>17.15280934215223</v>
+        <v>20.2311239838256</v>
       </c>
       <c r="E9">
-        <v>0.8981800000000001</v>
+        <v>1.17818</v>
       </c>
       <c r="F9">
-        <v>1.27218</v>
+        <v>1.55218</v>
       </c>
       <c r="G9">
         <v>0.031</v>
       </c>
       <c r="H9">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1953,45 +1953,45 @@
         <v>0.091</v>
       </c>
       <c r="M9">
-        <v>0.1560380144767832</v>
+        <v>0.3706605840000001</v>
       </c>
       <c r="N9">
-        <v>-0.06503801447678323</v>
+        <v>-0.279660584</v>
       </c>
       <c r="O9">
-        <v>-0.02113735470495455</v>
+        <v>-0.09088968980000001</v>
       </c>
       <c r="P9">
-        <v>-0.04390065977182868</v>
+        <v>-0.1887708942</v>
       </c>
       <c r="Q9">
-        <v>0.01209934022817132</v>
+        <v>-0.1327708942</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1053488840886635</v>
+        <v>0.1768661319810714</v>
       </c>
       <c r="T9">
-        <v>1.193810344064401</v>
+        <v>1.138999713057011</v>
       </c>
       <c r="U9">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V9">
-        <v>0.1895371464394046</v>
+        <v>0.07978997842403439</v>
       </c>
       <c r="W9">
-        <v>0.09940654190191892</v>
+        <v>0.2197461531523406</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y9">
-        <v>0.5831912198135527</v>
+        <v>0.245507625920106</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2002,25 +2002,25 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1060084605188452</v>
+        <v>0.1818677334630603</v>
       </c>
       <c r="C10">
-        <v>15.52695400446808</v>
+        <v>18.20538516096295</v>
       </c>
       <c r="D10">
-        <v>16.94987400446809</v>
+        <v>19.94830516096295</v>
       </c>
       <c r="E10">
-        <v>1.07992</v>
+        <v>1.39992</v>
       </c>
       <c r="F10">
-        <v>1.45392</v>
+        <v>1.77392</v>
       </c>
       <c r="G10">
         <v>0.031</v>
       </c>
       <c r="H10">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2035,45 +2035,45 @@
         <v>0.091</v>
       </c>
       <c r="M10">
-        <v>0.1783291594020379</v>
+        <v>0.423612096</v>
       </c>
       <c r="N10">
-        <v>-0.08732915940203795</v>
+        <v>-0.332612096</v>
       </c>
       <c r="O10">
-        <v>-0.02838197680566234</v>
+        <v>-0.1080989312</v>
       </c>
       <c r="P10">
-        <v>-0.05894718259637562</v>
+        <v>-0.2245131648</v>
       </c>
       <c r="Q10">
-        <v>-0.002947182596375622</v>
+        <v>-0.1685131648</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.106329850220062</v>
+        <v>0.1783668508069526</v>
       </c>
       <c r="T10">
-        <v>1.206786543456406</v>
+        <v>1.151380144720674</v>
       </c>
       <c r="U10">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V10">
-        <v>0.1658450031344791</v>
+        <v>0.06981623112103011</v>
       </c>
       <c r="W10">
-        <v>0.1023124789548517</v>
+        <v>0.222127884008298</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y10">
-        <v>0.5102923173368586</v>
+        <v>0.2148191726800928</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2084,25 +2084,25 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1105611699228434</v>
+        <v>0.1838677334630603</v>
       </c>
       <c r="C11">
-        <v>14.53684500124827</v>
+        <v>17.7086245938836</v>
       </c>
       <c r="D11">
-        <v>16.14150500124827</v>
+        <v>19.6732845938836</v>
       </c>
       <c r="E11">
-        <v>1.26166</v>
+        <v>1.62166</v>
       </c>
       <c r="F11">
-        <v>1.63566</v>
+        <v>1.99566</v>
       </c>
       <c r="G11">
         <v>0.031</v>
       </c>
       <c r="H11">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2117,37 +2117,37 @@
         <v>0.091</v>
       </c>
       <c r="M11">
-        <v>0.2591802560125812</v>
+        <v>0.476563608</v>
       </c>
       <c r="N11">
-        <v>-0.1681802560125812</v>
+        <v>-0.385563608</v>
       </c>
       <c r="O11">
-        <v>-0.05465858320408888</v>
+        <v>-0.1253081726</v>
       </c>
       <c r="P11">
-        <v>-0.1135216728084923</v>
+        <v>-0.2602554354</v>
       </c>
       <c r="Q11">
-        <v>-0.05752167280849228</v>
+        <v>-0.2042554354</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1076125805954633</v>
+        <v>0.1799005524641719</v>
       </c>
       <c r="T11">
-        <v>1.223754473932922</v>
+        <v>1.164032673783538</v>
       </c>
       <c r="U11">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V11">
-        <v>0.1141097723067469</v>
+        <v>0.06205887210758231</v>
       </c>
       <c r="W11">
-        <v>0.1403746842330198</v>
+        <v>0.2239803413407093</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.3511069917130674</v>
+        <v>0.190950375715638</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2166,25 +2166,25 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.111994730626245</v>
+        <v>0.1858677334630603</v>
       </c>
       <c r="C12">
-        <v>14.11629090770579</v>
+        <v>17.21934413302751</v>
       </c>
       <c r="D12">
-        <v>15.90269090770579</v>
+        <v>19.40574413302751</v>
       </c>
       <c r="E12">
-        <v>1.4434</v>
+        <v>1.8434</v>
       </c>
       <c r="F12">
-        <v>1.8174</v>
+        <v>2.2174</v>
       </c>
       <c r="G12">
         <v>0.031</v>
       </c>
       <c r="H12">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2199,37 +2199,37 @@
         <v>0.091</v>
       </c>
       <c r="M12">
-        <v>0.2879780622362013</v>
+        <v>0.52951512</v>
       </c>
       <c r="N12">
-        <v>-0.1969780622362013</v>
+        <v>-0.43851512</v>
       </c>
       <c r="O12">
-        <v>-0.06401787022676543</v>
+        <v>-0.142517414</v>
       </c>
       <c r="P12">
-        <v>-0.1329601920094359</v>
+        <v>-0.2959977060000001</v>
       </c>
       <c r="Q12">
-        <v>-0.07696019200943588</v>
+        <v>-0.2399977060000001</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1086404981576351</v>
+        <v>0.1814683363804405</v>
       </c>
       <c r="T12">
-        <v>1.237351745865511</v>
+        <v>1.176966370158911</v>
       </c>
       <c r="U12">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V12">
-        <v>0.1026987950760722</v>
+        <v>0.05585298489682409</v>
       </c>
       <c r="W12">
-        <v>0.1421828228437335</v>
+        <v>0.2254623072066384</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.3159962925417605</v>
+        <v>0.1718553381440741</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2248,25 +2248,25 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1134282913296465</v>
+        <v>0.1878677334630603</v>
       </c>
       <c r="C13">
-        <v>13.70270031358533</v>
+        <v>16.73724270292854</v>
       </c>
       <c r="D13">
-        <v>15.67084031358533</v>
+        <v>19.14538270292854</v>
       </c>
       <c r="E13">
-        <v>1.62514</v>
+        <v>2.06514</v>
       </c>
       <c r="F13">
-        <v>1.99914</v>
+        <v>2.43914</v>
       </c>
       <c r="G13">
         <v>0.031</v>
       </c>
       <c r="H13">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2281,37 +2281,37 @@
         <v>0.091</v>
       </c>
       <c r="M13">
-        <v>0.3167758684598214</v>
+        <v>0.582466632</v>
       </c>
       <c r="N13">
-        <v>-0.2257758684598214</v>
+        <v>-0.4914666320000001</v>
       </c>
       <c r="O13">
-        <v>-0.07337715724944197</v>
+        <v>-0.1597266554</v>
       </c>
       <c r="P13">
-        <v>-0.1523987112103795</v>
+        <v>-0.3317399766000001</v>
       </c>
       <c r="Q13">
-        <v>-0.09639871121037946</v>
+        <v>-0.2757399766000001</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.109691514990867</v>
+        <v>0.183071351395951</v>
       </c>
       <c r="T13">
-        <v>1.251254574470741</v>
+        <v>1.190190711396651</v>
       </c>
       <c r="U13">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V13">
-        <v>0.09336254097824744</v>
+        <v>0.05077544081529462</v>
       </c>
       <c r="W13">
-        <v>0.143662208979772</v>
+        <v>0.2266748247333077</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.287269356856146</v>
+        <v>0.1562321255855219</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2330,25 +2330,25 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1148618520330481</v>
+        <v>0.1898677334630603</v>
       </c>
       <c r="C14">
-        <v>13.29577302600976</v>
+        <v>16.26203517198674</v>
       </c>
       <c r="D14">
-        <v>15.44565302600976</v>
+        <v>18.89191517198674</v>
       </c>
       <c r="E14">
-        <v>1.80688</v>
+        <v>2.28688</v>
       </c>
       <c r="F14">
-        <v>2.18088</v>
+        <v>2.66088</v>
       </c>
       <c r="G14">
         <v>0.031</v>
       </c>
       <c r="H14">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2363,37 +2363,37 @@
         <v>0.091</v>
       </c>
       <c r="M14">
-        <v>0.3455736746834415</v>
+        <v>0.635418144</v>
       </c>
       <c r="N14">
-        <v>-0.2545736746834415</v>
+        <v>-0.544418144</v>
       </c>
       <c r="O14">
-        <v>-0.08273644427211849</v>
+        <v>-0.1769358968</v>
       </c>
       <c r="P14">
-        <v>-0.171837230411323</v>
+        <v>-0.3674822472</v>
       </c>
       <c r="Q14">
-        <v>-0.115837230411323</v>
+        <v>-0.3114822472</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1107664185703086</v>
+        <v>0.1847107985709051</v>
       </c>
       <c r="T14">
-        <v>1.265473376453363</v>
+        <v>1.203715605844341</v>
       </c>
       <c r="U14">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V14">
-        <v>0.08558232923006018</v>
+        <v>0.04654415408068675</v>
       </c>
       <c r="W14">
-        <v>0.1448950307598041</v>
+        <v>0.227685256005532</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.2633302437848006</v>
+        <v>0.1432127817867285</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2412,25 +2412,25 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1162954127364497</v>
+        <v>0.1918677334630603</v>
       </c>
       <c r="C15">
-        <v>12.89522586254545</v>
+        <v>15.79345131084672</v>
       </c>
       <c r="D15">
-        <v>15.22684586254545</v>
+        <v>18.64507131084672</v>
       </c>
       <c r="E15">
-        <v>1.98862</v>
+        <v>2.50862</v>
       </c>
       <c r="F15">
-        <v>2.36262</v>
+        <v>2.88262</v>
       </c>
       <c r="G15">
         <v>0.031</v>
       </c>
       <c r="H15">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2445,37 +2445,37 @@
         <v>0.091</v>
       </c>
       <c r="M15">
-        <v>0.3743714809070617</v>
+        <v>0.6883696560000001</v>
       </c>
       <c r="N15">
-        <v>-0.2833714809070618</v>
+        <v>-0.5973696560000001</v>
       </c>
       <c r="O15">
-        <v>-0.09209573129479508</v>
+        <v>-0.1941451382</v>
       </c>
       <c r="P15">
-        <v>-0.1912757496122667</v>
+        <v>-0.4032245178000001</v>
       </c>
       <c r="Q15">
-        <v>-0.1352757496122667</v>
+        <v>-0.3472245178000001</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1118660325768639</v>
+        <v>0.1863879341866626</v>
       </c>
       <c r="T15">
-        <v>1.28001904744708</v>
+        <v>1.21755141740577</v>
       </c>
       <c r="U15">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V15">
-        <v>0.07899907313544013</v>
+        <v>0.04296383453601852</v>
       </c>
       <c r="W15">
-        <v>0.1459381876506005</v>
+        <v>0.2285402363127988</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.2430740711859696</v>
+        <v>0.13219641395698</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2494,25 +2494,25 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1177289734398512</v>
+        <v>0.1938677334630603</v>
       </c>
       <c r="C16">
-        <v>12.50079146316036</v>
+        <v>15.33123483138249</v>
       </c>
       <c r="D16">
-        <v>15.01415146316036</v>
+        <v>18.40459483138249</v>
       </c>
       <c r="E16">
-        <v>2.17036</v>
+        <v>2.73036</v>
       </c>
       <c r="F16">
-        <v>2.54436</v>
+        <v>3.10436</v>
       </c>
       <c r="G16">
         <v>0.031</v>
       </c>
       <c r="H16">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2527,37 +2527,37 @@
         <v>0.091</v>
       </c>
       <c r="M16">
-        <v>0.4031692871306818</v>
+        <v>0.7413211680000001</v>
       </c>
       <c r="N16">
-        <v>-0.3121692871306818</v>
+        <v>-0.6503211680000002</v>
       </c>
       <c r="O16">
-        <v>-0.1014550183174716</v>
+        <v>-0.2113543796</v>
       </c>
       <c r="P16">
-        <v>-0.2107142688132102</v>
+        <v>-0.4389667884000001</v>
       </c>
       <c r="Q16">
-        <v>-0.1547142688132102</v>
+        <v>-0.3829667884000001</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1129912190021763</v>
+        <v>0.1881040729562749</v>
       </c>
       <c r="T16">
-        <v>1.294902989859255</v>
+        <v>1.231708992026767</v>
       </c>
       <c r="U16">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V16">
-        <v>0.07335628219719442</v>
+        <v>0.03989498921201719</v>
       </c>
       <c r="W16">
-        <v>0.1468323221284259</v>
+        <v>0.2292730765761703</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.225711637529829</v>
+        <v>0.1227538129600529</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2576,25 +2576,25 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1191625341432528</v>
+        <v>0.1958677334630603</v>
       </c>
       <c r="C17">
-        <v>12.11221720038067</v>
+        <v>14.87514249910399</v>
       </c>
       <c r="D17">
-        <v>14.80731720038067</v>
+        <v>18.170242499104</v>
       </c>
       <c r="E17">
-        <v>2.3521</v>
+        <v>2.9521</v>
       </c>
       <c r="F17">
-        <v>2.7261</v>
+        <v>3.3261</v>
       </c>
       <c r="G17">
         <v>0.031</v>
       </c>
       <c r="H17">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2609,37 +2609,37 @@
         <v>0.091</v>
       </c>
       <c r="M17">
-        <v>0.4319670933543019</v>
+        <v>0.79427268</v>
       </c>
       <c r="N17">
-        <v>-0.340967093354302</v>
+        <v>-0.70327268</v>
       </c>
       <c r="O17">
-        <v>-0.1108143053401481</v>
+        <v>-0.228563621</v>
       </c>
       <c r="P17">
-        <v>-0.2301527880141538</v>
+        <v>-0.474709059</v>
       </c>
       <c r="Q17">
-        <v>-0.1741527880141538</v>
+        <v>-0.4187090590000001</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1141428804022019</v>
+        <v>0.1898605914616429</v>
       </c>
       <c r="T17">
-        <v>1.310137142681129</v>
+        <v>1.246199686050612</v>
       </c>
       <c r="U17">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V17">
-        <v>0.06846586338404813</v>
+        <v>0.03723532326454939</v>
       </c>
       <c r="W17">
-        <v>0.1476072386758747</v>
+        <v>0.2299082048044256</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2106641950278403</v>
+        <v>0.1145702254293828</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2658,25 +2658,25 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1205960948466544</v>
+        <v>0.1978677334630603</v>
       </c>
       <c r="C18">
-        <v>11.72926417830508</v>
+        <v>14.42494331252328</v>
       </c>
       <c r="D18">
-        <v>14.60610417830508</v>
+        <v>17.94178331252328</v>
       </c>
       <c r="E18">
-        <v>2.53384</v>
+        <v>3.17384</v>
       </c>
       <c r="F18">
-        <v>2.90784</v>
+        <v>3.54784</v>
       </c>
       <c r="G18">
         <v>0.031</v>
       </c>
       <c r="H18">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2691,37 +2691,37 @@
         <v>0.091</v>
       </c>
       <c r="M18">
-        <v>0.460764899577922</v>
+        <v>0.847224192</v>
       </c>
       <c r="N18">
-        <v>-0.369764899577922</v>
+        <v>-0.756224192</v>
       </c>
       <c r="O18">
-        <v>-0.1201735923628247</v>
+        <v>-0.2457728624</v>
       </c>
       <c r="P18">
-        <v>-0.2495913072150974</v>
+        <v>-0.5104513296000001</v>
       </c>
       <c r="Q18">
-        <v>-0.1935913072150974</v>
+        <v>-0.4544513296000001</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1153219623117519</v>
+        <v>0.1916589318361862</v>
       </c>
       <c r="T18">
-        <v>1.325734013427333</v>
+        <v>1.261035396598833</v>
       </c>
       <c r="U18">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V18">
-        <v>0.06418674692254513</v>
+        <v>0.03490811556051505</v>
       </c>
       <c r="W18">
-        <v>0.1482852906548923</v>
+        <v>0.230463942004149</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.1974976828386005</v>
+        <v>0.1074095863400463</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2740,25 +2740,25 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1220296555500559</v>
+        <v>0.1998677334630603</v>
       </c>
       <c r="C19">
-        <v>11.35170631213786</v>
+        <v>13.98041774366025</v>
       </c>
       <c r="D19">
-        <v>14.41028631213786</v>
+        <v>17.71899774366026</v>
       </c>
       <c r="E19">
-        <v>2.71558</v>
+        <v>3.39558</v>
       </c>
       <c r="F19">
-        <v>3.08958</v>
+        <v>3.76958</v>
       </c>
       <c r="G19">
         <v>0.031</v>
       </c>
       <c r="H19">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2773,37 +2773,37 @@
         <v>0.091</v>
       </c>
       <c r="M19">
-        <v>0.4895627058015423</v>
+        <v>0.9001757040000001</v>
       </c>
       <c r="N19">
-        <v>-0.3985627058015423</v>
+        <v>-0.8091757040000002</v>
       </c>
       <c r="O19">
-        <v>-0.1295328793855013</v>
+        <v>-0.2629821038</v>
       </c>
       <c r="P19">
-        <v>-0.269029826416041</v>
+        <v>-0.5461936002000001</v>
       </c>
       <c r="Q19">
-        <v>-0.213029826416041</v>
+        <v>-0.4901936002000001</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1165294558335802</v>
+        <v>0.1935006057137307</v>
       </c>
       <c r="T19">
-        <v>1.341706712384289</v>
+        <v>1.276228594148217</v>
       </c>
       <c r="U19">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V19">
-        <v>0.06041105592710128</v>
+        <v>0.03285469699813182</v>
       </c>
       <c r="W19">
-        <v>0.1488835718128491</v>
+        <v>0.2309542983568461</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1858801720833885</v>
+        <v>0.1010913753788671</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2822,25 +2822,25 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1234632162534575</v>
+        <v>0.2018677334630603</v>
       </c>
       <c r="C20">
-        <v>10.97932948078424</v>
+        <v>13.54135703443884</v>
       </c>
       <c r="D20">
-        <v>14.21964948078424</v>
+        <v>17.50167703443884</v>
       </c>
       <c r="E20">
-        <v>2.89732</v>
+        <v>3.61732</v>
       </c>
       <c r="F20">
-        <v>3.27132</v>
+        <v>3.99132</v>
       </c>
       <c r="G20">
         <v>0.031</v>
       </c>
       <c r="H20">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2855,37 +2855,37 @@
         <v>0.091</v>
       </c>
       <c r="M20">
-        <v>0.5183605120251623</v>
+        <v>0.9531272160000001</v>
       </c>
       <c r="N20">
-        <v>-0.4273605120251623</v>
+        <v>-0.8621272160000001</v>
       </c>
       <c r="O20">
-        <v>-0.1388921664081778</v>
+        <v>-0.2801913452</v>
       </c>
       <c r="P20">
-        <v>-0.2884683456169846</v>
+        <v>-0.5819358708000001</v>
       </c>
       <c r="Q20">
-        <v>-0.2324683456169846</v>
+        <v>-0.5259358708000001</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1177664004169166</v>
+        <v>0.1953871984663371</v>
       </c>
       <c r="T20">
-        <v>1.358068989364585</v>
+        <v>1.291792357491488</v>
       </c>
       <c r="U20">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V20">
-        <v>0.05705488615337344</v>
+        <v>0.03102943605379116</v>
       </c>
       <c r="W20">
-        <v>0.1494153772865884</v>
+        <v>0.2313901706703547</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.1755534958565336</v>
+        <v>0.09547518785781894</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2904,25 +2904,25 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1248967769568591</v>
+        <v>0.2038677334630603</v>
       </c>
       <c r="C21">
-        <v>10.61193074583061</v>
+        <v>13.1075625442334</v>
       </c>
       <c r="D21">
-        <v>14.0339907458306</v>
+        <v>17.2896225442334</v>
       </c>
       <c r="E21">
-        <v>3.07906</v>
+        <v>3.839059999999999</v>
       </c>
       <c r="F21">
-        <v>3.45306</v>
+        <v>4.21306</v>
       </c>
       <c r="G21">
         <v>0.031</v>
       </c>
       <c r="H21">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2937,37 +2937,37 @@
         <v>0.091</v>
       </c>
       <c r="M21">
-        <v>0.5471583182487825</v>
+        <v>1.006078728</v>
       </c>
       <c r="N21">
-        <v>-0.4561583182487825</v>
+        <v>-0.9150787279999999</v>
       </c>
       <c r="O21">
-        <v>-0.1482514534308543</v>
+        <v>-0.2974005865999999</v>
       </c>
       <c r="P21">
-        <v>-0.3079068648179282</v>
+        <v>-0.6176781414</v>
       </c>
       <c r="Q21">
-        <v>-0.2519068648179282</v>
+        <v>-0.5616781414000001</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1190338868418168</v>
+        <v>0.197320373756045</v>
       </c>
       <c r="T21">
-        <v>1.374835273183901</v>
+        <v>1.307740411287679</v>
       </c>
       <c r="U21">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V21">
-        <v>0.05405199740845905</v>
+        <v>0.02939630784043374</v>
       </c>
       <c r="W21">
-        <v>0.1498912032367762</v>
+        <v>0.2317801616877044</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1663138381798739</v>
+        <v>0.09045017797056532</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2986,25 +2986,25 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1263303376602606</v>
+        <v>0.2058677334630603</v>
       </c>
       <c r="C22">
-        <v>10.24931763092042</v>
+        <v>12.67884514427895</v>
       </c>
       <c r="D22">
-        <v>13.85311763092042</v>
+        <v>17.08264514427895</v>
       </c>
       <c r="E22">
-        <v>3.2608</v>
+        <v>4.0608</v>
       </c>
       <c r="F22">
-        <v>3.6348</v>
+        <v>4.4348</v>
       </c>
       <c r="G22">
         <v>0.031</v>
       </c>
       <c r="H22">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3019,37 +3019,37 @@
         <v>0.091</v>
       </c>
       <c r="M22">
-        <v>0.5759561244724026</v>
+        <v>1.05903024</v>
       </c>
       <c r="N22">
-        <v>-0.4849561244724027</v>
+        <v>-0.96803024</v>
       </c>
       <c r="O22">
-        <v>-0.1576107404535309</v>
+        <v>-0.314609828</v>
       </c>
       <c r="P22">
-        <v>-0.3273453840188718</v>
+        <v>-0.653420412</v>
       </c>
       <c r="Q22">
-        <v>-0.2713453840188718</v>
+        <v>-0.597420412</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1203330604273395</v>
+        <v>0.1993018784279956</v>
       </c>
       <c r="T22">
-        <v>1.392020714098699</v>
+        <v>1.324087166428775</v>
       </c>
       <c r="U22">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V22">
-        <v>0.05134939753803609</v>
+        <v>0.02792649244841204</v>
       </c>
       <c r="W22">
-        <v>0.1503194465919453</v>
+        <v>0.2321311536033192</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1579981462708803</v>
+        <v>0.08592766907203708</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3068,25 +3068,25 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1277638983636622</v>
+        <v>0.2078677334630603</v>
       </c>
       <c r="C23">
-        <v>9.891307456146382</v>
+        <v>12.25502465506471</v>
       </c>
       <c r="D23">
-        <v>13.67684745614638</v>
+        <v>16.88056465506471</v>
       </c>
       <c r="E23">
-        <v>3.44254</v>
+        <v>4.28254</v>
       </c>
       <c r="F23">
-        <v>3.81654</v>
+        <v>4.65654</v>
       </c>
       <c r="G23">
         <v>0.031</v>
       </c>
       <c r="H23">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3101,37 +3101,37 @@
         <v>0.091</v>
       </c>
       <c r="M23">
-        <v>0.6047539306960227</v>
+        <v>1.111981752</v>
       </c>
       <c r="N23">
-        <v>-0.5137539306960227</v>
+        <v>-1.020981752</v>
       </c>
       <c r="O23">
-        <v>-0.1669700274762074</v>
+        <v>-0.3318190693999999</v>
       </c>
       <c r="P23">
-        <v>-0.3467839032198153</v>
+        <v>-0.6891626826</v>
       </c>
       <c r="Q23">
-        <v>-0.2907839032198153</v>
+        <v>-0.6331626826000001</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1216651244833818</v>
+        <v>0.2013335477751854</v>
       </c>
       <c r="T23">
-        <v>1.409641229467037</v>
+        <v>1.340847763472177</v>
       </c>
       <c r="U23">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V23">
-        <v>0.04890418813146295</v>
+        <v>0.02659665947467814</v>
       </c>
       <c r="W23">
-        <v>0.1507069048656696</v>
+        <v>0.2324487177174469</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1504744250198859</v>
+        <v>0.081835875306702</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3150,25 +3150,25 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1291974590670638</v>
+        <v>0.2098677334630603</v>
       </c>
       <c r="C24">
-        <v>9.537726722620269</v>
+        <v>11.83592932319308</v>
       </c>
       <c r="D24">
-        <v>13.50500672262027</v>
+        <v>16.68320932319308</v>
       </c>
       <c r="E24">
-        <v>3.62428</v>
+        <v>4.504280000000001</v>
       </c>
       <c r="F24">
-        <v>3.99828</v>
+        <v>4.87828</v>
       </c>
       <c r="G24">
         <v>0.031</v>
       </c>
       <c r="H24">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3183,37 +3183,37 @@
         <v>0.091</v>
       </c>
       <c r="M24">
-        <v>0.6335517369196428</v>
+        <v>1.164933264</v>
       </c>
       <c r="N24">
-        <v>-0.5425517369196429</v>
+        <v>-1.073933264</v>
       </c>
       <c r="O24">
-        <v>-0.1763293144988839</v>
+        <v>-0.3490283108</v>
       </c>
       <c r="P24">
-        <v>-0.3662224224207589</v>
+        <v>-0.7249049532000001</v>
       </c>
       <c r="Q24">
-        <v>-0.3102224224207589</v>
+        <v>-0.6689049532000002</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1230313440280405</v>
+        <v>0.2034173112082006</v>
       </c>
       <c r="T24">
-        <v>1.427713552921743</v>
+        <v>1.358038119414128</v>
       </c>
       <c r="U24">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V24">
-        <v>0.04668127048912372</v>
+        <v>0.02538772040764731</v>
       </c>
       <c r="W24">
-        <v>0.1510591396599645</v>
+        <v>0.2327374123666538</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.143634678428073</v>
+        <v>0.07811606279276095</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3232,25 +3232,25 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1306310197704654</v>
+        <v>0.2118677334630603</v>
       </c>
       <c r="C25">
-        <v>9.188410542861909</v>
+        <v>11.42139533451172</v>
       </c>
       <c r="D25">
-        <v>13.33743054286191</v>
+        <v>16.49041533451172</v>
       </c>
       <c r="E25">
-        <v>3.80602</v>
+        <v>4.72602</v>
       </c>
       <c r="F25">
-        <v>4.18002</v>
+        <v>5.10002</v>
       </c>
       <c r="G25">
         <v>0.031</v>
       </c>
       <c r="H25">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -3265,37 +3265,37 @@
         <v>0.091</v>
       </c>
       <c r="M25">
-        <v>0.662349543143263</v>
+        <v>1.217884776</v>
       </c>
       <c r="N25">
-        <v>-0.571349543143263</v>
+        <v>-1.126884776</v>
       </c>
       <c r="O25">
-        <v>-0.1856886015215605</v>
+        <v>-0.3662375522</v>
       </c>
       <c r="P25">
-        <v>-0.3856609416217025</v>
+        <v>-0.7606472238</v>
       </c>
       <c r="Q25">
-        <v>-0.3296609416217025</v>
+        <v>-0.7046472238000001</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1244330497946384</v>
+        <v>0.2055551983667486</v>
       </c>
       <c r="T25">
-        <v>1.446255287375272</v>
+        <v>1.375674978107818</v>
       </c>
       <c r="U25">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V25">
-        <v>0.04465165003307486</v>
+        <v>0.02428390647688004</v>
       </c>
       <c r="W25">
-        <v>0.151380745341712</v>
+        <v>0.2330010031333211</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1373896924094611</v>
+        <v>0.07471971223655394</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3314,25 +3314,25 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1320645804738669</v>
+        <v>0.2138677334630603</v>
       </c>
       <c r="C26">
-        <v>8.843202113076305</v>
+        <v>11.01126636061789</v>
       </c>
       <c r="D26">
-        <v>13.17396211307631</v>
+        <v>16.30202636061789</v>
       </c>
       <c r="E26">
-        <v>3.987759999999999</v>
+        <v>4.94776</v>
       </c>
       <c r="F26">
-        <v>4.361759999999999</v>
+        <v>5.321759999999999</v>
       </c>
       <c r="G26">
         <v>0.031</v>
       </c>
       <c r="H26">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3347,37 +3347,37 @@
         <v>0.091</v>
       </c>
       <c r="M26">
-        <v>0.691147349366883</v>
+        <v>1.270836288</v>
       </c>
       <c r="N26">
-        <v>-0.6001473493668831</v>
+        <v>-1.179836288</v>
       </c>
       <c r="O26">
-        <v>-0.195047888544237</v>
+        <v>-0.3834467935999999</v>
       </c>
       <c r="P26">
-        <v>-0.405099460822646</v>
+        <v>-0.7963894944000001</v>
       </c>
       <c r="Q26">
-        <v>-0.349099460822646</v>
+        <v>-0.7403894944</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1258716425550942</v>
+        <v>0.2077493457136795</v>
       </c>
       <c r="T26">
-        <v>1.465284962209157</v>
+        <v>1.393775964661868</v>
       </c>
       <c r="U26">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V26">
-        <v>0.04279116461503009</v>
+        <v>0.02327207704034337</v>
       </c>
       <c r="W26">
-        <v>0.1516755505499806</v>
+        <v>0.233242628002766</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1316651218924002</v>
+        <v>0.07160639089336418</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3396,25 +3396,25 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1334981411772685</v>
+        <v>0.2158677334630603</v>
       </c>
       <c r="C27">
-        <v>8.501952223768745</v>
+        <v>10.60539313609657</v>
       </c>
       <c r="D27">
-        <v>13.01445222376874</v>
+        <v>16.11789313609657</v>
       </c>
       <c r="E27">
-        <v>4.1695</v>
+        <v>5.1695</v>
       </c>
       <c r="F27">
-        <v>4.5435</v>
+        <v>5.5435</v>
       </c>
       <c r="G27">
         <v>0.031</v>
       </c>
       <c r="H27">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3429,37 +3429,37 @@
         <v>0.091</v>
       </c>
       <c r="M27">
-        <v>0.7199451555905033</v>
+        <v>1.3237878</v>
       </c>
       <c r="N27">
-        <v>-0.6289451555905033</v>
+        <v>-1.2327878</v>
       </c>
       <c r="O27">
-        <v>-0.2044071755669136</v>
+        <v>-0.400656035</v>
       </c>
       <c r="P27">
-        <v>-0.4245379800235898</v>
+        <v>-0.8321317650000002</v>
       </c>
       <c r="Q27">
-        <v>-0.3685379800235898</v>
+        <v>-0.7761317650000001</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1273485977891621</v>
+        <v>0.2100020036565285</v>
       </c>
       <c r="T27">
-        <v>1.484822095038613</v>
+        <v>1.412359644190693</v>
       </c>
       <c r="U27">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V27">
-        <v>0.04107951803042887</v>
+        <v>0.02234119395872963</v>
       </c>
       <c r="W27">
-        <v>0.1519467713415876</v>
+        <v>0.2334649228826554</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1263985170167041</v>
+        <v>0.06874213525762962</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3478,25 +3478,25 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1349317018806701</v>
+        <v>0.2178677334630603</v>
       </c>
       <c r="C28">
-        <v>8.164518805487237</v>
+        <v>10.20363306408933</v>
       </c>
       <c r="D28">
-        <v>12.85875880548724</v>
+        <v>15.93787306408933</v>
       </c>
       <c r="E28">
-        <v>4.351240000000001</v>
+        <v>5.391240000000001</v>
       </c>
       <c r="F28">
-        <v>4.72524</v>
+        <v>5.76524</v>
       </c>
       <c r="G28">
         <v>0.031</v>
       </c>
       <c r="H28">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3511,37 +3511,37 @@
         <v>0.091</v>
       </c>
       <c r="M28">
-        <v>0.7487429618141235</v>
+        <v>1.376739312</v>
       </c>
       <c r="N28">
-        <v>-0.6577429618141235</v>
+        <v>-1.285739312</v>
       </c>
       <c r="O28">
-        <v>-0.2137664625895901</v>
+        <v>-0.4178652764</v>
       </c>
       <c r="P28">
-        <v>-0.4439764992245334</v>
+        <v>-0.8678740356000002</v>
       </c>
       <c r="Q28">
-        <v>-0.3879764992245334</v>
+        <v>-0.8118740356000003</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1288654707322589</v>
+        <v>0.2123155442464817</v>
       </c>
       <c r="T28">
-        <v>1.50488725848508</v>
+        <v>1.431445585328405</v>
       </c>
       <c r="U28">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V28">
-        <v>0.03949953656772007</v>
+        <v>0.02148191726800926</v>
       </c>
       <c r="W28">
-        <v>0.1521971289953787</v>
+        <v>0.2336701181563994</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1215370355929848</v>
+        <v>0.06609820697849</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3560,25 +3560,25 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1363652625840716</v>
+        <v>0.2198677334630603</v>
       </c>
       <c r="C29">
-        <v>7.830766506785575</v>
+        <v>9.805849848003671</v>
       </c>
       <c r="D29">
-        <v>12.70674650678557</v>
+        <v>15.76182984800367</v>
       </c>
       <c r="E29">
-        <v>4.53298</v>
+        <v>5.61298</v>
       </c>
       <c r="F29">
-        <v>4.90698</v>
+        <v>5.98698</v>
       </c>
       <c r="G29">
         <v>0.031</v>
       </c>
       <c r="H29">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3593,37 +3593,37 @@
         <v>0.091</v>
       </c>
       <c r="M29">
-        <v>0.7775407680377435</v>
+        <v>1.429690824</v>
       </c>
       <c r="N29">
-        <v>-0.6865407680377436</v>
+        <v>-1.338690824</v>
       </c>
       <c r="O29">
-        <v>-0.2231257496122667</v>
+        <v>-0.4350745178</v>
       </c>
       <c r="P29">
-        <v>-0.4634150184254769</v>
+        <v>-0.9036163062000002</v>
       </c>
       <c r="Q29">
-        <v>-0.4074150184254769</v>
+        <v>-0.8476163062000002</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1304239018381803</v>
+        <v>0.2146924695101321</v>
       </c>
       <c r="T29">
-        <v>1.525502152436931</v>
+        <v>1.451054428963041</v>
       </c>
       <c r="U29">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V29">
-        <v>0.03803659076891563</v>
+        <v>0.02068629070252744</v>
       </c>
       <c r="W29">
-        <v>0.1524289416377779</v>
+        <v>0.2338601137802364</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1170356639043557</v>
+        <v>0.06365012523854596</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3642,25 +3642,25 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1377988232874732</v>
+        <v>0.2218677334630603</v>
       </c>
       <c r="C30">
-        <v>7.500566301771748</v>
+        <v>9.411913147363535</v>
       </c>
       <c r="D30">
-        <v>12.55828630177175</v>
+        <v>15.58963314736353</v>
       </c>
       <c r="E30">
-        <v>4.714720000000001</v>
+        <v>5.834720000000001</v>
       </c>
       <c r="F30">
-        <v>5.08872</v>
+        <v>6.20872</v>
       </c>
       <c r="G30">
         <v>0.031</v>
       </c>
       <c r="H30">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3675,37 +3675,37 @@
         <v>0.091</v>
       </c>
       <c r="M30">
-        <v>0.8063385742613637</v>
+        <v>1.482642336</v>
       </c>
       <c r="N30">
-        <v>-0.7153385742613637</v>
+        <v>-1.391642336</v>
       </c>
       <c r="O30">
-        <v>-0.2324850366349432</v>
+        <v>-0.4522837592</v>
       </c>
       <c r="P30">
-        <v>-0.4828535376264205</v>
+        <v>-0.9393585768000003</v>
       </c>
       <c r="Q30">
-        <v>-0.4268535376264205</v>
+        <v>-0.8833585768000003</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1320256226970439</v>
+        <v>0.2171354204755506</v>
       </c>
       <c r="T30">
-        <v>1.546689682331888</v>
+        <v>1.471207962698639</v>
       </c>
       <c r="U30">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V30">
-        <v>0.03667814109859721</v>
+        <v>0.0199474946060086</v>
       </c>
       <c r="W30">
-        <v>0.1526441962342915</v>
+        <v>0.2340365382880852</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1128558187649145</v>
+        <v>0.06137690648002647</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3724,25 +3724,25 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1392323839908748</v>
+        <v>0.2238677334630603</v>
       </c>
       <c r="C31">
-        <v>7.173795124850109</v>
+        <v>9.021698255974915</v>
       </c>
       <c r="D31">
-        <v>12.41325512485011</v>
+        <v>15.42115825597491</v>
       </c>
       <c r="E31">
-        <v>4.89646</v>
+        <v>6.05646</v>
       </c>
       <c r="F31">
-        <v>5.27046</v>
+        <v>6.430459999999999</v>
       </c>
       <c r="G31">
         <v>0.031</v>
       </c>
       <c r="H31">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3757,37 +3757,37 @@
         <v>0.091</v>
       </c>
       <c r="M31">
-        <v>0.8351363804849838</v>
+        <v>1.535593848</v>
       </c>
       <c r="N31">
-        <v>-0.7441363804849839</v>
+        <v>-1.444593848</v>
       </c>
       <c r="O31">
-        <v>-0.2418443236576198</v>
+        <v>-0.4694930005999999</v>
       </c>
       <c r="P31">
-        <v>-0.5022920568273641</v>
+        <v>-0.9751008474</v>
       </c>
       <c r="Q31">
-        <v>-0.4462920568273641</v>
+        <v>-0.9191008474</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1336724624533403</v>
+        <v>0.2196471869611218</v>
       </c>
       <c r="T31">
-        <v>1.568474044054872</v>
+        <v>1.491929201609887</v>
       </c>
       <c r="U31">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V31">
-        <v>0.03541337761243869</v>
+        <v>0.0192596499644221</v>
       </c>
       <c r="W31">
-        <v>0.1528446056862179</v>
+        <v>0.234200795588496</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1089642388075036</v>
+        <v>0.05926046142899111</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3806,25 +3806,25 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1406659446942763</v>
+        <v>0.2258677334630603</v>
       </c>
       <c r="C32">
-        <v>6.850335530483894</v>
+        <v>8.635085800736448</v>
       </c>
       <c r="D32">
-        <v>12.27153553048389</v>
+        <v>15.25628580073645</v>
       </c>
       <c r="E32">
-        <v>5.0782</v>
+        <v>6.2782</v>
       </c>
       <c r="F32">
-        <v>5.452199999999999</v>
+        <v>6.6522</v>
       </c>
       <c r="G32">
         <v>0.031</v>
       </c>
       <c r="H32">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3839,37 +3839,37 @@
         <v>0.091</v>
       </c>
       <c r="M32">
-        <v>0.8639341867086039</v>
+        <v>1.58854536</v>
       </c>
       <c r="N32">
-        <v>-0.7729341867086039</v>
+        <v>-1.49754536</v>
       </c>
       <c r="O32">
-        <v>-0.2512036106802963</v>
+        <v>-0.4867022419999999</v>
       </c>
       <c r="P32">
-        <v>-0.5217305760283076</v>
+        <v>-1.010843118</v>
       </c>
       <c r="Q32">
-        <v>-0.4657305760283076</v>
+        <v>-0.9548431179999999</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1353663547741023</v>
+        <v>0.2222307182034235</v>
       </c>
       <c r="T32">
-        <v>1.590880816112799</v>
+        <v>1.5132424759186</v>
       </c>
       <c r="U32">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V32">
-        <v>0.03423293169202406</v>
+        <v>0.0186176616322747</v>
       </c>
       <c r="W32">
-        <v>0.1530316545080158</v>
+        <v>0.2343541024022128</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1053320975139201</v>
+        <v>0.05728511271469139</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3888,25 +3888,25 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1420995053976779</v>
+        <v>0.2278677334630603</v>
       </c>
       <c r="C33">
-        <v>6.530075376001311</v>
+        <v>8.251961459566278</v>
       </c>
       <c r="D33">
-        <v>12.13301537600131</v>
+        <v>15.09490145956628</v>
       </c>
       <c r="E33">
-        <v>5.25994</v>
+        <v>6.49994</v>
       </c>
       <c r="F33">
-        <v>5.63394</v>
+        <v>6.87394</v>
       </c>
       <c r="G33">
         <v>0.031</v>
       </c>
       <c r="H33">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3921,37 +3921,37 @@
         <v>0.091</v>
       </c>
       <c r="M33">
-        <v>0.892731992932224</v>
+        <v>1.641496872</v>
       </c>
       <c r="N33">
-        <v>-0.8017319929322241</v>
+        <v>-1.550496872</v>
       </c>
       <c r="O33">
-        <v>-0.2605628977029729</v>
+        <v>-0.5039114833999999</v>
       </c>
       <c r="P33">
-        <v>-0.5411690952292512</v>
+        <v>-1.0465853886</v>
       </c>
       <c r="Q33">
-        <v>-0.4851690952292512</v>
+        <v>-0.9905853886</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1371093454230023</v>
+        <v>0.2248891344092702</v>
       </c>
       <c r="T33">
-        <v>1.613937059824579</v>
+        <v>1.535173526294232</v>
       </c>
       <c r="U33">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V33">
-        <v>0.03312864357292651</v>
+        <v>0.01801709190220132</v>
       </c>
       <c r="W33">
-        <v>0.1532066356638913</v>
+        <v>0.2344975184537543</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1019342879166969</v>
+        <v>0.05543720585292711</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3970,25 +3970,25 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1435330661010795</v>
+        <v>0.2298677334630603</v>
       </c>
       <c r="C34">
-        <v>6.212907525644506</v>
+        <v>7.872215697044533</v>
       </c>
       <c r="D34">
-        <v>11.99758752564451</v>
+        <v>14.93689569704453</v>
       </c>
       <c r="E34">
-        <v>5.44168</v>
+        <v>6.72168</v>
       </c>
       <c r="F34">
-        <v>5.81568</v>
+        <v>7.09568</v>
       </c>
       <c r="G34">
         <v>0.031</v>
       </c>
       <c r="H34">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -4003,37 +4003,37 @@
         <v>0.091</v>
       </c>
       <c r="M34">
-        <v>0.9215297991558441</v>
+        <v>1.694448384</v>
       </c>
       <c r="N34">
-        <v>-0.8305297991558441</v>
+        <v>-1.603448384</v>
       </c>
       <c r="O34">
-        <v>-0.2699221847256493</v>
+        <v>-0.5211207247999999</v>
       </c>
       <c r="P34">
-        <v>-0.5606076144301948</v>
+        <v>-1.0823276592</v>
       </c>
       <c r="Q34">
-        <v>-0.5046076144301948</v>
+        <v>-1.0263276592</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1389036005027524</v>
+        <v>0.2276257393270536</v>
       </c>
       <c r="T34">
-        <v>1.637671428351411</v>
+        <v>1.557749607563264</v>
       </c>
       <c r="U34">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V34">
-        <v>0.03209337346127256</v>
+        <v>0.01745405778025753</v>
       </c>
       <c r="W34">
-        <v>0.1533706804975246</v>
+        <v>0.2346319710020745</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.09874884141930018</v>
+        <v>0.05370479317002319</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4052,25 +4052,25 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1449666268044811</v>
+        <v>0.2318677334630603</v>
       </c>
       <c r="C35">
-        <v>5.89872957422009</v>
+        <v>7.495743516486746</v>
       </c>
       <c r="D35">
-        <v>11.86514957422009</v>
+        <v>14.78216351648675</v>
       </c>
       <c r="E35">
-        <v>5.62342</v>
+        <v>6.943420000000001</v>
       </c>
       <c r="F35">
-        <v>5.99742</v>
+        <v>7.31742</v>
       </c>
       <c r="G35">
         <v>0.031</v>
       </c>
       <c r="H35">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4085,37 +4085,37 @@
         <v>0.091</v>
       </c>
       <c r="M35">
-        <v>0.9503276053794644</v>
+        <v>1.747399896</v>
       </c>
       <c r="N35">
-        <v>-0.8593276053794644</v>
+        <v>-1.656399896</v>
       </c>
       <c r="O35">
-        <v>-0.279281471748326</v>
+        <v>-0.5383299662</v>
       </c>
       <c r="P35">
-        <v>-0.5800461336311384</v>
+        <v>-1.1180699298</v>
       </c>
       <c r="Q35">
-        <v>-0.5240461336311384</v>
+        <v>-1.0620699298</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1407514154356292</v>
+        <v>0.2304440339438753</v>
       </c>
       <c r="T35">
-        <v>1.662114285490984</v>
+        <v>1.580999601706</v>
       </c>
       <c r="U35">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V35">
-        <v>0.03112084699274915</v>
+        <v>0.01692514693843154</v>
       </c>
       <c r="W35">
-        <v>0.1535247832200287</v>
+        <v>0.2347582749111026</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.09575645228538199</v>
+        <v>0.05207737519517397</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4134,25 +4134,25 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1464001875078826</v>
+        <v>0.2338677334630603</v>
       </c>
       <c r="C36">
-        <v>5.587443588853065</v>
+        <v>7.122444227269021</v>
       </c>
       <c r="D36">
-        <v>11.73560358885307</v>
+        <v>14.63060422726902</v>
       </c>
       <c r="E36">
-        <v>5.805160000000001</v>
+        <v>7.165160000000001</v>
       </c>
       <c r="F36">
-        <v>6.17916</v>
+        <v>7.539160000000001</v>
       </c>
       <c r="G36">
         <v>0.031</v>
       </c>
       <c r="H36">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -4167,37 +4167,37 @@
         <v>0.091</v>
       </c>
       <c r="M36">
-        <v>0.9791254116030845</v>
+        <v>1.800351408</v>
       </c>
       <c r="N36">
-        <v>-0.8881254116030846</v>
+        <v>-1.709351408</v>
       </c>
       <c r="O36">
-        <v>-0.2886407587710025</v>
+        <v>-0.5555392076</v>
       </c>
       <c r="P36">
-        <v>-0.5994846528320821</v>
+        <v>-1.1538122004</v>
       </c>
       <c r="Q36">
-        <v>-0.543484652832082</v>
+        <v>-1.0978122004</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1426552247604115</v>
+        <v>0.2333477314278734</v>
       </c>
       <c r="T36">
-        <v>1.687297835271151</v>
+        <v>1.604954141125788</v>
       </c>
       <c r="U36">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V36">
-        <v>0.03020552796355064</v>
+        <v>0.01642734849906591</v>
       </c>
       <c r="W36">
-        <v>0.153669821076503</v>
+        <v>0.2348771491784231</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.09294008604169424</v>
+        <v>0.05054568768943357</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4216,25 +4216,25 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1478337482112842</v>
+        <v>0.2358677334630603</v>
       </c>
       <c r="C37">
-        <v>5.278955867475541</v>
+        <v>6.752221226321418</v>
       </c>
       <c r="D37">
-        <v>11.60885586747554</v>
+        <v>14.48212122632142</v>
       </c>
       <c r="E37">
-        <v>5.9869</v>
+        <v>7.386900000000001</v>
       </c>
       <c r="F37">
-        <v>6.3609</v>
+        <v>7.7609</v>
       </c>
       <c r="G37">
         <v>0.031</v>
       </c>
       <c r="H37">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -4249,37 +4249,37 @@
         <v>0.091</v>
       </c>
       <c r="M37">
-        <v>1.007923217826705</v>
+        <v>1.85330292</v>
       </c>
       <c r="N37">
-        <v>-0.9169232178267046</v>
+        <v>-1.76230292</v>
       </c>
       <c r="O37">
-        <v>-0.298000045793679</v>
+        <v>-0.572748449</v>
       </c>
       <c r="P37">
-        <v>-0.6189231720330256</v>
+        <v>-1.189554471</v>
       </c>
       <c r="Q37">
-        <v>-0.5629231720330257</v>
+        <v>-1.133554471</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1446176128336486</v>
+        <v>0.2363407734498407</v>
       </c>
       <c r="T37">
-        <v>1.713256263506092</v>
+        <v>1.629645743296954</v>
       </c>
       <c r="U37">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V37">
-        <v>0.02934251287887777</v>
+        <v>0.01595799568480688</v>
       </c>
       <c r="W37">
-        <v>0.1538065710554646</v>
+        <v>0.2349892306304681</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.09028465501193161</v>
+        <v>0.04910152518402111</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4298,25 +4298,25 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1492673089146858</v>
+        <v>0.2378677334630603</v>
       </c>
       <c r="C38">
-        <v>4.973176712798538</v>
+        <v>6.384981792793091</v>
       </c>
       <c r="D38">
-        <v>11.48481671279854</v>
+        <v>14.33662179279309</v>
       </c>
       <c r="E38">
-        <v>6.16864</v>
+        <v>7.60864</v>
       </c>
       <c r="F38">
-        <v>6.54264</v>
+        <v>7.98264</v>
       </c>
       <c r="G38">
         <v>0.031</v>
       </c>
       <c r="H38">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -4331,37 +4331,37 @@
         <v>0.091</v>
       </c>
       <c r="M38">
-        <v>1.036721024050325</v>
+        <v>1.906254432</v>
       </c>
       <c r="N38">
-        <v>-0.9457210240503247</v>
+        <v>-1.815254432</v>
       </c>
       <c r="O38">
-        <v>-0.3073593328163555</v>
+        <v>-0.5899576904</v>
       </c>
       <c r="P38">
-        <v>-0.6383616912339691</v>
+        <v>-1.2252967416</v>
       </c>
       <c r="Q38">
-        <v>-0.5823616912339691</v>
+        <v>-1.1692967416</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1466413255341744</v>
+        <v>0.2394273480349944</v>
       </c>
       <c r="T38">
-        <v>1.740025892623374</v>
+        <v>1.655108958035968</v>
       </c>
       <c r="U38">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V38">
-        <v>0.02852744307668672</v>
+        <v>0.01551471802689558</v>
       </c>
       <c r="W38">
-        <v>0.1539357238133727</v>
+        <v>0.2350950853351774</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.08777674792826684</v>
+        <v>0.04773759392890942</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4380,25 +4380,25 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1507008696180873</v>
+        <v>0.2398677334630603</v>
       </c>
       <c r="C39">
-        <v>4.670020220621108</v>
+        <v>6.02063689497216</v>
       </c>
       <c r="D39">
-        <v>11.36340022062111</v>
+        <v>14.19401689497216</v>
       </c>
       <c r="E39">
-        <v>6.35038</v>
+        <v>7.830380000000001</v>
       </c>
       <c r="F39">
-        <v>6.72438</v>
+        <v>8.20438</v>
       </c>
       <c r="G39">
         <v>0.031</v>
       </c>
       <c r="H39">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -4413,37 +4413,37 @@
         <v>0.091</v>
       </c>
       <c r="M39">
-        <v>1.065518830273945</v>
+        <v>1.959205944</v>
       </c>
       <c r="N39">
-        <v>-0.9745188302739449</v>
+        <v>-1.868205944</v>
       </c>
       <c r="O39">
-        <v>-0.3167186198390321</v>
+        <v>-0.6071669318</v>
       </c>
       <c r="P39">
-        <v>-0.6578002104349128</v>
+        <v>-1.2610390122</v>
       </c>
       <c r="Q39">
-        <v>-0.6018002104349127</v>
+        <v>-1.2050390122</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1487292830823359</v>
+        <v>0.242611909114915</v>
       </c>
       <c r="T39">
-        <v>1.767645351236443</v>
+        <v>1.681380528798444</v>
       </c>
       <c r="U39">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V39">
-        <v>0.02775643110164113</v>
+        <v>0.01509540132346597</v>
       </c>
       <c r="W39">
-        <v>0.1540578953411236</v>
+        <v>0.2351952181639563</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.08540440338966504</v>
+        <v>0.04644738868758758</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4462,25 +4462,25 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1521344303214889</v>
+        <v>0.2418677334630603</v>
       </c>
       <c r="C40">
-        <v>4.369404081426822</v>
+        <v>5.659101008615314</v>
       </c>
       <c r="D40">
-        <v>11.24452408142682</v>
+        <v>14.05422100861531</v>
       </c>
       <c r="E40">
-        <v>6.53212</v>
+        <v>8.052119999999999</v>
       </c>
       <c r="F40">
-        <v>6.90612</v>
+        <v>8.426119999999999</v>
       </c>
       <c r="G40">
         <v>0.031</v>
       </c>
       <c r="H40">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4495,37 +4495,37 @@
         <v>0.091</v>
       </c>
       <c r="M40">
-        <v>1.094316636497565</v>
+        <v>2.012157456</v>
       </c>
       <c r="N40">
-        <v>-1.003316636497565</v>
+        <v>-1.921157456</v>
       </c>
       <c r="O40">
-        <v>-0.3260779068617086</v>
+        <v>-0.6243761731999998</v>
       </c>
       <c r="P40">
-        <v>-0.6772387296358564</v>
+        <v>-1.2967812828</v>
       </c>
       <c r="Q40">
-        <v>-0.6212387296358564</v>
+        <v>-1.2407812828</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1508845940997929</v>
+        <v>0.2458991979716072</v>
       </c>
       <c r="T40">
-        <v>1.796155760127354</v>
+        <v>1.708499569585516</v>
       </c>
       <c r="U40">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V40">
-        <v>0.02702599870422952</v>
+        <v>0.01469815392021687</v>
       </c>
       <c r="W40">
-        <v>0.1541736367884666</v>
+        <v>0.2352900808438522</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.08315691908993694</v>
+        <v>0.04522508898528266</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4544,25 +4544,25 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1535679910248905</v>
+        <v>0.2438677334630603</v>
       </c>
       <c r="C41">
-        <v>4.071249394304735</v>
+        <v>5.300291945908313</v>
       </c>
       <c r="D41">
-        <v>11.12810939430473</v>
+        <v>13.91715194590831</v>
       </c>
       <c r="E41">
-        <v>6.71386</v>
+        <v>8.273859999999999</v>
       </c>
       <c r="F41">
-        <v>7.08786</v>
+        <v>8.64786</v>
       </c>
       <c r="G41">
         <v>0.031</v>
       </c>
       <c r="H41">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4577,37 +4577,37 @@
         <v>0.091</v>
       </c>
       <c r="M41">
-        <v>1.123114442721185</v>
+        <v>2.065108968</v>
       </c>
       <c r="N41">
-        <v>-1.032114442721185</v>
+        <v>-1.974108968</v>
       </c>
       <c r="O41">
-        <v>-0.3354371938843852</v>
+        <v>-0.6415854146</v>
       </c>
       <c r="P41">
-        <v>-0.6966772488368</v>
+        <v>-1.3325235534</v>
       </c>
       <c r="Q41">
-        <v>-0.6406772488368</v>
+        <v>-1.2765235534</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1531105710522485</v>
+        <v>0.2492942667908138</v>
       </c>
       <c r="T41">
-        <v>1.825600936522884</v>
+        <v>1.736507759250852</v>
       </c>
       <c r="U41">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V41">
-        <v>0.02633302437848005</v>
+        <v>0.01432127817867284</v>
       </c>
       <c r="W41">
-        <v>0.1542834427769715</v>
+        <v>0.2353800787709329</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.08102469039532323</v>
+        <v>0.04406547131899341</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4626,25 +4626,25 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1550015517282921</v>
+        <v>0.2458677334630603</v>
       </c>
       <c r="C42">
-        <v>3.775480492310768</v>
+        <v>4.944130694338561</v>
       </c>
       <c r="D42">
-        <v>11.01408049231077</v>
+        <v>13.78273069433856</v>
       </c>
       <c r="E42">
-        <v>6.895600000000001</v>
+        <v>8.4956</v>
       </c>
       <c r="F42">
-        <v>7.269600000000001</v>
+        <v>8.8696</v>
       </c>
       <c r="G42">
         <v>0.031</v>
       </c>
       <c r="H42">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4659,37 +4659,37 @@
         <v>0.091</v>
       </c>
       <c r="M42">
-        <v>1.151912248944805</v>
+        <v>2.11806048</v>
       </c>
       <c r="N42">
-        <v>-1.060912248944805</v>
+        <v>-2.02706048</v>
       </c>
       <c r="O42">
-        <v>-0.3447964809070617</v>
+        <v>-0.6587946559999999</v>
       </c>
       <c r="P42">
-        <v>-0.7161157680377436</v>
+        <v>-1.368265824</v>
       </c>
       <c r="Q42">
-        <v>-0.6601157680377436</v>
+        <v>-1.312265824</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1554107472364527</v>
+        <v>0.2528025045706607</v>
       </c>
       <c r="T42">
-        <v>1.856027618798266</v>
+        <v>1.765449555238366</v>
       </c>
       <c r="U42">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V42">
-        <v>0.02567469876901804</v>
+        <v>0.01396324622420602</v>
       </c>
       <c r="W42">
-        <v>0.1543877584660511</v>
+        <v>0.2354655768016596</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.07899907313544008</v>
+        <v>0.0429638345360186</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4708,25 +4708,25 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1564351124316936</v>
+        <v>0.2478677334630602</v>
       </c>
       <c r="C43">
-        <v>3.482024778457221</v>
+        <v>4.590541264816011</v>
       </c>
       <c r="D43">
-        <v>10.90236477845722</v>
+        <v>13.65088126481601</v>
       </c>
       <c r="E43">
-        <v>7.07734</v>
+        <v>8.71734</v>
       </c>
       <c r="F43">
-        <v>7.45134</v>
+        <v>9.091340000000001</v>
       </c>
       <c r="G43">
         <v>0.031</v>
       </c>
       <c r="H43">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -4741,37 +4741,37 @@
         <v>0.091</v>
       </c>
       <c r="M43">
-        <v>1.180710055168425</v>
+        <v>2.171011992</v>
       </c>
       <c r="N43">
-        <v>-1.089710055168425</v>
+        <v>-2.080011992</v>
       </c>
       <c r="O43">
-        <v>-0.3541557679297382</v>
+        <v>-0.6760038974</v>
       </c>
       <c r="P43">
-        <v>-0.7355542872386871</v>
+        <v>-1.4040080946</v>
       </c>
       <c r="Q43">
-        <v>-0.679554287238687</v>
+        <v>-1.3480080946</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1577888954946976</v>
+        <v>0.2564296656650786</v>
       </c>
       <c r="T43">
-        <v>1.887485714032135</v>
+        <v>1.795372429055966</v>
       </c>
       <c r="U43">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V43">
-        <v>0.02504848660392005</v>
+        <v>0.01362267924312782</v>
       </c>
       <c r="W43">
-        <v>0.1544869855849318</v>
+        <v>0.2355469041967411</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.0770722664736001</v>
+        <v>0.04191593613270106</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4790,25 +4790,25 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1578686731350952</v>
+        <v>0.2498677334630603</v>
       </c>
       <c r="C44">
-        <v>3.190812571583402</v>
+        <v>4.239450548428987</v>
       </c>
       <c r="D44">
-        <v>10.7928925715834</v>
+        <v>13.52153054842899</v>
       </c>
       <c r="E44">
-        <v>7.25908</v>
+        <v>8.939079999999999</v>
       </c>
       <c r="F44">
-        <v>7.63308</v>
+        <v>9.313079999999999</v>
       </c>
       <c r="G44">
         <v>0.031</v>
       </c>
       <c r="H44">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4823,37 +4823,37 @@
         <v>0.091</v>
       </c>
       <c r="M44">
-        <v>1.209507861392045</v>
+        <v>2.223963504</v>
       </c>
       <c r="N44">
-        <v>-1.118507861392045</v>
+        <v>-2.132963504</v>
       </c>
       <c r="O44">
-        <v>-0.3635150549524148</v>
+        <v>-0.6932131387999998</v>
       </c>
       <c r="P44">
-        <v>-0.7549928064396306</v>
+        <v>-1.4397503652</v>
       </c>
       <c r="Q44">
-        <v>-0.6989928064396307</v>
+        <v>-1.3837503652</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1602490488652959</v>
+        <v>0.2601819012799939</v>
       </c>
       <c r="T44">
-        <v>1.92002857117062</v>
+        <v>1.826327126108655</v>
       </c>
       <c r="U44">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V44">
-        <v>0.02445209406573148</v>
+        <v>0.01329832973733907</v>
       </c>
       <c r="W44">
-        <v>0.1545814876029133</v>
+        <v>0.2356243588587235</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.07523721250994297</v>
+        <v>0.04091793765335106</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4872,25 +4872,25 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1593022338384968</v>
+        <v>0.2518677334630603</v>
       </c>
       <c r="C45">
-        <v>2.901776961419794</v>
+        <v>3.89078818126753</v>
       </c>
       <c r="D45">
-        <v>10.68559696141979</v>
+        <v>13.39460818126753</v>
       </c>
       <c r="E45">
-        <v>7.44082</v>
+        <v>9.160819999999999</v>
       </c>
       <c r="F45">
-        <v>7.81482</v>
+        <v>9.53482</v>
       </c>
       <c r="G45">
         <v>0.031</v>
       </c>
       <c r="H45">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4905,37 +4905,37 @@
         <v>0.091</v>
       </c>
       <c r="M45">
-        <v>1.238305667615666</v>
+        <v>2.276915016</v>
       </c>
       <c r="N45">
-        <v>-1.147305667615666</v>
+        <v>-2.185915016</v>
       </c>
       <c r="O45">
-        <v>-0.3728743419750913</v>
+        <v>-0.7104223801999999</v>
       </c>
       <c r="P45">
-        <v>-0.7744313256405744</v>
+        <v>-1.4754926358</v>
       </c>
       <c r="Q45">
-        <v>-0.7184313256405743</v>
+        <v>-1.4194926358</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1627955234067923</v>
+        <v>0.264065794284906</v>
       </c>
       <c r="T45">
-        <v>1.953713282945543</v>
+        <v>1.858367952882491</v>
       </c>
       <c r="U45">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V45">
-        <v>0.02388344071536562</v>
+        <v>0.01298906625507537</v>
       </c>
       <c r="W45">
-        <v>0.154671594178198</v>
+        <v>0.235698210978288</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.07348750989343267</v>
+        <v>0.03996635770792434</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4954,25 +4954,25 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1607357945418983</v>
+        <v>0.2538677334630603</v>
       </c>
       <c r="C46">
-        <v>2.614853672212198</v>
+        <v>3.5444864167891</v>
       </c>
       <c r="D46">
-        <v>10.5804136722122</v>
+        <v>13.2700464167891</v>
       </c>
       <c r="E46">
-        <v>7.62256</v>
+        <v>9.38256</v>
       </c>
       <c r="F46">
-        <v>7.99656</v>
+        <v>9.75656</v>
       </c>
       <c r="G46">
         <v>0.031</v>
       </c>
       <c r="H46">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4987,37 +4987,37 @@
         <v>0.091</v>
       </c>
       <c r="M46">
-        <v>1.267103473839286</v>
+        <v>2.329866528</v>
       </c>
       <c r="N46">
-        <v>-1.176103473839286</v>
+        <v>-2.238866528</v>
       </c>
       <c r="O46">
-        <v>-0.3822336289977679</v>
+        <v>-0.7276316215999999</v>
       </c>
       <c r="P46">
-        <v>-0.7938698448415178</v>
+        <v>-1.5112349064</v>
       </c>
       <c r="Q46">
-        <v>-0.7378698448415177</v>
+        <v>-1.4552349064</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1654329434676279</v>
+        <v>0.2680883977542793</v>
       </c>
       <c r="T46">
-        <v>1.988601020140999</v>
+        <v>1.89155309489825</v>
       </c>
       <c r="U46">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V46">
-        <v>0.02334063524456186</v>
+        <v>0.01269386020382366</v>
       </c>
       <c r="W46">
-        <v>0.1547576050000607</v>
+        <v>0.2357687061833269</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.07181733921403644</v>
+        <v>0.03905803139638053</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1621693552452999</v>
+        <v>0.2558677334630603</v>
       </c>
       <c r="C47">
-        <v>2.329980934321847</v>
+        <v>3.200480005240216</v>
       </c>
       <c r="D47">
-        <v>10.47728093432185</v>
+        <v>13.14778000524022</v>
       </c>
       <c r="E47">
-        <v>7.8043</v>
+        <v>9.6043</v>
       </c>
       <c r="F47">
-        <v>8.1783</v>
+        <v>9.978300000000001</v>
       </c>
       <c r="G47">
         <v>0.031</v>
       </c>
       <c r="H47">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -5069,37 +5069,37 @@
         <v>0.091</v>
       </c>
       <c r="M47">
-        <v>1.295901280062906</v>
+        <v>2.382818040000001</v>
       </c>
       <c r="N47">
-        <v>-1.204901280062906</v>
+        <v>-2.29181804</v>
       </c>
       <c r="O47">
-        <v>-0.3915929160204444</v>
+        <v>-0.744840863</v>
       </c>
       <c r="P47">
-        <v>-0.8133083640424615</v>
+        <v>-1.546977177</v>
       </c>
       <c r="Q47">
-        <v>-0.7573083640424616</v>
+        <v>-1.490977177</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1681662697124938</v>
+        <v>0.272257277713448</v>
       </c>
       <c r="T47">
-        <v>2.024757402325381</v>
+        <v>1.925944969350945</v>
       </c>
       <c r="U47">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V47">
-        <v>0.02282195446134937</v>
+        <v>0.01241177442151646</v>
       </c>
       <c r="W47">
-        <v>0.1548397931187296</v>
+        <v>0.2358360682681419</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.07022139834261343</v>
+        <v>0.03819007514312767</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5118,25 +5118,25 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1636029159487015</v>
+        <v>0.2578677334630603</v>
       </c>
       <c r="C48">
-        <v>2.047099363262527</v>
+        <v>2.85870607968306</v>
       </c>
       <c r="D48">
-        <v>10.37613936326253</v>
+        <v>13.02774607968306</v>
       </c>
       <c r="E48">
-        <v>7.98604</v>
+        <v>9.826039999999999</v>
       </c>
       <c r="F48">
-        <v>8.36004</v>
+        <v>10.20004</v>
       </c>
       <c r="G48">
         <v>0.031</v>
       </c>
       <c r="H48">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5151,37 +5151,37 @@
         <v>0.091</v>
       </c>
       <c r="M48">
-        <v>1.324699086286526</v>
+        <v>2.435769552</v>
       </c>
       <c r="N48">
-        <v>-1.233699086286526</v>
+        <v>-2.344769552</v>
       </c>
       <c r="O48">
-        <v>-0.400952203043121</v>
+        <v>-0.7620501043999999</v>
       </c>
       <c r="P48">
-        <v>-0.8327468832434051</v>
+        <v>-1.5827194476</v>
       </c>
       <c r="Q48">
-        <v>-0.776746883243405</v>
+        <v>-1.5267194476</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1710008302627252</v>
+        <v>0.2765805606340675</v>
       </c>
       <c r="T48">
-        <v>2.062252909775851</v>
+        <v>1.961610616931518</v>
       </c>
       <c r="U48">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V48">
-        <v>0.02232582501653743</v>
+        <v>0.01214195323844002</v>
       </c>
       <c r="W48">
-        <v>0.1549184078409345</v>
+        <v>0.2359005015666605</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.06869484620473054</v>
+        <v>0.03735985611827708</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5200,25 +5200,25 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.165036476652103</v>
+        <v>0.2598677334630603</v>
       </c>
       <c r="C49">
-        <v>1.766151845676893</v>
+        <v>2.519104048208799</v>
       </c>
       <c r="D49">
-        <v>10.27693184567689</v>
+        <v>12.9098840482088</v>
       </c>
       <c r="E49">
-        <v>8.16778</v>
+        <v>10.04778</v>
       </c>
       <c r="F49">
-        <v>8.541780000000001</v>
+        <v>10.42178</v>
       </c>
       <c r="G49">
         <v>0.031</v>
       </c>
       <c r="H49">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -5233,37 +5233,37 @@
         <v>0.091</v>
       </c>
       <c r="M49">
-        <v>1.353496892510146</v>
+        <v>2.488721064</v>
       </c>
       <c r="N49">
-        <v>-1.262496892510146</v>
+        <v>-2.397721064</v>
       </c>
       <c r="O49">
-        <v>-0.4103114900657975</v>
+        <v>-0.7792593457999998</v>
       </c>
       <c r="P49">
-        <v>-0.8521854024443487</v>
+        <v>-1.6184617182</v>
       </c>
       <c r="Q49">
-        <v>-0.7961854024443487</v>
+        <v>-1.5624617182</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1739423553620219</v>
+        <v>0.2810669863064084</v>
       </c>
       <c r="T49">
-        <v>2.101163342035772</v>
+        <v>1.998622138005698</v>
       </c>
       <c r="U49">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V49">
-        <v>0.02185080746299408</v>
+        <v>0.01188361380783491</v>
       </c>
       <c r="W49">
-        <v>0.1549936772558116</v>
+        <v>0.235962193022689</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.0672332537322895</v>
+        <v>0.03656496556256905</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5282,25 +5282,25 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1664700373555046</v>
+        <v>0.2618677334630603</v>
       </c>
       <c r="C50">
-        <v>1.487083431792067</v>
+        <v>2.181615491949348</v>
       </c>
       <c r="D50">
-        <v>10.17960343179207</v>
+        <v>12.79413549194935</v>
       </c>
       <c r="E50">
-        <v>8.349519999999998</v>
+        <v>10.26952</v>
       </c>
       <c r="F50">
-        <v>8.723519999999999</v>
+        <v>10.64352</v>
       </c>
       <c r="G50">
         <v>0.031</v>
       </c>
       <c r="H50">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5315,37 +5315,37 @@
         <v>0.091</v>
       </c>
       <c r="M50">
-        <v>1.382294698733766</v>
+        <v>2.541672576</v>
       </c>
       <c r="N50">
-        <v>-1.291294698733766</v>
+        <v>-2.450672576</v>
       </c>
       <c r="O50">
-        <v>-0.419670777088474</v>
+        <v>-0.7964685871999998</v>
       </c>
       <c r="P50">
-        <v>-0.8716239216452921</v>
+        <v>-1.6542039888</v>
       </c>
       <c r="Q50">
-        <v>-0.8156239216452921</v>
+        <v>-1.5982039888</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1769970160420608</v>
+        <v>0.2857259668123008</v>
       </c>
       <c r="T50">
-        <v>2.141570329382614</v>
+        <v>2.037057179121192</v>
       </c>
       <c r="U50">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V50">
-        <v>0.02139558230751504</v>
+        <v>0.01163603852017169</v>
       </c>
       <c r="W50">
-        <v>0.1550658104450688</v>
+        <v>0.236021314001383</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.06583256094620016</v>
+        <v>0.0358031954466822</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5364,25 +5364,25 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1679035980589062</v>
+        <v>0.2638677334630603</v>
       </c>
       <c r="C51">
-        <v>1.209841233928875</v>
+        <v>1.846184068526814</v>
       </c>
       <c r="D51">
-        <v>10.08410123392887</v>
+        <v>12.68044406852681</v>
       </c>
       <c r="E51">
-        <v>8.53126</v>
+        <v>10.49126</v>
       </c>
       <c r="F51">
-        <v>8.90526</v>
+        <v>10.86526</v>
       </c>
       <c r="G51">
         <v>0.031</v>
       </c>
       <c r="H51">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5397,37 +5397,37 @@
         <v>0.091</v>
       </c>
       <c r="M51">
-        <v>1.411092504957386</v>
+        <v>2.594624088</v>
       </c>
       <c r="N51">
-        <v>-1.320092504957386</v>
+        <v>-2.503624088</v>
       </c>
       <c r="O51">
-        <v>-0.4290300641111506</v>
+        <v>-0.8136778285999997</v>
       </c>
       <c r="P51">
-        <v>-0.8910624408462358</v>
+        <v>-1.6899462594</v>
       </c>
       <c r="Q51">
-        <v>-0.8350624408462357</v>
+        <v>-1.6339462594</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1801714673370031</v>
+        <v>0.2905676524360715</v>
       </c>
       <c r="T51">
-        <v>2.183561904468548</v>
+        <v>2.076999476751019</v>
       </c>
       <c r="U51">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V51">
-        <v>0.02095893777062698</v>
+        <v>0.01139856834629063</v>
       </c>
       <c r="W51">
-        <v>0.1551349994225195</v>
+        <v>0.2360780218789058</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.06448903929423688</v>
+        <v>0.03507251798858668</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5446,25 +5446,25 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1693371587623078</v>
+        <v>0.2658677334630603</v>
       </c>
       <c r="C52">
-        <v>0.9343743306710035</v>
+        <v>1.512755420605473</v>
       </c>
       <c r="D52">
-        <v>9.990374330671003</v>
+        <v>12.56875542060547</v>
       </c>
       <c r="E52">
-        <v>8.712999999999999</v>
+        <v>10.713</v>
       </c>
       <c r="F52">
-        <v>9.087</v>
+        <v>11.087</v>
       </c>
       <c r="G52">
         <v>0.031</v>
       </c>
       <c r="H52">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5479,37 +5479,37 @@
         <v>0.091</v>
       </c>
       <c r="M52">
-        <v>1.439890311181007</v>
+        <v>2.6475756</v>
       </c>
       <c r="N52">
-        <v>-1.348890311181007</v>
+        <v>-2.5565756</v>
       </c>
       <c r="O52">
-        <v>-0.4383893511338272</v>
+        <v>-0.8308870699999998</v>
       </c>
       <c r="P52">
-        <v>-0.9105009600471795</v>
+        <v>-1.72568853</v>
       </c>
       <c r="Q52">
-        <v>-0.8545009600471796</v>
+        <v>-1.66968853</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1834728966837432</v>
+        <v>0.2956030054847928</v>
       </c>
       <c r="T52">
-        <v>2.227233142557919</v>
+        <v>2.11853946628604</v>
       </c>
       <c r="U52">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V52">
-        <v>0.02053975901521444</v>
+        <v>0.01117059697936482</v>
       </c>
       <c r="W52">
-        <v>0.1552014208408723</v>
+        <v>0.2361324614413277</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.06319925850835206</v>
+        <v>0.03437106762881492</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5528,25 +5528,25 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1707707194657093</v>
+        <v>0.2678677334630603</v>
       </c>
       <c r="C53">
-        <v>0.6606336763290894</v>
+        <v>1.181277089234307</v>
       </c>
       <c r="D53">
-        <v>9.898373676329088</v>
+        <v>12.45901708923431</v>
       </c>
       <c r="E53">
-        <v>8.894739999999999</v>
+        <v>10.93474</v>
       </c>
       <c r="F53">
-        <v>9.268739999999999</v>
+        <v>11.30874</v>
       </c>
       <c r="G53">
         <v>0.031</v>
       </c>
       <c r="H53">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -5561,37 +5561,37 @@
         <v>0.091</v>
       </c>
       <c r="M53">
-        <v>1.468688117404627</v>
+        <v>2.700527112</v>
       </c>
       <c r="N53">
-        <v>-1.377688117404627</v>
+        <v>-2.609527112</v>
       </c>
       <c r="O53">
-        <v>-0.4477486381565037</v>
+        <v>-0.8480963113999999</v>
       </c>
       <c r="P53">
-        <v>-0.929939479248123</v>
+        <v>-1.7614308006</v>
       </c>
       <c r="Q53">
-        <v>-0.873939479248123</v>
+        <v>-1.7054308006</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1869090782487175</v>
+        <v>0.3008438831477478</v>
       </c>
       <c r="T53">
-        <v>2.272686880161142</v>
+        <v>2.161774965598</v>
       </c>
       <c r="U53">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V53">
-        <v>0.0201370186423671</v>
+        <v>0.01095156566604394</v>
       </c>
       <c r="W53">
-        <v>0.155265237497721</v>
+        <v>0.2361847661189487</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.06196005736112953</v>
+        <v>0.03369712512628908</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5610,25 +5610,25 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1722042801691109</v>
+        <v>0.2698677334630603</v>
       </c>
       <c r="C54">
-        <v>0.3885720153616354</v>
+        <v>0.8516984316899663</v>
       </c>
       <c r="D54">
-        <v>9.808052015361636</v>
+        <v>12.35117843168997</v>
       </c>
       <c r="E54">
-        <v>9.07648</v>
+        <v>11.15648</v>
       </c>
       <c r="F54">
-        <v>9.450480000000001</v>
+        <v>11.53048</v>
       </c>
       <c r="G54">
         <v>0.031</v>
       </c>
       <c r="H54">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -5643,37 +5643,37 @@
         <v>0.091</v>
       </c>
       <c r="M54">
-        <v>1.497485923628247</v>
+        <v>2.753478624</v>
       </c>
       <c r="N54">
-        <v>-1.406485923628247</v>
+        <v>-2.662478624</v>
       </c>
       <c r="O54">
-        <v>-0.4571079251791803</v>
+        <v>-0.8653055528</v>
       </c>
       <c r="P54">
-        <v>-0.9493779984490667</v>
+        <v>-1.7971730712</v>
       </c>
       <c r="Q54">
-        <v>-0.8933779984490666</v>
+        <v>-1.7411730712</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1904884340455659</v>
+        <v>0.3063031307133259</v>
       </c>
       <c r="T54">
-        <v>2.320034523497833</v>
+        <v>2.206811944047958</v>
       </c>
       <c r="U54">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V54">
-        <v>0.01974976828386003</v>
+        <v>0.01074095863400463</v>
       </c>
       <c r="W54">
-        <v>0.1553265996677679</v>
+        <v>0.2362350590781997</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.06076851779649239</v>
+        <v>0.03304910348924506</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5692,25 +5692,25 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1736378408725124</v>
+        <v>0.2718677334630603</v>
       </c>
       <c r="C55">
-        <v>0.1181438014389613</v>
+        <v>0.5239705435497406</v>
       </c>
       <c r="D55">
-        <v>9.719363801438961</v>
+        <v>12.24519054354974</v>
       </c>
       <c r="E55">
-        <v>9.25822</v>
+        <v>11.37822</v>
       </c>
       <c r="F55">
-        <v>9.63222</v>
+        <v>11.75222</v>
       </c>
       <c r="G55">
         <v>0.031</v>
       </c>
       <c r="H55">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5725,37 +5725,37 @@
         <v>0.091</v>
       </c>
       <c r="M55">
-        <v>1.526283729851867</v>
+        <v>2.806430136</v>
       </c>
       <c r="N55">
-        <v>-1.435283729851867</v>
+        <v>-2.715430136</v>
       </c>
       <c r="O55">
-        <v>-0.4664672122018568</v>
+        <v>-0.8825147941999998</v>
       </c>
       <c r="P55">
-        <v>-0.9688165176500103</v>
+        <v>-1.8329153418</v>
       </c>
       <c r="Q55">
-        <v>-0.9128165176500103</v>
+        <v>-1.7769153418</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.194220102855046</v>
+        <v>0.3119946866859498</v>
       </c>
       <c r="T55">
-        <v>2.369396960167999</v>
+        <v>2.253765389665999</v>
       </c>
       <c r="U55">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V55">
-        <v>0.01937713114642872</v>
+        <v>0.01053829903713662</v>
       </c>
       <c r="W55">
-        <v>0.155385646284228</v>
+        <v>0.2362834541899318</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.05962194198901138</v>
+        <v>0.03242553549888194</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5774,25 +5774,25 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1750714015759141</v>
+        <v>0.2738677334630603</v>
       </c>
       <c r="C56">
-        <v>-0.1506948791411098</v>
+        <v>0.1980461847425889</v>
       </c>
       <c r="D56">
-        <v>9.632265120858889</v>
+        <v>12.14100618474259</v>
       </c>
       <c r="E56">
-        <v>9.439959999999999</v>
+        <v>11.59996</v>
       </c>
       <c r="F56">
-        <v>9.81396</v>
+        <v>11.97396</v>
       </c>
       <c r="G56">
         <v>0.031</v>
       </c>
       <c r="H56">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5807,37 +5807,37 @@
         <v>0.091</v>
       </c>
       <c r="M56">
-        <v>1.555081536075487</v>
+        <v>2.859381648</v>
       </c>
       <c r="N56">
-        <v>-1.464081536075487</v>
+        <v>-2.768381648</v>
       </c>
       <c r="O56">
-        <v>-0.4758264992245333</v>
+        <v>-0.8997240355999999</v>
       </c>
       <c r="P56">
-        <v>-0.9882550368509537</v>
+        <v>-1.8686576124</v>
       </c>
       <c r="Q56">
-        <v>-0.9322550368509537</v>
+        <v>-1.8126576124</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1981140181345035</v>
+        <v>0.3179337016139053</v>
       </c>
       <c r="T56">
-        <v>2.420905589736869</v>
+        <v>2.302760289441347</v>
       </c>
       <c r="U56">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V56">
-        <v>0.01901829538445781</v>
+        <v>0.01034314535126372</v>
       </c>
       <c r="W56">
-        <v>0.1554425059889675</v>
+        <v>0.2363300568901182</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.05851783195217786</v>
+        <v>0.03182506261927309</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5856,25 +5856,25 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1765049622793156</v>
+        <v>0.2758677334630603</v>
       </c>
       <c r="C57">
-        <v>-0.4179863799562664</v>
+        <v>-0.1261202906565586</v>
       </c>
       <c r="D57">
-        <v>9.546713620043734</v>
+        <v>12.03857970934344</v>
       </c>
       <c r="E57">
-        <v>9.621700000000001</v>
+        <v>11.8217</v>
       </c>
       <c r="F57">
-        <v>9.995700000000001</v>
+        <v>12.1957</v>
       </c>
       <c r="G57">
         <v>0.031</v>
       </c>
       <c r="H57">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5889,37 +5889,37 @@
         <v>0.091</v>
       </c>
       <c r="M57">
-        <v>1.583879342299107</v>
+        <v>2.91233316</v>
       </c>
       <c r="N57">
-        <v>-1.492879342299107</v>
+        <v>-2.82133316</v>
       </c>
       <c r="O57">
-        <v>-0.4851857862472099</v>
+        <v>-0.9169332769999998</v>
       </c>
       <c r="P57">
-        <v>-1.007693556051897</v>
+        <v>-1.904399883</v>
       </c>
       <c r="Q57">
-        <v>-0.9516935560518973</v>
+        <v>-1.848399883</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.2021809963152703</v>
+        <v>0.324136672760881</v>
       </c>
       <c r="T57">
-        <v>2.474703491731022</v>
+        <v>2.353932740317822</v>
       </c>
       <c r="U57">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V57">
-        <v>0.01867250819564949</v>
+        <v>0.01015508816305892</v>
       </c>
       <c r="W57">
-        <v>0.15549729806808</v>
+        <v>0.2363749649466615</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.05745387137122915</v>
+        <v>0.0312464251171044</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5938,25 +5938,25 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1779385229827172</v>
+        <v>0.2778677334630603</v>
       </c>
       <c r="C58">
-        <v>-0.6837715631330727</v>
+        <v>-0.4485730011085813</v>
       </c>
       <c r="D58">
-        <v>9.462668436866927</v>
+        <v>11.93786699889142</v>
       </c>
       <c r="E58">
-        <v>9.80344</v>
+        <v>12.04344</v>
       </c>
       <c r="F58">
-        <v>10.17744</v>
+        <v>12.41744</v>
       </c>
       <c r="G58">
         <v>0.031</v>
       </c>
       <c r="H58">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5971,37 +5971,37 @@
         <v>0.091</v>
       </c>
       <c r="M58">
-        <v>1.612677148522727</v>
+        <v>2.965284672000001</v>
       </c>
       <c r="N58">
-        <v>-1.521677148522727</v>
+        <v>-2.874284672</v>
       </c>
       <c r="O58">
-        <v>-0.4945450732698864</v>
+        <v>-0.9341425184</v>
       </c>
       <c r="P58">
-        <v>-1.027132075252841</v>
+        <v>-1.940142153600001</v>
       </c>
       <c r="Q58">
-        <v>-0.971132075252841</v>
+        <v>-1.8841421536</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.2064328371406173</v>
+        <v>0.3306215971418101</v>
       </c>
       <c r="T58">
-        <v>2.530946752906726</v>
+        <v>2.407431211688682</v>
       </c>
       <c r="U58">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V58">
-        <v>0.01833907054929861</v>
+        <v>0.009973747303004299</v>
       </c>
       <c r="W58">
-        <v>0.1555501332872242</v>
+        <v>0.2364182691440426</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.05642790938245723</v>
+        <v>0.03068845324001335</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6020,25 +6020,25 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1793720836861187</v>
+        <v>0.2798677334630603</v>
       </c>
       <c r="C59">
-        <v>-0.9480898644245457</v>
+        <v>-0.7693546009726404</v>
       </c>
       <c r="D59">
-        <v>9.380090135575454</v>
+        <v>11.83882539902736</v>
       </c>
       <c r="E59">
-        <v>9.98518</v>
+        <v>12.26518</v>
       </c>
       <c r="F59">
-        <v>10.35918</v>
+        <v>12.63918</v>
       </c>
       <c r="G59">
         <v>0.031</v>
       </c>
       <c r="H59">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6053,37 +6053,37 @@
         <v>0.091</v>
       </c>
       <c r="M59">
-        <v>1.641474954746348</v>
+        <v>3.018236184</v>
       </c>
       <c r="N59">
-        <v>-1.550474954746348</v>
+        <v>-2.927236184</v>
       </c>
       <c r="O59">
-        <v>-0.503904360292563</v>
+        <v>-0.9513517598</v>
       </c>
       <c r="P59">
-        <v>-1.046570594453785</v>
+        <v>-1.9758844242</v>
       </c>
       <c r="Q59">
-        <v>-0.9905705944537846</v>
+        <v>-1.9198844242</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.2108824380043526</v>
+        <v>0.3374081459125499</v>
       </c>
       <c r="T59">
-        <v>2.58980597971851</v>
+        <v>2.463417984053535</v>
       </c>
       <c r="U59">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V59">
-        <v>0.01801733246948635</v>
+        <v>0.009798769280144575</v>
       </c>
       <c r="W59">
-        <v>0.1556011146390301</v>
+        <v>0.2364600538959015</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.055437946059958</v>
+        <v>0.03015005932352188</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6102,25 +6102,25 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1808056443895203</v>
+        <v>0.2818677334630603</v>
       </c>
       <c r="C60">
-        <v>-1.210979354909712</v>
+        <v>-1.088506340740443</v>
       </c>
       <c r="D60">
-        <v>9.298940645090287</v>
+        <v>11.74141365925956</v>
       </c>
       <c r="E60">
-        <v>10.16692</v>
+        <v>12.48692</v>
       </c>
       <c r="F60">
-        <v>10.54092</v>
+        <v>12.86092</v>
       </c>
       <c r="G60">
         <v>0.031</v>
       </c>
       <c r="H60">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6135,37 +6135,37 @@
         <v>0.091</v>
       </c>
       <c r="M60">
-        <v>1.670272760969968</v>
+        <v>3.071187696</v>
       </c>
       <c r="N60">
-        <v>-1.579272760969968</v>
+        <v>-2.980187696</v>
       </c>
       <c r="O60">
-        <v>-0.5132636473152395</v>
+        <v>-0.9685610011999998</v>
       </c>
       <c r="P60">
-        <v>-1.066009113654728</v>
+        <v>-2.0116266948</v>
       </c>
       <c r="Q60">
-        <v>-1.010009113654728</v>
+        <v>-1.9556266948</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.2155439246235038</v>
+        <v>0.3445178636723724</v>
       </c>
       <c r="T60">
-        <v>2.651468026854665</v>
+        <v>2.522070793197666</v>
       </c>
       <c r="U60">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V60">
-        <v>0.01770668880621934</v>
+        <v>0.009629824982211051</v>
       </c>
       <c r="W60">
-        <v>0.1556503380131874</v>
+        <v>0.236500397794248</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.05448211940375181</v>
+        <v>0.02963023071449555</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6184,25 +6184,25 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1822392050929219</v>
+        <v>0.2838677334630603</v>
       </c>
       <c r="C61">
-        <v>-1.472476799517958</v>
+        <v>-1.40606812432118</v>
       </c>
       <c r="D61">
-        <v>9.219183200482041</v>
+        <v>11.64559187567882</v>
       </c>
       <c r="E61">
-        <v>10.34866</v>
+        <v>12.70866</v>
       </c>
       <c r="F61">
-        <v>10.72266</v>
+        <v>13.08266</v>
       </c>
       <c r="G61">
         <v>0.031</v>
       </c>
       <c r="H61">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6217,37 +6217,37 @@
         <v>0.091</v>
       </c>
       <c r="M61">
-        <v>1.699070567193588</v>
+        <v>3.124139208</v>
       </c>
       <c r="N61">
-        <v>-1.608070567193588</v>
+        <v>-3.033139208</v>
       </c>
       <c r="O61">
-        <v>-0.5226229343379161</v>
+        <v>-0.9857702425999998</v>
       </c>
       <c r="P61">
-        <v>-1.085447632855672</v>
+        <v>-2.0473689654</v>
       </c>
       <c r="Q61">
-        <v>-1.029447632855672</v>
+        <v>-1.9913689654</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.2204328008338332</v>
+        <v>0.3519743969326742</v>
       </c>
       <c r="T61">
-        <v>2.716137978729169</v>
+        <v>2.583584714982975</v>
       </c>
       <c r="U61">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V61">
-        <v>0.01740657543662241</v>
+        <v>0.009466607609631202</v>
       </c>
       <c r="W61">
-        <v>0.1556978927983903</v>
+        <v>0.2365393741028201</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.05355869365114585</v>
+        <v>0.02912802341424992</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6266,25 +6266,25 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1836727657963235</v>
+        <v>0.2858677334630603</v>
       </c>
       <c r="C62">
-        <v>-1.732617712567221</v>
+        <v>-1.722078563544034</v>
       </c>
       <c r="D62">
-        <v>9.140782287432778</v>
+        <v>11.55132143645596</v>
       </c>
       <c r="E62">
-        <v>10.5304</v>
+        <v>12.9304</v>
       </c>
       <c r="F62">
-        <v>10.9044</v>
+        <v>13.3044</v>
       </c>
       <c r="G62">
         <v>0.031</v>
       </c>
       <c r="H62">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6299,37 +6299,37 @@
         <v>0.091</v>
       </c>
       <c r="M62">
-        <v>1.727868373417208</v>
+        <v>3.17709072</v>
       </c>
       <c r="N62">
-        <v>-1.636868373417208</v>
+        <v>-3.08609072</v>
       </c>
       <c r="O62">
-        <v>-0.5319822213605926</v>
+        <v>-1.002979484</v>
       </c>
       <c r="P62">
-        <v>-1.104886152056615</v>
+        <v>-2.083111236</v>
       </c>
       <c r="Q62">
-        <v>-1.048886152056615</v>
+        <v>-2.027111236</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.225566120854679</v>
+        <v>0.3598037568559911</v>
       </c>
       <c r="T62">
-        <v>2.784041428197398</v>
+        <v>2.64817433285755</v>
       </c>
       <c r="U62">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V62">
-        <v>0.01711646584601203</v>
+        <v>0.009308830816137348</v>
       </c>
       <c r="W62">
-        <v>0.1557438624240864</v>
+        <v>0.2365770512011064</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.05266604875696013</v>
+        <v>0.02864255635734581</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6348,25 +6348,25 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.185106326499725</v>
+        <v>0.2878677334630603</v>
       </c>
       <c r="C63">
-        <v>-1.991436410492229</v>
+        <v>-2.036575030034857</v>
       </c>
       <c r="D63">
-        <v>9.063703589507771</v>
+        <v>11.45856496996514</v>
       </c>
       <c r="E63">
-        <v>10.71214</v>
+        <v>13.15214</v>
       </c>
       <c r="F63">
-        <v>11.08614</v>
+        <v>13.52614</v>
       </c>
       <c r="G63">
         <v>0.031</v>
       </c>
       <c r="H63">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6381,37 +6381,37 @@
         <v>0.091</v>
       </c>
       <c r="M63">
-        <v>1.756666179640828</v>
+        <v>3.230042232</v>
       </c>
       <c r="N63">
-        <v>-1.665666179640828</v>
+        <v>-3.139042232</v>
       </c>
       <c r="O63">
-        <v>-0.5413415083832691</v>
+        <v>-1.0201887254</v>
       </c>
       <c r="P63">
-        <v>-1.124324671257559</v>
+        <v>-2.1188535066</v>
       </c>
       <c r="Q63">
-        <v>-1.068324671257559</v>
+        <v>-2.0628535066</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.230962688056081</v>
+        <v>0.3680346224164011</v>
       </c>
       <c r="T63">
-        <v>2.855427105843486</v>
+        <v>2.716076238828256</v>
       </c>
       <c r="U63">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V63">
-        <v>0.01683586804525774</v>
+        <v>0.009156227032266245</v>
       </c>
       <c r="W63">
-        <v>0.15578832484894</v>
+        <v>0.2366134929846948</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.05180267090848534</v>
+        <v>0.02817300625312702</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6430,25 +6430,25 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1865398872031266</v>
+        <v>0.2898677334630603</v>
       </c>
       <c r="C64">
-        <v>-2.24896606192733</v>
+        <v>-2.349593704613337</v>
       </c>
       <c r="D64">
-        <v>8.987913938072669</v>
+        <v>11.36728629538666</v>
       </c>
       <c r="E64">
-        <v>10.89388</v>
+        <v>13.37388</v>
       </c>
       <c r="F64">
-        <v>11.26788</v>
+        <v>13.74788</v>
       </c>
       <c r="G64">
         <v>0.031</v>
       </c>
       <c r="H64">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6463,37 +6463,37 @@
         <v>0.091</v>
       </c>
       <c r="M64">
-        <v>1.785463985864448</v>
+        <v>3.282993744</v>
       </c>
       <c r="N64">
-        <v>-1.694463985864448</v>
+        <v>-3.191993744</v>
       </c>
       <c r="O64">
-        <v>-0.5507007954059456</v>
+        <v>-1.0373979668</v>
       </c>
       <c r="P64">
-        <v>-1.143763190458503</v>
+        <v>-2.1545957772</v>
       </c>
       <c r="Q64">
-        <v>-1.087763190458503</v>
+        <v>-2.0985957772</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2366432851101884</v>
+        <v>0.376698691427359</v>
       </c>
       <c r="T64">
-        <v>2.930569924418315</v>
+        <v>2.787551929323736</v>
       </c>
       <c r="U64">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V64">
-        <v>0.01656432178646326</v>
+        <v>0.00900854595110066</v>
       </c>
       <c r="W64">
-        <v>0.1558313530020242</v>
+        <v>0.2366487592268772</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.05096714395834845</v>
+        <v>0.02771860292646366</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6512,25 +6512,25 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1879734479065281</v>
+        <v>0.2918677334630603</v>
       </c>
       <c r="C65">
-        <v>-2.505238735297407</v>
+        <v>-2.661169624347812</v>
       </c>
       <c r="D65">
-        <v>8.913381264702592</v>
+        <v>11.27745037565219</v>
       </c>
       <c r="E65">
-        <v>11.07562</v>
+        <v>13.59562</v>
       </c>
       <c r="F65">
-        <v>11.44962</v>
+        <v>13.96962</v>
       </c>
       <c r="G65">
         <v>0.031</v>
       </c>
       <c r="H65">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6545,37 +6545,37 @@
         <v>0.091</v>
       </c>
       <c r="M65">
-        <v>1.814261792088068</v>
+        <v>3.335945256</v>
       </c>
       <c r="N65">
-        <v>-1.723261792088068</v>
+        <v>-3.244945256</v>
       </c>
       <c r="O65">
-        <v>-0.5600600824286222</v>
+        <v>-1.0546072082</v>
       </c>
       <c r="P65">
-        <v>-1.163201709659446</v>
+        <v>-2.1903380478</v>
       </c>
       <c r="Q65">
-        <v>-1.107201709659446</v>
+        <v>-2.1343380478</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2426309414645178</v>
+        <v>0.3858310884929634</v>
       </c>
       <c r="T65">
-        <v>3.009774516970161</v>
+        <v>2.862891170656811</v>
       </c>
       <c r="U65">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V65">
-        <v>0.01630139604382098</v>
+        <v>0.008865553158226045</v>
       </c>
       <c r="W65">
-        <v>0.1558730151819945</v>
+        <v>0.2366829059058156</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.05015814167329535</v>
+        <v>0.027278625102234</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6594,25 +6594,25 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1894070086099297</v>
+        <v>0.2938677334630603</v>
       </c>
       <c r="C66">
-        <v>-2.760285444060381</v>
+        <v>-2.971336727396388</v>
       </c>
       <c r="D66">
-        <v>8.840074555939617</v>
+        <v>11.18902327260361</v>
       </c>
       <c r="E66">
-        <v>11.25736</v>
+        <v>13.81736</v>
       </c>
       <c r="F66">
-        <v>11.63136</v>
+        <v>14.19136</v>
       </c>
       <c r="G66">
         <v>0.031</v>
       </c>
       <c r="H66">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6627,37 +6627,37 @@
         <v>0.091</v>
       </c>
       <c r="M66">
-        <v>1.843059598311688</v>
+        <v>3.388896768</v>
       </c>
       <c r="N66">
-        <v>-1.752059598311688</v>
+        <v>-3.297896768</v>
       </c>
       <c r="O66">
-        <v>-0.5694193694512987</v>
+        <v>-1.0718164496</v>
       </c>
       <c r="P66">
-        <v>-1.182640228860389</v>
+        <v>-2.2260803184</v>
       </c>
       <c r="Q66">
-        <v>-1.126640228860389</v>
+        <v>-2.1700803184</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2489512453940878</v>
+        <v>0.3954708409511012</v>
       </c>
       <c r="T66">
-        <v>3.093379364663777</v>
+        <v>2.942415925397277</v>
       </c>
       <c r="U66">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V66">
-        <v>0.01604668673063628</v>
+        <v>0.008727028890128764</v>
       </c>
       <c r="W66">
-        <v>0.1559133754188408</v>
+        <v>0.2367159855010373</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.04937442070965004</v>
+        <v>0.0268523965850116</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6676,25 +6676,25 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1908405693133313</v>
+        <v>0.2958677334630603</v>
       </c>
       <c r="C67">
-        <v>-3.014136189735394</v>
+        <v>-3.280127895754795</v>
       </c>
       <c r="D67">
-        <v>8.767963810264606</v>
+        <v>11.1019721042452</v>
       </c>
       <c r="E67">
-        <v>11.4391</v>
+        <v>14.0391</v>
       </c>
       <c r="F67">
-        <v>11.8131</v>
+        <v>14.4131</v>
       </c>
       <c r="G67">
         <v>0.031</v>
       </c>
       <c r="H67">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6709,37 +6709,37 @@
         <v>0.091</v>
       </c>
       <c r="M67">
-        <v>1.871857404535309</v>
+        <v>3.44184828</v>
       </c>
       <c r="N67">
-        <v>-1.780857404535309</v>
+        <v>-3.35084828</v>
       </c>
       <c r="O67">
-        <v>-0.5787786564739753</v>
+        <v>-1.089025691</v>
       </c>
       <c r="P67">
-        <v>-1.202078748061334</v>
+        <v>-2.261822589</v>
       </c>
       <c r="Q67">
-        <v>-1.146078748061333</v>
+        <v>-2.205822589</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2556327095482046</v>
+        <v>0.405661436406847</v>
       </c>
       <c r="T67">
-        <v>3.181761632225599</v>
+        <v>3.0264849518372</v>
       </c>
       <c r="U67">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V67">
-        <v>0.01579981462708803</v>
+        <v>0.008592766907203704</v>
       </c>
       <c r="W67">
-        <v>0.1559524938022457</v>
+        <v>0.2367480472625598</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.04861481423719394</v>
+        <v>0.02643928279139607</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6758,25 +6758,25 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1922741300167329</v>
+        <v>0.2978677334630603</v>
       </c>
       <c r="C68">
-        <v>-3.266820002842055</v>
+        <v>-3.587574996024216</v>
       </c>
       <c r="D68">
-        <v>8.697019997157945</v>
+        <v>11.01626500397578</v>
       </c>
       <c r="E68">
-        <v>11.62084</v>
+        <v>14.26084</v>
       </c>
       <c r="F68">
-        <v>11.99484</v>
+        <v>14.63484</v>
       </c>
       <c r="G68">
         <v>0.031</v>
       </c>
       <c r="H68">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6791,37 +6791,37 @@
         <v>0.091</v>
       </c>
       <c r="M68">
-        <v>1.900655210758929</v>
+        <v>3.494799792</v>
       </c>
       <c r="N68">
-        <v>-1.809655210758929</v>
+        <v>-3.403799792</v>
       </c>
       <c r="O68">
-        <v>-0.5881379434966518</v>
+        <v>-1.1062349324</v>
       </c>
       <c r="P68">
-        <v>-1.221517267262277</v>
+        <v>-2.2975648596</v>
       </c>
       <c r="Q68">
-        <v>-1.165517267262277</v>
+        <v>-2.2415648596</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2627072010055047</v>
+        <v>0.4164514786541072</v>
       </c>
       <c r="T68">
-        <v>3.275342856702822</v>
+        <v>3.115499215126529</v>
       </c>
       <c r="U68">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V68">
-        <v>0.01556042349637457</v>
+        <v>0.00846257346921577</v>
       </c>
       <c r="W68">
-        <v>0.1559904267800928</v>
+        <v>0.2367791374555513</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.04787822614269099</v>
+        <v>0.0260386875975871</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6840,25 +6840,25 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1937076907201344</v>
+        <v>0.2998677334630603</v>
       </c>
       <c r="C69">
-        <v>-3.518364981868176</v>
+        <v>-3.893708918305194</v>
       </c>
       <c r="D69">
-        <v>8.627215018131823</v>
+        <v>10.93187108169481</v>
       </c>
       <c r="E69">
-        <v>11.80258</v>
+        <v>14.48258</v>
       </c>
       <c r="F69">
-        <v>12.17658</v>
+        <v>14.85658</v>
       </c>
       <c r="G69">
         <v>0.031</v>
       </c>
       <c r="H69">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6873,37 +6873,37 @@
         <v>0.091</v>
       </c>
       <c r="M69">
-        <v>1.929453016982549</v>
+        <v>3.547751304000001</v>
       </c>
       <c r="N69">
-        <v>-1.838453016982549</v>
+        <v>-3.456751304</v>
       </c>
       <c r="O69">
-        <v>-0.5974972305193283</v>
+        <v>-1.1234441738</v>
       </c>
       <c r="P69">
-        <v>-1.24095578646322</v>
+        <v>-2.333307130200001</v>
       </c>
       <c r="Q69">
-        <v>-1.18495578646322</v>
+        <v>-2.277307130200001</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2702104495208231</v>
+        <v>0.4278954628557468</v>
       </c>
       <c r="T69">
-        <v>3.374595670542302</v>
+        <v>3.209908282251575</v>
       </c>
       <c r="U69">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V69">
-        <v>0.01532817836956301</v>
+        <v>0.008336266402511058</v>
       </c>
       <c r="W69">
-        <v>0.156027227430243</v>
+        <v>0.2368092995830804</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.04716362575250155</v>
+        <v>0.02565005046926483</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6922,25 +6922,25 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.195141251423536</v>
+        <v>0.3018677334630603</v>
       </c>
       <c r="C70">
-        <v>-3.768798330375825</v>
+        <v>-4.198559613317357</v>
       </c>
       <c r="D70">
-        <v>8.558521669624175</v>
+        <v>10.84876038668264</v>
       </c>
       <c r="E70">
-        <v>11.98432</v>
+        <v>14.70432</v>
       </c>
       <c r="F70">
-        <v>12.35832</v>
+        <v>15.07832</v>
       </c>
       <c r="G70">
         <v>0.031</v>
       </c>
       <c r="H70">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -6955,37 +6955,37 @@
         <v>0.091</v>
       </c>
       <c r="M70">
-        <v>1.958250823206169</v>
+        <v>3.600702816000001</v>
       </c>
       <c r="N70">
-        <v>-1.867250823206169</v>
+        <v>-3.509702816</v>
       </c>
       <c r="O70">
-        <v>-0.606856517542005</v>
+        <v>-1.1406534152</v>
       </c>
       <c r="P70">
-        <v>-1.260394305664164</v>
+        <v>-2.369049400800001</v>
       </c>
       <c r="Q70">
-        <v>-1.204394305664164</v>
+        <v>-2.313049400800001</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2781826510683488</v>
+        <v>0.4400546960699889</v>
       </c>
       <c r="T70">
-        <v>3.480051785246749</v>
+        <v>3.310217916071938</v>
       </c>
       <c r="U70">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V70">
-        <v>0.01510276398177532</v>
+        <v>0.008213674249532954</v>
       </c>
       <c r="W70">
-        <v>0.15606294570833</v>
+        <v>0.2368385745892116</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.04647004302084712</v>
+        <v>0.02527284384471684</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7004,25 +7004,25 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1965748121269376</v>
+        <v>0.3038677334630603</v>
       </c>
       <c r="C71">
-        <v>-4.018146392348644</v>
+        <v>-4.502156127838724</v>
       </c>
       <c r="D71">
-        <v>8.490913607651356</v>
+        <v>10.76690387216128</v>
       </c>
       <c r="E71">
-        <v>12.16606</v>
+        <v>14.92606</v>
       </c>
       <c r="F71">
-        <v>12.54006</v>
+        <v>15.30006</v>
       </c>
       <c r="G71">
         <v>0.031</v>
       </c>
       <c r="H71">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -7037,37 +7037,37 @@
         <v>0.091</v>
       </c>
       <c r="M71">
-        <v>1.987048629429789</v>
+        <v>3.653654328</v>
       </c>
       <c r="N71">
-        <v>-1.896048629429789</v>
+        <v>-3.562654328</v>
       </c>
       <c r="O71">
-        <v>-0.6162158045646815</v>
+        <v>-1.1578626566</v>
       </c>
       <c r="P71">
-        <v>-1.279832824865108</v>
+        <v>-2.4047916714</v>
       </c>
       <c r="Q71">
-        <v>-1.223832824865108</v>
+        <v>-2.3487916714</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2866691881995859</v>
+        <v>0.4529983959432144</v>
       </c>
       <c r="T71">
-        <v>3.592311520254709</v>
+        <v>3.416999139171033</v>
       </c>
       <c r="U71">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V71">
-        <v>0.01488388334435829</v>
+        <v>0.008094635492293346</v>
       </c>
       <c r="W71">
-        <v>0.1560976286740087</v>
+        <v>0.2368670010444404</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.04579656413648703</v>
+        <v>0.02490657074551805</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7086,25 +7086,25 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1980083728303391</v>
+        <v>0.3058677334630603</v>
       </c>
       <c r="C72">
-        <v>-4.266434685876996</v>
+        <v>-4.804526638552595</v>
       </c>
       <c r="D72">
-        <v>8.424365314123003</v>
+        <v>10.68627336144741</v>
       </c>
       <c r="E72">
-        <v>12.3478</v>
+        <v>15.1478</v>
       </c>
       <c r="F72">
-        <v>12.7218</v>
+        <v>15.5218</v>
       </c>
       <c r="G72">
         <v>0.031</v>
       </c>
       <c r="H72">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -7119,37 +7119,37 @@
         <v>0.091</v>
       </c>
       <c r="M72">
-        <v>2.015846435653409</v>
+        <v>3.70660584</v>
       </c>
       <c r="N72">
-        <v>-1.924846435653409</v>
+        <v>-3.61560584</v>
       </c>
       <c r="O72">
-        <v>-0.625575091587358</v>
+        <v>-1.175071898</v>
       </c>
       <c r="P72">
-        <v>-1.299271344066051</v>
+        <v>-2.440533942</v>
       </c>
       <c r="Q72">
-        <v>-1.243271344066051</v>
+        <v>-2.384533942</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2957214944729054</v>
+        <v>0.4668050091413215</v>
       </c>
       <c r="T72">
-        <v>3.712055237596532</v>
+        <v>3.530899110476733</v>
       </c>
       <c r="U72">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V72">
-        <v>0.01467125643943888</v>
+        <v>0.00797899784240344</v>
       </c>
       <c r="W72">
-        <v>0.1561313206978108</v>
+        <v>0.2368946153152341</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.04514232750596581</v>
+        <v>0.02455076259201061</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7168,25 +7168,25 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1994419335337407</v>
+        <v>0.3078677334630603</v>
       </c>
       <c r="C73">
-        <v>-4.513687935271308</v>
+        <v>-5.105698484384934</v>
       </c>
       <c r="D73">
-        <v>8.358852064728691</v>
+        <v>10.60684151561506</v>
       </c>
       <c r="E73">
-        <v>12.52954</v>
+        <v>15.36954</v>
       </c>
       <c r="F73">
-        <v>12.90354</v>
+        <v>15.74354</v>
       </c>
       <c r="G73">
         <v>0.031</v>
       </c>
       <c r="H73">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -7201,37 +7201,37 @@
         <v>0.091</v>
       </c>
       <c r="M73">
-        <v>2.044644241877029</v>
+        <v>3.759557352</v>
       </c>
       <c r="N73">
-        <v>-1.953644241877029</v>
+        <v>-3.668557352</v>
       </c>
       <c r="O73">
-        <v>-0.6349343786100345</v>
+        <v>-1.1922811394</v>
       </c>
       <c r="P73">
-        <v>-1.318709863266995</v>
+        <v>-2.4762762126</v>
       </c>
       <c r="Q73">
-        <v>-1.262709863266995</v>
+        <v>-2.4202762126</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.3053980977305917</v>
+        <v>0.4815638025599877</v>
       </c>
       <c r="T73">
-        <v>3.840057142341239</v>
+        <v>3.652654252217309</v>
       </c>
       <c r="U73">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V73">
-        <v>0.0144646190247989</v>
+        <v>0.007866617591101984</v>
       </c>
       <c r="W73">
-        <v>0.1561640636505199</v>
+        <v>0.2369214517192449</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.04450652007630429</v>
+        <v>0.02420497720339077</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7250,25 +7250,25 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2008754942371423</v>
+        <v>0.3098677334630603</v>
       </c>
       <c r="C74">
-        <v>-4.759930101688619</v>
+        <v>-5.405698197410207</v>
       </c>
       <c r="D74">
-        <v>8.294349898311379</v>
+        <v>10.52858180258979</v>
       </c>
       <c r="E74">
-        <v>12.71128</v>
+        <v>15.59128</v>
       </c>
       <c r="F74">
-        <v>13.08528</v>
+        <v>15.96528</v>
       </c>
       <c r="G74">
         <v>0.031</v>
       </c>
       <c r="H74">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -7283,37 +7283,37 @@
         <v>0.091</v>
       </c>
       <c r="M74">
-        <v>2.073442048100649</v>
+        <v>3.812508864</v>
       </c>
       <c r="N74">
-        <v>-1.982442048100649</v>
+        <v>-3.721508864</v>
       </c>
       <c r="O74">
-        <v>-0.6442936656327111</v>
+        <v>-1.2094903808</v>
       </c>
       <c r="P74">
-        <v>-1.338148382467938</v>
+        <v>-2.5120184832</v>
       </c>
       <c r="Q74">
-        <v>-1.282148382467938</v>
+        <v>-2.4560184832</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.3157658869352557</v>
+        <v>0.4973767955085587</v>
       </c>
       <c r="T74">
-        <v>3.977202040281998</v>
+        <v>3.783106189796499</v>
       </c>
       <c r="U74">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V74">
-        <v>0.01426372153834336</v>
+        <v>0.007757359013447789</v>
       </c>
       <c r="W74">
-        <v>0.1561958970767648</v>
+        <v>0.2369475426675887</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.04388837396413336</v>
+        <v>0.02386879696445476</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7332,25 +7332,25 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2023090549405439</v>
+        <v>0.3118677334630603</v>
       </c>
       <c r="C75">
-        <v>-5.005184412351946</v>
+        <v>-5.704551532399044</v>
       </c>
       <c r="D75">
-        <v>8.230835587648052</v>
+        <v>10.45146846760096</v>
       </c>
       <c r="E75">
-        <v>12.89302</v>
+        <v>15.81302</v>
       </c>
       <c r="F75">
-        <v>13.26702</v>
+        <v>16.18702</v>
       </c>
       <c r="G75">
         <v>0.031</v>
       </c>
       <c r="H75">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -7365,37 +7365,37 @@
         <v>0.091</v>
       </c>
       <c r="M75">
-        <v>2.10223985432427</v>
+        <v>3.865460376</v>
       </c>
       <c r="N75">
-        <v>-2.011239854324269</v>
+        <v>-3.774460376</v>
       </c>
       <c r="O75">
-        <v>-0.6536529526553876</v>
+        <v>-1.2266996222</v>
       </c>
       <c r="P75">
-        <v>-1.357586901668882</v>
+        <v>-2.5477607538</v>
       </c>
       <c r="Q75">
-        <v>-1.301586901668882</v>
+        <v>-2.4917607538</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.3269016605254503</v>
+        <v>0.5143611212681349</v>
       </c>
       <c r="T75">
-        <v>4.124505819551701</v>
+        <v>3.923221233863036</v>
       </c>
       <c r="U75">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V75">
-        <v>0.01406832809261263</v>
+        <v>0.007651093821482752</v>
       </c>
       <c r="W75">
-        <v>0.1562268583543455</v>
+        <v>0.2369729187954299</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.04328716336188509</v>
+        <v>0.02354182714302389</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7414,25 +7414,25 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2037426156439454</v>
+        <v>0.3138677334630603</v>
       </c>
       <c r="C76">
-        <v>-5.249473388437407</v>
+        <v>-6.002283495076883</v>
       </c>
       <c r="D76">
-        <v>8.168286611562593</v>
+        <v>10.37547650492312</v>
       </c>
       <c r="E76">
-        <v>13.07476</v>
+        <v>16.03476</v>
       </c>
       <c r="F76">
-        <v>13.44876</v>
+        <v>16.40876</v>
       </c>
       <c r="G76">
         <v>0.031</v>
       </c>
       <c r="H76">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -7447,37 +7447,37 @@
         <v>0.091</v>
       </c>
       <c r="M76">
-        <v>2.13103766054789</v>
+        <v>3.918411888000001</v>
       </c>
       <c r="N76">
-        <v>-2.04003766054789</v>
+        <v>-3.827411888</v>
       </c>
       <c r="O76">
-        <v>-0.6630122396780641</v>
+        <v>-1.2439088636</v>
       </c>
       <c r="P76">
-        <v>-1.377025420869825</v>
+        <v>-2.583503024400001</v>
       </c>
       <c r="Q76">
-        <v>-1.321025420869825</v>
+        <v>-2.527503024400001</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.3388940320841214</v>
+        <v>0.5326519336246016</v>
       </c>
       <c r="T76">
-        <v>4.283140658765228</v>
+        <v>4.074114358242384</v>
       </c>
       <c r="U76">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V76">
-        <v>0.01387821555082057</v>
+        <v>0.007547700661732984</v>
       </c>
       <c r="W76">
-        <v>0.1562569828406403</v>
+        <v>0.2369976090819782</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.04270220169483263</v>
+        <v>0.0232236943437939</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7496,25 +7496,25 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.205176176347347</v>
+        <v>0.3158677334630602</v>
       </c>
       <c r="C77">
-        <v>-5.492818871699331</v>
+        <v>-6.298918369158679</v>
       </c>
       <c r="D77">
-        <v>8.106681128300668</v>
+        <v>10.30058163084132</v>
       </c>
       <c r="E77">
-        <v>13.2565</v>
+        <v>16.2565</v>
       </c>
       <c r="F77">
-        <v>13.6305</v>
+        <v>16.6305</v>
       </c>
       <c r="G77">
         <v>0.031</v>
       </c>
       <c r="H77">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -7529,37 +7529,37 @@
         <v>0.091</v>
       </c>
       <c r="M77">
-        <v>2.15983546677151</v>
+        <v>3.9713634</v>
       </c>
       <c r="N77">
-        <v>-2.068835466771509</v>
+        <v>-3.880363399999999</v>
       </c>
       <c r="O77">
-        <v>-0.6723715267007406</v>
+        <v>-1.261118105</v>
       </c>
       <c r="P77">
-        <v>-1.396463940070769</v>
+        <v>-2.619245295</v>
       </c>
       <c r="Q77">
-        <v>-1.340463940070769</v>
+        <v>-2.563245295</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.3518457933674864</v>
+        <v>0.5524060109695856</v>
       </c>
       <c r="T77">
-        <v>4.454466285115838</v>
+        <v>4.237078932572079</v>
       </c>
       <c r="U77">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V77">
-        <v>0.01369317267680963</v>
+        <v>0.00744706465290988</v>
       </c>
       <c r="W77">
-        <v>0.1562863040073005</v>
+        <v>0.2370216409608851</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.04213283900556819</v>
+        <v>0.02291404508587658</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7578,25 +7578,25 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2066097370507486</v>
+        <v>0.3178677334630603</v>
       </c>
       <c r="C78">
-        <v>-5.735242049899609</v>
+        <v>-6.594479742221182</v>
       </c>
       <c r="D78">
-        <v>8.045997950100389</v>
+        <v>10.22676025777882</v>
       </c>
       <c r="E78">
-        <v>13.43824</v>
+        <v>16.47824</v>
       </c>
       <c r="F78">
-        <v>13.81224</v>
+        <v>16.85224</v>
       </c>
       <c r="G78">
         <v>0.031</v>
       </c>
       <c r="H78">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -7611,37 +7611,37 @@
         <v>0.091</v>
       </c>
       <c r="M78">
-        <v>2.18863327299513</v>
+        <v>4.024314911999999</v>
       </c>
       <c r="N78">
-        <v>-2.09763327299513</v>
+        <v>-3.933314911999999</v>
       </c>
       <c r="O78">
-        <v>-0.6817308137234172</v>
+        <v>-1.2783273464</v>
       </c>
       <c r="P78">
-        <v>-1.415902459271713</v>
+        <v>-2.6549875656</v>
       </c>
       <c r="Q78">
-        <v>-1.359902459271713</v>
+        <v>-2.5989875656</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3658768680911317</v>
+        <v>0.5738062614266519</v>
       </c>
       <c r="T78">
-        <v>4.640069046995665</v>
+        <v>4.413623888095916</v>
       </c>
       <c r="U78">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V78">
-        <v>0.01351299935211476</v>
+        <v>0.007349076960108434</v>
       </c>
       <c r="W78">
-        <v>0.1563148535643118</v>
+        <v>0.2370450404219261</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.04157845954496864</v>
+        <v>0.02261254449264138</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7660,25 +7660,25 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2080432977541501</v>
+        <v>0.3198677334630602</v>
       </c>
       <c r="C79">
-        <v>-5.976763481103356</v>
+        <v>-6.888990530470503</v>
       </c>
       <c r="D79">
-        <v>7.986216518896644</v>
+        <v>10.1539894695295</v>
       </c>
       <c r="E79">
-        <v>13.61998</v>
+        <v>16.69998</v>
       </c>
       <c r="F79">
-        <v>13.99398</v>
+        <v>17.07398</v>
       </c>
       <c r="G79">
         <v>0.031</v>
       </c>
       <c r="H79">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -7693,37 +7693,37 @@
         <v>0.091</v>
       </c>
       <c r="M79">
-        <v>2.21743107921875</v>
+        <v>4.077266424</v>
       </c>
       <c r="N79">
-        <v>-2.12643107921875</v>
+        <v>-3.986266424</v>
       </c>
       <c r="O79">
-        <v>-0.6910901007460938</v>
+        <v>-1.2955365878</v>
       </c>
       <c r="P79">
-        <v>-1.435340978472656</v>
+        <v>-2.6907298362</v>
       </c>
       <c r="Q79">
-        <v>-1.379340978472656</v>
+        <v>-2.6347298362</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.381128036269007</v>
+        <v>0.5970674032278105</v>
       </c>
       <c r="T79">
-        <v>4.841811179473737</v>
+        <v>4.605520578882695</v>
       </c>
       <c r="U79">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V79">
-        <v>0.01333750585403535</v>
+        <v>0.007253634402184946</v>
       </c>
       <c r="W79">
-        <v>0.1563426615743877</v>
+        <v>0.2370678321047582</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.04103847955087803</v>
+        <v>0.02231887508364605</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7742,25 +7742,25 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2094768584575517</v>
+        <v>0.3218677334630603</v>
       </c>
       <c r="C80">
-        <v>-6.217403116899492</v>
+        <v>-7.182473002459844</v>
       </c>
       <c r="D80">
-        <v>7.927316883100509</v>
+        <v>10.08224699754015</v>
       </c>
       <c r="E80">
-        <v>13.80172</v>
+        <v>16.92172</v>
       </c>
       <c r="F80">
-        <v>14.17572</v>
+        <v>17.29572</v>
       </c>
       <c r="G80">
         <v>0.031</v>
       </c>
       <c r="H80">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -7775,37 +7775,37 @@
         <v>0.091</v>
       </c>
       <c r="M80">
-        <v>2.24622888544237</v>
+        <v>4.130217936</v>
       </c>
       <c r="N80">
-        <v>-2.15522888544237</v>
+        <v>-4.039217936</v>
       </c>
       <c r="O80">
-        <v>-0.7004493877687703</v>
+        <v>-1.3127458292</v>
       </c>
       <c r="P80">
-        <v>-1.4547794976736</v>
+        <v>-2.7264721068</v>
       </c>
       <c r="Q80">
-        <v>-1.3987794976736</v>
+        <v>-2.6704721068</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3977656742812345</v>
+        <v>0.6224431942836202</v>
       </c>
       <c r="T80">
-        <v>5.061893505813452</v>
+        <v>4.814862423377363</v>
       </c>
       <c r="U80">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V80">
-        <v>0.01316651218924002</v>
+        <v>0.007160639089336421</v>
       </c>
       <c r="W80">
-        <v>0.1563697565585642</v>
+        <v>0.2370900393854665</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.04051234519766167</v>
+        <v>0.0220327356594967</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7824,25 +7824,25 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2109104191609533</v>
+        <v>0.3238677334630603</v>
       </c>
       <c r="C81">
-        <v>-6.457180324601312</v>
+        <v>-7.474948801808715</v>
       </c>
       <c r="D81">
-        <v>7.869279675398688</v>
+        <v>10.01151119819128</v>
       </c>
       <c r="E81">
-        <v>13.98346</v>
+        <v>17.14346</v>
       </c>
       <c r="F81">
-        <v>14.35746</v>
+        <v>17.51746</v>
       </c>
       <c r="G81">
         <v>0.031</v>
       </c>
       <c r="H81">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -7857,37 +7857,37 @@
         <v>0.091</v>
       </c>
       <c r="M81">
-        <v>2.27502669166599</v>
+        <v>4.183169448</v>
       </c>
       <c r="N81">
-        <v>-2.18402669166599</v>
+        <v>-4.092169448</v>
       </c>
       <c r="O81">
-        <v>-0.7098086747914468</v>
+        <v>-1.3299550706</v>
       </c>
       <c r="P81">
-        <v>-1.474218016874543</v>
+        <v>-2.7622143774</v>
       </c>
       <c r="Q81">
-        <v>-1.418218016874543</v>
+        <v>-2.7062143774</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.4159878492470077</v>
+        <v>0.650235727344745</v>
       </c>
       <c r="T81">
-        <v>5.302936053709332</v>
+        <v>5.044141586395333</v>
       </c>
       <c r="U81">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V81">
-        <v>0.01299984747798382</v>
+        <v>0.007069998088205581</v>
       </c>
       <c r="W81">
-        <v>0.1563961655937743</v>
+        <v>0.2371116844565365</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.03999953070148876</v>
+        <v>0.02175384027140181</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7906,25 +7906,25 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2123439798643549</v>
+        <v>0.3258677334630602</v>
       </c>
       <c r="C82">
-        <v>-6.696113908478938</v>
+        <v>-7.766438968972516</v>
       </c>
       <c r="D82">
-        <v>7.812086091521063</v>
+        <v>9.941761031027484</v>
       </c>
       <c r="E82">
-        <v>14.1652</v>
+        <v>17.3652</v>
       </c>
       <c r="F82">
-        <v>14.5392</v>
+        <v>17.7392</v>
       </c>
       <c r="G82">
         <v>0.031</v>
       </c>
       <c r="H82">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7939,37 +7939,37 @@
         <v>0.091</v>
       </c>
       <c r="M82">
-        <v>2.303824497889611</v>
+        <v>4.23612096</v>
       </c>
       <c r="N82">
-        <v>-2.21282449788961</v>
+        <v>-4.14512096</v>
       </c>
       <c r="O82">
-        <v>-0.7191679618141233</v>
+        <v>-1.347164312</v>
       </c>
       <c r="P82">
-        <v>-1.493656536075487</v>
+        <v>-2.797956648</v>
       </c>
       <c r="Q82">
-        <v>-1.437656536075487</v>
+        <v>-2.741956648</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.4360322417093581</v>
+        <v>0.6808075137119822</v>
       </c>
       <c r="T82">
-        <v>5.568082856394799</v>
+        <v>5.2963486657151</v>
       </c>
       <c r="U82">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V82">
-        <v>0.01283734938450902</v>
+        <v>0.006981623112103011</v>
       </c>
       <c r="W82">
-        <v>0.1564219144031041</v>
+        <v>0.2371327884008298</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.03949953656772021</v>
+        <v>0.0214819172680093</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -7988,25 +7988,25 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2137775405677564</v>
+        <v>0.3278677334630603</v>
       </c>
       <c r="C83">
-        <v>-6.934222130072534</v>
+        <v>-8.056963962108375</v>
       </c>
       <c r="D83">
-        <v>7.755717869927467</v>
+        <v>9.872976037891625</v>
       </c>
       <c r="E83">
-        <v>14.34694</v>
+        <v>17.58694</v>
       </c>
       <c r="F83">
-        <v>14.72094</v>
+        <v>17.96094</v>
       </c>
       <c r="G83">
         <v>0.031</v>
       </c>
       <c r="H83">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -8021,37 +8021,37 @@
         <v>0.091</v>
       </c>
       <c r="M83">
-        <v>2.332622304113231</v>
+        <v>4.289072472</v>
       </c>
       <c r="N83">
-        <v>-2.241622304113231</v>
+        <v>-4.198072472</v>
       </c>
       <c r="O83">
-        <v>-0.7285272488368</v>
+        <v>-1.3643735534</v>
       </c>
       <c r="P83">
-        <v>-1.513095055276431</v>
+        <v>-2.8336989186</v>
       </c>
       <c r="Q83">
-        <v>-1.457095055276431</v>
+        <v>-2.7776989186</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.458186570220377</v>
+        <v>0.7145973828547181</v>
       </c>
       <c r="T83">
-        <v>5.86113984883663</v>
+        <v>5.575103858647473</v>
       </c>
       <c r="U83">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V83">
-        <v>0.01267886358963854</v>
+        <v>0.006895430234175813</v>
       </c>
       <c r="W83">
-        <v>0.156447027439364</v>
+        <v>0.2371533712600788</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.03901188796811872</v>
+        <v>0.02121670841284873</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8070,25 +8070,25 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.215211101271158</v>
+        <v>0.3298677334630603</v>
       </c>
       <c r="C84">
-        <v>-7.171522727632446</v>
+        <v>-8.346543677080733</v>
       </c>
       <c r="D84">
-        <v>7.700157272367554</v>
+        <v>9.805136322919267</v>
       </c>
       <c r="E84">
-        <v>14.52868</v>
+        <v>17.80868</v>
       </c>
       <c r="F84">
-        <v>14.90268</v>
+        <v>18.18268</v>
       </c>
       <c r="G84">
         <v>0.031</v>
       </c>
       <c r="H84">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -8103,37 +8103,37 @@
         <v>0.091</v>
       </c>
       <c r="M84">
-        <v>2.361420110336851</v>
+        <v>4.342023984000001</v>
       </c>
       <c r="N84">
-        <v>-2.27042011033685</v>
+        <v>-4.251023984000001</v>
       </c>
       <c r="O84">
-        <v>-0.7378865358594764</v>
+        <v>-1.3815827948</v>
       </c>
       <c r="P84">
-        <v>-1.532533574477374</v>
+        <v>-2.869441189200001</v>
       </c>
       <c r="Q84">
-        <v>-1.476533574477374</v>
+        <v>-2.813441189200001</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.4828024907881757</v>
+        <v>0.7521416819022027</v>
       </c>
       <c r="T84">
-        <v>6.186758729327554</v>
+        <v>5.884831850794557</v>
       </c>
       <c r="U84">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V84">
-        <v>0.01252424330196002</v>
+        <v>0.006811339621563912</v>
       </c>
       <c r="W84">
-        <v>0.1564715279625444</v>
+        <v>0.2371734520983706</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.03853613323680016</v>
+        <v>0.02095796806635053</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8152,25 +8152,25 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2166446619745596</v>
+        <v>0.3318677334630603</v>
       </c>
       <c r="C85">
-        <v>-7.408032934729627</v>
+        <v>-8.63519746664778</v>
       </c>
       <c r="D85">
-        <v>7.645387065270375</v>
+        <v>9.738222533352221</v>
       </c>
       <c r="E85">
-        <v>14.71042</v>
+        <v>18.03042</v>
       </c>
       <c r="F85">
-        <v>15.08442</v>
+        <v>18.40442</v>
       </c>
       <c r="G85">
         <v>0.031</v>
       </c>
       <c r="H85">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -8185,37 +8185,37 @@
         <v>0.091</v>
       </c>
       <c r="M85">
-        <v>2.390217916560471</v>
+        <v>4.394975496000001</v>
       </c>
       <c r="N85">
-        <v>-2.299217916560471</v>
+        <v>-4.303975496000001</v>
       </c>
       <c r="O85">
-        <v>-0.7472458228821531</v>
+        <v>-1.3987920362</v>
       </c>
       <c r="P85">
-        <v>-1.551972093678318</v>
+        <v>-2.905183459800001</v>
       </c>
       <c r="Q85">
-        <v>-1.495972093678318</v>
+        <v>-2.849183459800001</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.5103144020110095</v>
+        <v>0.7941029573082146</v>
       </c>
       <c r="T85">
-        <v>6.550685713405646</v>
+        <v>6.23099843025306</v>
       </c>
       <c r="U85">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V85">
-        <v>0.01237334880434604</v>
+        <v>0.006729275288773986</v>
       </c>
       <c r="W85">
-        <v>0.1564954381116722</v>
+        <v>0.2371930490610408</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.03807184247491102</v>
+        <v>0.02070546242699689</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8234,25 +8234,25 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2180782226779611</v>
+        <v>0.3338677334630603</v>
       </c>
       <c r="C86">
-        <v>-7.643769498077484</v>
+        <v>-8.922944158867626</v>
       </c>
       <c r="D86">
-        <v>7.591390501922516</v>
+        <v>9.672215841132372</v>
       </c>
       <c r="E86">
-        <v>14.89216</v>
+        <v>18.25216</v>
       </c>
       <c r="F86">
-        <v>15.26616</v>
+        <v>18.62616</v>
       </c>
       <c r="G86">
         <v>0.031</v>
       </c>
       <c r="H86">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -8267,37 +8267,37 @@
         <v>0.091</v>
       </c>
       <c r="M86">
-        <v>2.419015722784091</v>
+        <v>4.447927008</v>
       </c>
       <c r="N86">
-        <v>-2.328015722784091</v>
+        <v>-4.356927008</v>
       </c>
       <c r="O86">
-        <v>-0.7566051099048294</v>
+        <v>-1.4160012776</v>
       </c>
       <c r="P86">
-        <v>-1.571410612879261</v>
+        <v>-2.9409257304</v>
       </c>
       <c r="Q86">
-        <v>-1.515410612879261</v>
+        <v>-2.8849257304</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.5412653021366974</v>
+        <v>0.8413093921399777</v>
       </c>
       <c r="T86">
-        <v>6.960103570493495</v>
+        <v>6.620435832143873</v>
       </c>
       <c r="U86">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V86">
-        <v>0.01222604703286574</v>
+        <v>0.006649164868669535</v>
       </c>
       <c r="W86">
-        <v>0.1565187789715352</v>
+        <v>0.2372121794293617</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.0376186062549716</v>
+        <v>0.02045896882667553</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8316,25 +8316,25 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2195117833813627</v>
+        <v>0.3358677334630603</v>
       </c>
       <c r="C87">
-        <v>-7.878748694603784</v>
+        <v>-9.209802074760939</v>
       </c>
       <c r="D87">
-        <v>7.538151305396215</v>
+        <v>9.60709792523906</v>
       </c>
       <c r="E87">
-        <v>15.0739</v>
+        <v>18.4739</v>
       </c>
       <c r="F87">
-        <v>15.4479</v>
+        <v>18.8479</v>
       </c>
       <c r="G87">
         <v>0.031</v>
       </c>
       <c r="H87">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -8349,37 +8349,37 @@
         <v>0.091</v>
       </c>
       <c r="M87">
-        <v>2.447813529007711</v>
+        <v>4.50087852</v>
       </c>
       <c r="N87">
-        <v>-2.356813529007711</v>
+        <v>-4.409878519999999</v>
       </c>
       <c r="O87">
-        <v>-0.7659643969275061</v>
+        <v>-1.433210519</v>
       </c>
       <c r="P87">
-        <v>-1.590849132080205</v>
+        <v>-2.976668001</v>
       </c>
       <c r="Q87">
-        <v>-1.534849132080205</v>
+        <v>-2.920668001</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.5763429889458106</v>
+        <v>0.8948100182826428</v>
       </c>
       <c r="T87">
-        <v>7.424110475193062</v>
+        <v>7.061798220953465</v>
       </c>
       <c r="U87">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V87">
-        <v>0.01208221118542026</v>
+        <v>0.006570939399626364</v>
       </c>
       <c r="W87">
-        <v>0.1565415706346954</v>
+        <v>0.2372308596713692</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.03717603441667783</v>
+        <v>0.02021827507577345</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8398,25 +8398,25 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2209453440847643</v>
+        <v>0.3378677334630603</v>
       </c>
       <c r="C88">
-        <v>-8.112986347809201</v>
+        <v>-9.495789045264869</v>
       </c>
       <c r="D88">
-        <v>7.485653652190799</v>
+        <v>9.54285095473513</v>
       </c>
       <c r="E88">
-        <v>15.25564</v>
+        <v>18.69564</v>
       </c>
       <c r="F88">
-        <v>15.62964</v>
+        <v>19.06964</v>
       </c>
       <c r="G88">
         <v>0.031</v>
       </c>
       <c r="H88">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -8431,37 +8431,37 @@
         <v>0.091</v>
       </c>
       <c r="M88">
-        <v>2.476611335231331</v>
+        <v>4.553830032</v>
       </c>
       <c r="N88">
-        <v>-2.385611335231331</v>
+        <v>-4.462830032</v>
       </c>
       <c r="O88">
-        <v>-0.7753236839501826</v>
+        <v>-1.4504197604</v>
       </c>
       <c r="P88">
-        <v>-1.610287651281149</v>
+        <v>-3.0124102716</v>
       </c>
       <c r="Q88">
-        <v>-1.554287651281149</v>
+        <v>-2.9564102716</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.6164317738705114</v>
+        <v>0.9559535910171173</v>
       </c>
       <c r="T88">
-        <v>7.954404080563996</v>
+        <v>7.566212379592998</v>
       </c>
       <c r="U88">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V88">
-        <v>0.01194172035768281</v>
+        <v>0.006494533127537684</v>
       </c>
       <c r="W88">
-        <v>0.1565638322591775</v>
+        <v>0.237249105489144</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.03674375494671644</v>
+        <v>0.01998317885396217</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8480,25 +8480,25 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2223789047881659</v>
+        <v>0.3398677334630603</v>
       </c>
       <c r="C89">
-        <v>-8.346497843447032</v>
+        <v>-9.780922427511234</v>
       </c>
       <c r="D89">
-        <v>7.433882156552968</v>
+        <v>9.479457572488766</v>
       </c>
       <c r="E89">
-        <v>15.43738</v>
+        <v>18.91738</v>
       </c>
       <c r="F89">
-        <v>15.81138</v>
+        <v>19.29138</v>
       </c>
       <c r="G89">
         <v>0.031</v>
       </c>
       <c r="H89">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -8513,37 +8513,37 @@
         <v>0.091</v>
       </c>
       <c r="M89">
-        <v>2.505409141454952</v>
+        <v>4.606781544</v>
       </c>
       <c r="N89">
-        <v>-2.414409141454951</v>
+        <v>-4.515781544</v>
       </c>
       <c r="O89">
-        <v>-0.7846829709728592</v>
+        <v>-1.4676290018</v>
       </c>
       <c r="P89">
-        <v>-1.629726170482092</v>
+        <v>-3.0481525422</v>
       </c>
       <c r="Q89">
-        <v>-1.573726170482092</v>
+        <v>-2.9921525422</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.662688064168243</v>
+        <v>1.026503867249203</v>
       </c>
       <c r="T89">
-        <v>8.566281317530457</v>
+        <v>8.148228716484768</v>
       </c>
       <c r="U89">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V89">
-        <v>0.01180445920414623</v>
+        <v>0.006419883321474033</v>
       </c>
       <c r="W89">
-        <v>0.1565855821221773</v>
+        <v>0.237266931862832</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.03632141293583457</v>
+        <v>0.01975348714299707</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8562,25 +8562,25 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2238124654915674</v>
+        <v>0.3418677334630603</v>
       </c>
       <c r="C90">
-        <v>-8.579298144556759</v>
+        <v>-10.06521912046017</v>
       </c>
       <c r="D90">
-        <v>7.382821855443241</v>
+        <v>9.416900879539835</v>
       </c>
       <c r="E90">
-        <v>15.61912</v>
+        <v>19.13912</v>
       </c>
       <c r="F90">
-        <v>15.99312</v>
+        <v>19.51312</v>
       </c>
       <c r="G90">
         <v>0.031</v>
       </c>
       <c r="H90">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -8595,37 +8595,37 @@
         <v>0.091</v>
       </c>
       <c r="M90">
-        <v>2.534206947678571</v>
+        <v>4.659733056</v>
       </c>
       <c r="N90">
-        <v>-2.443206947678571</v>
+        <v>-4.568733056</v>
       </c>
       <c r="O90">
-        <v>-0.7940422579955356</v>
+        <v>-1.4848382432</v>
       </c>
       <c r="P90">
-        <v>-1.649164689683035</v>
+        <v>-3.083894812800001</v>
       </c>
       <c r="Q90">
-        <v>-1.593164689683035</v>
+        <v>-3.027894812800001</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.7166537361822635</v>
+        <v>1.108812522853304</v>
       </c>
       <c r="T90">
-        <v>9.280138093991331</v>
+        <v>8.827247776191832</v>
       </c>
       <c r="U90">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V90">
-        <v>0.01167031762228093</v>
+        <v>0.006346930101911828</v>
       </c>
       <c r="W90">
-        <v>0.1566068376701089</v>
+        <v>0.2372843530916635</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.03590866960701833</v>
+        <v>0.01952901569819032</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8644,25 +8644,25 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.225246026194969</v>
+        <v>0.3438677334630603</v>
       </c>
       <c r="C91">
-        <v>-8.81140180588223</v>
+        <v>-10.3486955799188</v>
       </c>
       <c r="D91">
-        <v>7.332458194117768</v>
+        <v>9.355164420081202</v>
       </c>
       <c r="E91">
-        <v>15.80086</v>
+        <v>19.36086</v>
       </c>
       <c r="F91">
-        <v>16.17486</v>
+        <v>19.73486</v>
       </c>
       <c r="G91">
         <v>0.031</v>
       </c>
       <c r="H91">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -8677,37 +8677,37 @@
         <v>0.091</v>
       </c>
       <c r="M91">
-        <v>2.563004753902192</v>
+        <v>4.712684568</v>
       </c>
       <c r="N91">
-        <v>-2.472004753902191</v>
+        <v>-4.621684568</v>
       </c>
       <c r="O91">
-        <v>-0.8034015450182123</v>
+        <v>-1.5020474846</v>
       </c>
       <c r="P91">
-        <v>-1.668603208883979</v>
+        <v>-3.1196370834</v>
       </c>
       <c r="Q91">
-        <v>-1.612603208883979</v>
+        <v>-3.0636370834</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.7804313485624691</v>
+        <v>1.20608638856724</v>
       </c>
       <c r="T91">
-        <v>10.1237870116269</v>
+        <v>9.629724846754726</v>
       </c>
       <c r="U91">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V91">
-        <v>0.01153919045798564</v>
+        <v>0.006275616280542032</v>
       </c>
       <c r="W91">
-        <v>0.1566276155652779</v>
+        <v>0.2373013828322066</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.03550520140918667</v>
+        <v>0.01930958855551401</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8726,25 +8726,25 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2266795868983705</v>
+        <v>0.3458677334630603</v>
       </c>
       <c r="C92">
-        <v>-9.042822987703762</v>
+        <v>-10.63136783297304</v>
       </c>
       <c r="D92">
-        <v>7.282777012296239</v>
+        <v>9.294232167026962</v>
       </c>
       <c r="E92">
-        <v>15.9826</v>
+        <v>19.5826</v>
       </c>
       <c r="F92">
-        <v>16.3566</v>
+        <v>19.9566</v>
       </c>
       <c r="G92">
         <v>0.031</v>
       </c>
       <c r="H92">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -8759,37 +8759,37 @@
         <v>0.091</v>
       </c>
       <c r="M92">
-        <v>2.591802560125812</v>
+        <v>4.765636080000001</v>
       </c>
       <c r="N92">
-        <v>-2.500802560125812</v>
+        <v>-4.674636080000001</v>
       </c>
       <c r="O92">
-        <v>-0.8127608320408888</v>
+        <v>-1.519256726</v>
       </c>
       <c r="P92">
-        <v>-1.688041728084923</v>
+        <v>-3.155379354000001</v>
       </c>
       <c r="Q92">
-        <v>-1.632041728084923</v>
+        <v>-3.099379354000001</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.8569644834187162</v>
+        <v>1.322815027423965</v>
       </c>
       <c r="T92">
-        <v>11.1361657127896</v>
+        <v>10.5926973314302</v>
       </c>
       <c r="U92">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V92">
-        <v>0.01141097723067469</v>
+        <v>0.006205887210758231</v>
       </c>
       <c r="W92">
-        <v>0.1566479317294433</v>
+        <v>0.237318034134071</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.03511069917130683</v>
+        <v>0.01909503757156383</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8808,25 +8808,25 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2281131476017721</v>
+        <v>0.3478677334630603</v>
       </c>
       <c r="C93">
-        <v>-9.273575469111634</v>
+        <v>-10.91325149185898</v>
       </c>
       <c r="D93">
-        <v>7.233764530888367</v>
+        <v>9.234088508141021</v>
       </c>
       <c r="E93">
-        <v>16.16434</v>
+        <v>19.80434</v>
       </c>
       <c r="F93">
-        <v>16.53834</v>
+        <v>20.17834</v>
       </c>
       <c r="G93">
         <v>0.031</v>
       </c>
       <c r="H93">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -8841,37 +8841,37 @@
         <v>0.091</v>
       </c>
       <c r="M93">
-        <v>2.620600366349432</v>
+        <v>4.818587592</v>
       </c>
       <c r="N93">
-        <v>-2.529600366349432</v>
+        <v>-4.727587592</v>
       </c>
       <c r="O93">
-        <v>-0.8221201190635654</v>
+        <v>-1.5364659674</v>
       </c>
       <c r="P93">
-        <v>-1.707480247285867</v>
+        <v>-3.1911216246</v>
       </c>
       <c r="Q93">
-        <v>-1.651480247285867</v>
+        <v>-3.1351216246</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.9505049815763513</v>
+        <v>1.465483363804405</v>
       </c>
       <c r="T93">
-        <v>12.37351745865511</v>
+        <v>11.76966370158911</v>
       </c>
       <c r="U93">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V93">
-        <v>0.01128558187649145</v>
+        <v>0.006137690648002648</v>
       </c>
       <c r="W93">
-        <v>0.1566678013845061</v>
+        <v>0.237334319473257</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.03472486731228142</v>
+        <v>0.01888520199385435</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8890,25 +8890,25 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2295467083051737</v>
+        <v>0.3498677334630603</v>
       </c>
       <c r="C94">
-        <v>-9.503672660747256</v>
+        <v>-11.19436176729925</v>
       </c>
       <c r="D94">
-        <v>7.185407339252744</v>
+        <v>9.17471823270075</v>
       </c>
       <c r="E94">
-        <v>16.34608</v>
+        <v>20.02608</v>
       </c>
       <c r="F94">
-        <v>16.72008</v>
+        <v>20.40008</v>
       </c>
       <c r="G94">
         <v>0.031</v>
       </c>
       <c r="H94">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -8923,37 +8923,37 @@
         <v>0.091</v>
       </c>
       <c r="M94">
-        <v>2.649398172573052</v>
+        <v>4.871539104</v>
       </c>
       <c r="N94">
-        <v>-2.558398172573052</v>
+        <v>-4.780539104</v>
       </c>
       <c r="O94">
-        <v>-0.8314794060862418</v>
+        <v>-1.5536752088</v>
       </c>
       <c r="P94">
-        <v>-1.72691876648681</v>
+        <v>-3.2268638952</v>
       </c>
       <c r="Q94">
-        <v>-1.67091876648681</v>
+        <v>-3.1708638952</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>1.067430604273395</v>
+        <v>1.643818784279956</v>
       </c>
       <c r="T94">
-        <v>13.920207140987</v>
+        <v>13.24087166428776</v>
       </c>
       <c r="U94">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V94">
-        <v>0.01116291250826872</v>
+        <v>0.00607097661922001</v>
       </c>
       <c r="W94">
-        <v>0.1566872390905457</v>
+        <v>0.2373502507833303</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.03434742310236538</v>
+        <v>0.01867992805913854</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8972,25 +8972,25 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2309802690085752</v>
+        <v>0.3518677334630603</v>
       </c>
       <c r="C95">
-        <v>-9.733127617036644</v>
+        <v>-11.47471348132811</v>
       </c>
       <c r="D95">
-        <v>7.137692382963357</v>
+        <v>9.116106518671888</v>
       </c>
       <c r="E95">
-        <v>16.52782</v>
+        <v>20.24782</v>
       </c>
       <c r="F95">
-        <v>16.90182</v>
+        <v>20.62182</v>
       </c>
       <c r="G95">
         <v>0.031</v>
       </c>
       <c r="H95">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -9005,37 +9005,37 @@
         <v>0.091</v>
       </c>
       <c r="M95">
-        <v>2.678195978796672</v>
+        <v>4.924490616</v>
       </c>
       <c r="N95">
-        <v>-2.587195978796672</v>
+        <v>-4.833490616</v>
       </c>
       <c r="O95">
-        <v>-0.8408386931089185</v>
+        <v>-1.5708844502</v>
       </c>
       <c r="P95">
-        <v>-1.746357285687754</v>
+        <v>-3.2626061658</v>
       </c>
       <c r="Q95">
-        <v>-1.690357285687754</v>
+        <v>-3.2066061658</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>1.217763547741024</v>
+        <v>1.873107182034236</v>
       </c>
       <c r="T95">
-        <v>15.908808161128</v>
+        <v>15.13242475918601</v>
       </c>
       <c r="U95">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V95">
-        <v>0.0110428811909755</v>
+        <v>0.006005697300733774</v>
       </c>
       <c r="W95">
-        <v>0.1567062587814018</v>
+        <v>0.2373658394845848</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.03397809597223234</v>
+        <v>0.01847906861764237</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9054,25 +9054,25 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2324138297119768</v>
+        <v>0.3538677334630603</v>
       </c>
       <c r="C96">
-        <v>-9.961953047939719</v>
+        <v>-11.75432107962815</v>
       </c>
       <c r="D96">
-        <v>7.090606952060283</v>
+        <v>9.058238920371847</v>
       </c>
       <c r="E96">
-        <v>16.70956</v>
+        <v>20.46956</v>
       </c>
       <c r="F96">
-        <v>17.08356</v>
+        <v>20.84356</v>
       </c>
       <c r="G96">
         <v>0.031</v>
       </c>
       <c r="H96">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -9087,37 +9087,37 @@
         <v>0.091</v>
       </c>
       <c r="M96">
-        <v>2.706993785020293</v>
+        <v>4.977442128</v>
       </c>
       <c r="N96">
-        <v>-2.615993785020292</v>
+        <v>-4.886442128</v>
       </c>
       <c r="O96">
-        <v>-0.8501979801315951</v>
+        <v>-1.5880936916</v>
       </c>
       <c r="P96">
-        <v>-1.765795804888697</v>
+        <v>-3.2983484364</v>
       </c>
       <c r="Q96">
-        <v>-1.709795804888697</v>
+        <v>-3.2423484364</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.418207472364528</v>
+        <v>2.178825045706609</v>
       </c>
       <c r="T96">
-        <v>18.56027618798267</v>
+        <v>17.65449555238368</v>
       </c>
       <c r="U96">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V96">
-        <v>0.01092540373149704</v>
+        <v>0.005941806903917457</v>
       </c>
       <c r="W96">
-        <v>0.1567248737979843</v>
+        <v>0.2373810965113445</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.03361662686614486</v>
+        <v>0.01828248278128453</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9136,25 +9136,25 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2338473904153784</v>
+        <v>0.3558677334630603</v>
       </c>
       <c r="C97">
-        <v>-10.19016133023757</v>
+        <v>-12.03319864340001</v>
       </c>
       <c r="D97">
-        <v>7.044138669762433</v>
+        <v>9.001101356599991</v>
       </c>
       <c r="E97">
-        <v>16.8913</v>
+        <v>20.6913</v>
       </c>
       <c r="F97">
-        <v>17.2653</v>
+        <v>21.0653</v>
       </c>
       <c r="G97">
         <v>0.031</v>
       </c>
       <c r="H97">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -9169,37 +9169,37 @@
         <v>0.091</v>
       </c>
       <c r="M97">
-        <v>2.735791591243912</v>
+        <v>5.030393640000001</v>
       </c>
       <c r="N97">
-        <v>-2.644791591243912</v>
+        <v>-4.93939364</v>
       </c>
       <c r="O97">
-        <v>-0.8595572671542715</v>
+        <v>-1.605302933</v>
       </c>
       <c r="P97">
-        <v>-1.785234324089641</v>
+        <v>-3.334090707000001</v>
       </c>
       <c r="Q97">
-        <v>-1.729234324089641</v>
+        <v>-3.278090707</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.698828966837434</v>
+        <v>2.606830054847933</v>
       </c>
       <c r="T97">
-        <v>22.27233142557922</v>
+        <v>21.18539466286043</v>
       </c>
       <c r="U97">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V97">
-        <v>0.01081039948169181</v>
+        <v>0.005879261568086745</v>
       </c>
       <c r="W97">
-        <v>0.1567430969194808</v>
+        <v>0.2373960323375409</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.03326276763597491</v>
+        <v>0.01809003559411315</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9218,25 +9218,25 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2352809511187799</v>
+        <v>0.3578677334630603</v>
       </c>
       <c r="C98">
-        <v>-10.41776451837883</v>
+        <v>-12.31135990078573</v>
       </c>
       <c r="D98">
-        <v>6.998275481621172</v>
+        <v>8.944680099214265</v>
       </c>
       <c r="E98">
-        <v>17.07304</v>
+        <v>20.91304</v>
       </c>
       <c r="F98">
-        <v>17.44704</v>
+        <v>21.28704</v>
       </c>
       <c r="G98">
         <v>0.031</v>
       </c>
       <c r="H98">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -9251,37 +9251,37 @@
         <v>0.091</v>
       </c>
       <c r="M98">
-        <v>2.764589397467532</v>
+        <v>5.083345152</v>
       </c>
       <c r="N98">
-        <v>-2.673589397467532</v>
+        <v>-4.992345152</v>
       </c>
       <c r="O98">
-        <v>-0.8689165541769479</v>
+        <v>-1.6225121744</v>
       </c>
       <c r="P98">
-        <v>-1.804672843290584</v>
+        <v>-3.3698329776</v>
       </c>
       <c r="Q98">
-        <v>-1.748672843290584</v>
+        <v>-3.3138329776</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>2.119761208546788</v>
+        <v>3.248837568559908</v>
       </c>
       <c r="T98">
-        <v>27.84041428197396</v>
+        <v>26.48174332857548</v>
       </c>
       <c r="U98">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V98">
-        <v>0.01069779115375752</v>
+        <v>0.005818019260085843</v>
       </c>
       <c r="W98">
-        <v>0.1567609403926129</v>
+        <v>0.2374106570006915</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.03291628047310013</v>
+        <v>0.0179015977233411</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9300,25 +9300,25 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2367145118221815</v>
+        <v>0.3598677334630603</v>
       </c>
       <c r="C99">
-        <v>-10.64477435490506</v>
+        <v>-12.58881823786518</v>
       </c>
       <c r="D99">
-        <v>6.95300564509494</v>
+        <v>8.888961762134816</v>
       </c>
       <c r="E99">
-        <v>17.25478</v>
+        <v>21.13478</v>
       </c>
       <c r="F99">
-        <v>17.62878</v>
+        <v>21.50878</v>
       </c>
       <c r="G99">
         <v>0.031</v>
       </c>
       <c r="H99">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -9333,37 +9333,37 @@
         <v>0.091</v>
       </c>
       <c r="M99">
-        <v>2.793387203691152</v>
+        <v>5.136296664</v>
       </c>
       <c r="N99">
-        <v>-2.702387203691152</v>
+        <v>-5.045296663999999</v>
       </c>
       <c r="O99">
-        <v>-0.8782758411996245</v>
+        <v>-1.6397214158</v>
       </c>
       <c r="P99">
-        <v>-1.824111362491528</v>
+        <v>-3.4055752482</v>
       </c>
       <c r="Q99">
-        <v>-1.768111362491528</v>
+        <v>-3.3495752482</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.821314944729051</v>
+        <v>4.318850091413212</v>
       </c>
       <c r="T99">
-        <v>37.12055237596529</v>
+        <v>35.3089911047673</v>
       </c>
       <c r="U99">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V99">
-        <v>0.01058750464701775</v>
+        <v>0.005758039680084958</v>
       </c>
       <c r="W99">
-        <v>0.1567784159590824</v>
+        <v>0.2374249801243957</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.03257693737543932</v>
+        <v>0.01771704516949224</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9382,25 +9382,25 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2381480725255831</v>
+        <v>0.3618677334630603</v>
       </c>
       <c r="C100">
-        <v>-10.87120228047408</v>
+        <v>-12.86558670924393</v>
       </c>
       <c r="D100">
-        <v>6.908317719525917</v>
+        <v>8.83393329075607</v>
       </c>
       <c r="E100">
-        <v>17.43652</v>
+        <v>21.35652</v>
       </c>
       <c r="F100">
-        <v>17.81052</v>
+        <v>21.73052</v>
       </c>
       <c r="G100">
         <v>0.031</v>
       </c>
       <c r="H100">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -9415,37 +9415,37 @@
         <v>0.091</v>
       </c>
       <c r="M100">
-        <v>2.822185009914773</v>
+        <v>5.189248176</v>
       </c>
       <c r="N100">
-        <v>-2.731185009914773</v>
+        <v>-5.098248175999999</v>
       </c>
       <c r="O100">
-        <v>-0.8876351282223011</v>
+        <v>-1.6569306572</v>
       </c>
       <c r="P100">
-        <v>-1.843549881692471</v>
+        <v>-3.4413175188</v>
       </c>
       <c r="Q100">
-        <v>-1.787549881692471</v>
+        <v>-3.3853175188</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>4.224422417093576</v>
+        <v>6.458875137119816</v>
       </c>
       <c r="T100">
-        <v>55.68082856394792</v>
+        <v>52.96348665715094</v>
       </c>
       <c r="U100">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V100">
-        <v>0.01047946888531349</v>
+        <v>0.005699284173145316</v>
       </c>
       <c r="W100">
-        <v>0.1567955348813383</v>
+        <v>0.2374390109394529</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0322445196471185</v>
+        <v>0.01753625899429334</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9464,25 +9464,25 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2395816332289847</v>
+        <v>0.3638677334630603</v>
       </c>
       <c r="C101">
-        <v>-11.09705944349928</v>
+        <v>-13.14167804825039</v>
       </c>
       <c r="D101">
-        <v>6.864200556500723</v>
+        <v>8.779581951749609</v>
       </c>
       <c r="E101">
-        <v>17.61826</v>
+        <v>21.57826</v>
       </c>
       <c r="F101">
-        <v>17.99226</v>
+        <v>21.95226</v>
       </c>
       <c r="G101">
         <v>0.031</v>
       </c>
       <c r="H101">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -9497,37 +9497,37 @@
         <v>0.091</v>
       </c>
       <c r="M101">
-        <v>2.850982816138393</v>
+        <v>5.242199688</v>
       </c>
       <c r="N101">
-        <v>-2.759982816138392</v>
+        <v>-5.151199688</v>
       </c>
       <c r="O101">
-        <v>-0.8969944152449776</v>
+        <v>-1.6741398986</v>
       </c>
       <c r="P101">
-        <v>-1.862988400893415</v>
+        <v>-3.4770597894</v>
       </c>
       <c r="Q101">
-        <v>-1.806988400893415</v>
+        <v>-3.4210597894</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>8.433744834187152</v>
+        <v>12.87895027423963</v>
       </c>
       <c r="T101">
-        <v>111.3616571278958</v>
+        <v>105.9269733143019</v>
       </c>
       <c r="U101">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V101">
-        <v>0.01037361566424972</v>
+        <v>0.005641715646143847</v>
       </c>
       <c r="W101">
-        <v>0.1568123079667809</v>
+        <v>0.2374527583037009</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.0319188174284607</v>
+        <v>0.01735912506505799</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_machinery.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_machinery.xlsx
@@ -1133,13 +1133,13 @@
         <v>5.20833333333333</v>
       </c>
       <c r="F2">
-        <v>2.10193080870782</v>
+        <v>2.10193080870781</v>
       </c>
       <c r="G2">
         <v>2.59756097560976</v>
       </c>
       <c r="H2">
-        <v>4.91195121951219</v>
+        <v>4.9119512195122</v>
       </c>
       <c r="I2">
         <v>0.0317294801132132</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.166293957332215</v>
+        <v>0.1658265754602183</v>
       </c>
       <c r="C2">
-        <v>13.41415657628944</v>
+        <v>13.33206492397452</v>
       </c>
       <c r="D2">
-        <v>13.39715657628944</v>
+        <v>13.44932492397452</v>
       </c>
       <c r="E2">
-        <v>-0.426</v>
+        <v>-0.29174</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.13426</v>
       </c>
       <c r="G2">
         <v>0.017</v>
@@ -1451,28 +1451,28 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006753278000000001</v>
       </c>
       <c r="N2">
-        <v>0.1283469387755102</v>
+        <v>0.1215936607755102</v>
       </c>
       <c r="O2">
-        <v>0.03850408163265306</v>
+        <v>0.03647809823265306</v>
       </c>
       <c r="P2">
-        <v>0.08984285714285714</v>
+        <v>0.08511556254285715</v>
       </c>
       <c r="Q2">
-        <v>0.1288428571428571</v>
+        <v>0.1241155625428572</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.166293957332215</v>
+        <v>0.1671459348083014</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.039423033698481</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>19.00513184493667</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1658265754602183</v>
+        <v>0.1654039935882217</v>
       </c>
       <c r="C3">
-        <v>13.33206492397452</v>
+        <v>13.24532374615559</v>
       </c>
       <c r="D3">
-        <v>13.44932492397452</v>
+        <v>13.49684374615559</v>
       </c>
       <c r="E3">
-        <v>-0.29174</v>
+        <v>-0.15748</v>
       </c>
       <c r="F3">
-        <v>0.13426</v>
+        <v>0.26852</v>
       </c>
       <c r="G3">
         <v>0.017</v>
@@ -1533,45 +1533,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M3">
-        <v>0.006753278000000001</v>
+        <v>0.01436582</v>
       </c>
       <c r="N3">
-        <v>0.1215936607755102</v>
+        <v>0.1139811187755102</v>
       </c>
       <c r="O3">
-        <v>0.03647809823265306</v>
+        <v>0.03419433563265306</v>
       </c>
       <c r="P3">
-        <v>0.08511556254285715</v>
+        <v>0.07978678314285714</v>
       </c>
       <c r="Q3">
-        <v>0.1241155625428572</v>
+        <v>0.1187867831428571</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1671459348083014</v>
+        <v>0.1680152995798181</v>
       </c>
       <c r="T3">
-        <v>1.039423033698481</v>
+        <v>1.046869824311022</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.03521</v>
+        <v>0.03745</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>19.00513184493667</v>
+        <v>8.934188147666489</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1654039935882217</v>
+        <v>0.164996811716225</v>
       </c>
       <c r="C4">
-        <v>13.24532374615559</v>
+        <v>13.15716959431946</v>
       </c>
       <c r="D4">
-        <v>13.49684374615559</v>
+        <v>13.54294959431946</v>
       </c>
       <c r="E4">
-        <v>-0.15748</v>
+        <v>-0.02322000000000002</v>
       </c>
       <c r="F4">
-        <v>0.26852</v>
+        <v>0.40278</v>
       </c>
       <c r="G4">
         <v>0.017</v>
@@ -1615,45 +1615,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M4">
-        <v>0.01436582</v>
+        <v>0.022273734</v>
       </c>
       <c r="N4">
-        <v>0.1139811187755102</v>
+        <v>0.1060732047755102</v>
       </c>
       <c r="O4">
-        <v>0.03419433563265306</v>
+        <v>0.03182196143265306</v>
       </c>
       <c r="P4">
-        <v>0.07978678314285714</v>
+        <v>0.07425124334285714</v>
       </c>
       <c r="Q4">
-        <v>0.1187867831428571</v>
+        <v>0.1132512433428571</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1680152995798181</v>
+        <v>0.1689025893981702</v>
       </c>
       <c r="T4">
-        <v>1.046869824311022</v>
+        <v>1.054470156998049</v>
       </c>
       <c r="U4">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.03745</v>
+        <v>0.03871</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>8.934188147666489</v>
+        <v>5.762255164558857</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.164996811716225</v>
+        <v>0.1646344298442284</v>
       </c>
       <c r="C5">
-        <v>13.15716959431946</v>
+        <v>13.06420839495139</v>
       </c>
       <c r="D5">
-        <v>13.54294959431946</v>
+        <v>13.58424839495139</v>
       </c>
       <c r="E5">
-        <v>-0.02322000000000002</v>
+        <v>0.1110400000000001</v>
       </c>
       <c r="F5">
-        <v>0.40278</v>
+        <v>0.5370400000000001</v>
       </c>
       <c r="G5">
         <v>0.017</v>
@@ -1697,45 +1697,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M5">
-        <v>0.022273734</v>
+        <v>0.03104091200000001</v>
       </c>
       <c r="N5">
-        <v>0.1060732047755102</v>
+        <v>0.0973060267755102</v>
       </c>
       <c r="O5">
-        <v>0.03182196143265306</v>
+        <v>0.02919180803265306</v>
       </c>
       <c r="P5">
-        <v>0.07425124334285714</v>
+        <v>0.06811421874285714</v>
       </c>
       <c r="Q5">
-        <v>0.1132512433428571</v>
+        <v>0.1071142187428571</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1689025893981702</v>
+        <v>0.1698083644210713</v>
       </c>
       <c r="T5">
-        <v>1.054470156998049</v>
+        <v>1.062228829949388</v>
       </c>
       <c r="U5">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.762255164558857</v>
+        <v>4.134767006056722</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1646344298442284</v>
+        <v>0.1647130479722318</v>
       </c>
       <c r="C6">
-        <v>13.06420839495139</v>
+        <v>12.92096731005486</v>
       </c>
       <c r="D6">
-        <v>13.58424839495139</v>
+        <v>13.57526731005486</v>
       </c>
       <c r="E6">
-        <v>0.1110400000000001</v>
+        <v>0.2453</v>
       </c>
       <c r="F6">
-        <v>0.5370400000000001</v>
+        <v>0.6713</v>
       </c>
       <c r="G6">
         <v>0.017</v>
@@ -1779,45 +1779,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M6">
-        <v>0.03104091200000001</v>
+        <v>0.04826647000000001</v>
       </c>
       <c r="N6">
-        <v>0.0973060267755102</v>
+        <v>0.0800804687755102</v>
       </c>
       <c r="O6">
-        <v>0.02919180803265306</v>
+        <v>0.02402414063265306</v>
       </c>
       <c r="P6">
-        <v>0.06811421874285714</v>
+        <v>0.05605632814285715</v>
       </c>
       <c r="Q6">
-        <v>0.1071142187428571</v>
+        <v>0.09505632814285715</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1698083644210713</v>
+        <v>0.1707332083918229</v>
       </c>
       <c r="T6">
-        <v>1.062228829949388</v>
+        <v>1.070150843383914</v>
       </c>
       <c r="U6">
-        <v>0.0578</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.04046</v>
+        <v>0.05033</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.134767006056722</v>
+        <v>2.659132494576674</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1647130479722318</v>
+        <v>0.1645606661002351</v>
       </c>
       <c r="C7">
-        <v>12.92096731005486</v>
+        <v>12.80412574255013</v>
       </c>
       <c r="D7">
-        <v>13.57526731005486</v>
+        <v>13.59268574255013</v>
       </c>
       <c r="E7">
-        <v>0.2453</v>
+        <v>0.3795600000000001</v>
       </c>
       <c r="F7">
-        <v>0.6713</v>
+        <v>0.8055600000000001</v>
       </c>
       <c r="G7">
         <v>0.017</v>
@@ -1861,45 +1861,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M7">
-        <v>0.04826647000000001</v>
+        <v>0.06106144800000001</v>
       </c>
       <c r="N7">
-        <v>0.0800804687755102</v>
+        <v>0.06728549077551019</v>
       </c>
       <c r="O7">
-        <v>0.02402414063265306</v>
+        <v>0.02018564723265305</v>
       </c>
       <c r="P7">
-        <v>0.05605632814285715</v>
+        <v>0.04709984354285714</v>
       </c>
       <c r="Q7">
-        <v>0.09505632814285715</v>
+        <v>0.08609984354285714</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1707332083918229</v>
+        <v>0.1716777298938671</v>
       </c>
       <c r="T7">
-        <v>1.070150843383914</v>
+        <v>1.07824141029577</v>
       </c>
       <c r="U7">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y7">
-        <v>2.659132494576674</v>
+        <v>2.101930808707815</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1645606661002351</v>
+        <v>0.1649675842282385</v>
       </c>
       <c r="C8">
-        <v>12.80412574255013</v>
+        <v>12.62345118885487</v>
       </c>
       <c r="D8">
-        <v>13.59268574255013</v>
+        <v>13.54627118885487</v>
       </c>
       <c r="E8">
-        <v>0.37956</v>
+        <v>0.5138199999999999</v>
       </c>
       <c r="F8">
-        <v>0.8055599999999999</v>
+        <v>0.9398199999999999</v>
       </c>
       <c r="G8">
         <v>0.017</v>
@@ -1943,45 +1943,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M8">
-        <v>0.061061448</v>
+        <v>0.08458379999999999</v>
       </c>
       <c r="N8">
-        <v>0.06728549077551021</v>
+        <v>0.04376313877551022</v>
       </c>
       <c r="O8">
-        <v>0.02018564723265306</v>
+        <v>0.01312894163265307</v>
       </c>
       <c r="P8">
-        <v>0.04709984354285715</v>
+        <v>0.03063419714285715</v>
       </c>
       <c r="Q8">
-        <v>0.08609984354285716</v>
+        <v>0.06963419714285715</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1716777298938671</v>
+        <v>0.1726425636862779</v>
       </c>
       <c r="T8">
-        <v>1.07824141029577</v>
+        <v>1.086505967893902</v>
       </c>
       <c r="U8">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.101930808707816</v>
+        <v>1.517393860000499</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1649675842282385</v>
+        <v>0.1691521215265035</v>
       </c>
       <c r="C9">
-        <v>12.62345118885487</v>
+        <v>12.0296540820691</v>
       </c>
       <c r="D9">
-        <v>13.54627118885487</v>
+        <v>13.08673408206911</v>
       </c>
       <c r="E9">
-        <v>0.5138200000000002</v>
+        <v>0.6480800000000002</v>
       </c>
       <c r="F9">
-        <v>0.9398200000000001</v>
+        <v>1.07408</v>
       </c>
       <c r="G9">
         <v>0.017</v>
@@ -2025,45 +2025,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M9">
-        <v>0.0845838</v>
+        <v>0.157674944</v>
       </c>
       <c r="N9">
-        <v>0.0437631387755102</v>
+        <v>-0.02932800522448983</v>
       </c>
       <c r="O9">
-        <v>0.01312894163265306</v>
+        <v>-0.00879840156734695</v>
       </c>
       <c r="P9">
-        <v>0.03063419714285714</v>
+        <v>-0.02052960365714288</v>
       </c>
       <c r="Q9">
-        <v>0.06963419714285715</v>
+        <v>0.01847039634285712</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1726425636862779</v>
+        <v>0.1742130390455483</v>
       </c>
       <c r="T9">
-        <v>1.086505967893902</v>
+        <v>1.099958320169735</v>
       </c>
       <c r="U9">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V9">
-        <v>0.3</v>
+        <v>0.2441991140498078</v>
       </c>
       <c r="W9">
-        <v>0.063</v>
+        <v>0.1109515700574882</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y9">
-        <v>1.517393860000499</v>
+        <v>0.8139970468326925</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1691521215265035</v>
+        <v>0.1756551589575631</v>
       </c>
       <c r="C10">
-        <v>12.0296540820691</v>
+        <v>11.24002141709989</v>
       </c>
       <c r="D10">
-        <v>13.08673408206911</v>
+        <v>12.43136141709989</v>
       </c>
       <c r="E10">
-        <v>0.6480800000000002</v>
+        <v>0.78234</v>
       </c>
       <c r="F10">
-        <v>1.07408</v>
+        <v>1.20834</v>
       </c>
       <c r="G10">
         <v>0.017</v>
@@ -2107,45 +2107,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M10">
-        <v>0.157674944</v>
+        <v>0.242634672</v>
       </c>
       <c r="N10">
-        <v>-0.02932800522448983</v>
+        <v>-0.1142877332244898</v>
       </c>
       <c r="O10">
-        <v>-0.00879840156734695</v>
+        <v>-0.03428631996734693</v>
       </c>
       <c r="P10">
-        <v>-0.02052960365714288</v>
+        <v>-0.08000141325714286</v>
       </c>
       <c r="Q10">
-        <v>0.01847039634285712</v>
+        <v>-0.04100141325714285</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1742130390455483</v>
+        <v>0.1763198168713891</v>
       </c>
       <c r="T10">
-        <v>1.099958320169735</v>
+        <v>1.118004523386378</v>
       </c>
       <c r="U10">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V10">
-        <v>0.2441991140498078</v>
+        <v>0.1586915889442753</v>
       </c>
       <c r="W10">
-        <v>0.1109515700574882</v>
+        <v>0.1689347289399895</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y10">
-        <v>0.8139970468326925</v>
+        <v>0.5289719631475843</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1756551589575631</v>
+        <v>0.1809605972072399</v>
       </c>
       <c r="C11">
-        <v>11.24002141709989</v>
+        <v>10.61779508874229</v>
       </c>
       <c r="D11">
-        <v>12.43136141709989</v>
+        <v>11.94339508874229</v>
       </c>
       <c r="E11">
-        <v>0.78234</v>
+        <v>0.9165999999999999</v>
       </c>
       <c r="F11">
-        <v>1.20834</v>
+        <v>1.3426</v>
       </c>
       <c r="G11">
         <v>0.017</v>
@@ -2189,45 +2189,45 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M11">
-        <v>0.242634672</v>
+        <v>0.31658508</v>
       </c>
       <c r="N11">
-        <v>-0.1142877332244898</v>
+        <v>-0.1882381412244898</v>
       </c>
       <c r="O11">
-        <v>-0.03428631996734693</v>
+        <v>-0.05647144236734693</v>
       </c>
       <c r="P11">
-        <v>-0.08000141325714286</v>
+        <v>-0.1317666988571428</v>
       </c>
       <c r="Q11">
-        <v>-0.04100141325714285</v>
+        <v>-0.09276669885714281</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1763198168713891</v>
+        <v>0.1780538573362676</v>
       </c>
       <c r="T11">
-        <v>1.118004523386378</v>
+        <v>1.132857938982107</v>
       </c>
       <c r="U11">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.1586915889442753</v>
+        <v>0.1216231719847728</v>
       </c>
       <c r="W11">
-        <v>0.1689347289399895</v>
+        <v>0.2071212560459906</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.5289719631475843</v>
+        <v>0.4054105732825761</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1809605972072399</v>
+        <v>0.1828605972072399</v>
       </c>
       <c r="C12">
-        <v>10.61779508874228</v>
+        <v>10.31796999468175</v>
       </c>
       <c r="D12">
-        <v>11.94339508874229</v>
+        <v>11.77782999468175</v>
       </c>
       <c r="E12">
-        <v>0.9166000000000001</v>
+        <v>1.05086</v>
       </c>
       <c r="F12">
-        <v>1.3426</v>
+        <v>1.47686</v>
       </c>
       <c r="G12">
         <v>0.017</v>
@@ -2271,37 +2271,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M12">
-        <v>0.31658508</v>
+        <v>0.348243588</v>
       </c>
       <c r="N12">
-        <v>-0.1882381412244898</v>
+        <v>-0.2198966492244898</v>
       </c>
       <c r="O12">
-        <v>-0.05647144236734694</v>
+        <v>-0.06596899476734695</v>
       </c>
       <c r="P12">
-        <v>-0.1317666988571429</v>
+        <v>-0.1539276544571429</v>
       </c>
       <c r="Q12">
-        <v>-0.09276669885714287</v>
+        <v>-0.1149276544571429</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1780538573362676</v>
+        <v>0.1795398557333043</v>
       </c>
       <c r="T12">
-        <v>1.132857938982107</v>
+        <v>1.145586679869546</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.1216231719847728</v>
+        <v>0.1105665199861571</v>
       </c>
       <c r="W12">
-        <v>0.2071212560459906</v>
+        <v>0.2097284145872642</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.405410573282576</v>
+        <v>0.3685550666205236</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1828605972072399</v>
+        <v>0.1847605972072399</v>
       </c>
       <c r="C13">
-        <v>10.31796999468175</v>
+        <v>10.02267242403486</v>
       </c>
       <c r="D13">
-        <v>11.77782999468175</v>
+        <v>11.61679242403486</v>
       </c>
       <c r="E13">
-        <v>1.05086</v>
+        <v>1.18512</v>
       </c>
       <c r="F13">
-        <v>1.47686</v>
+        <v>1.61112</v>
       </c>
       <c r="G13">
         <v>0.017</v>
@@ -2353,37 +2353,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M13">
-        <v>0.348243588</v>
+        <v>0.379902096</v>
       </c>
       <c r="N13">
-        <v>-0.2198966492244898</v>
+        <v>-0.2515551572244897</v>
       </c>
       <c r="O13">
-        <v>-0.06596899476734695</v>
+        <v>-0.07546654716734692</v>
       </c>
       <c r="P13">
-        <v>-0.1539276544571429</v>
+        <v>-0.1760886100571428</v>
       </c>
       <c r="Q13">
-        <v>-0.1149276544571429</v>
+        <v>-0.1370886100571428</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1795398557333043</v>
+        <v>0.1810596268211827</v>
       </c>
       <c r="T13">
-        <v>1.145586679869546</v>
+        <v>1.158604710322609</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.1105665199861571</v>
+        <v>0.101352643320644</v>
       </c>
       <c r="W13">
-        <v>0.2097284145872642</v>
+        <v>0.2119010467049922</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.3685550666205236</v>
+        <v>0.3378421444021468</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1847605972072399</v>
+        <v>0.1866605972072399</v>
       </c>
       <c r="C14">
-        <v>10.02267242403486</v>
+        <v>9.731719168126011</v>
       </c>
       <c r="D14">
-        <v>11.61679242403486</v>
+        <v>11.46009916812601</v>
       </c>
       <c r="E14">
-        <v>1.18512</v>
+        <v>1.31938</v>
       </c>
       <c r="F14">
-        <v>1.61112</v>
+        <v>1.74538</v>
       </c>
       <c r="G14">
         <v>0.017</v>
@@ -2435,37 +2435,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M14">
-        <v>0.379902096</v>
+        <v>0.4115606040000001</v>
       </c>
       <c r="N14">
-        <v>-0.2515551572244897</v>
+        <v>-0.2832136652244899</v>
       </c>
       <c r="O14">
-        <v>-0.07546654716734692</v>
+        <v>-0.08496409956734696</v>
       </c>
       <c r="P14">
-        <v>-0.1760886100571428</v>
+        <v>-0.1982495656571429</v>
       </c>
       <c r="Q14">
-        <v>-0.1370886100571428</v>
+        <v>-0.1592495656571429</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1810596268211827</v>
+        <v>0.1826143351754492</v>
       </c>
       <c r="T14">
-        <v>1.158604710322609</v>
+        <v>1.171922005843559</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.101352643320644</v>
+        <v>0.09355628614213293</v>
       </c>
       <c r="W14">
-        <v>0.2119010467049922</v>
+        <v>0.2137394277276851</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3378421444021468</v>
+        <v>0.3118542871404431</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1866605972072399</v>
+        <v>0.1885605972072399</v>
       </c>
       <c r="C15">
-        <v>9.731719168126011</v>
+        <v>9.444936771572635</v>
       </c>
       <c r="D15">
-        <v>11.46009916812601</v>
+        <v>11.30757677157264</v>
       </c>
       <c r="E15">
-        <v>1.31938</v>
+        <v>1.45364</v>
       </c>
       <c r="F15">
-        <v>1.74538</v>
+        <v>1.87964</v>
       </c>
       <c r="G15">
         <v>0.017</v>
@@ -2517,37 +2517,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M15">
-        <v>0.4115606040000001</v>
+        <v>0.4432191120000001</v>
       </c>
       <c r="N15">
-        <v>-0.2832136652244899</v>
+        <v>-0.3148721732244899</v>
       </c>
       <c r="O15">
-        <v>-0.08496409956734696</v>
+        <v>-0.09446165196734697</v>
       </c>
       <c r="P15">
-        <v>-0.1982495656571429</v>
+        <v>-0.2204105212571429</v>
       </c>
       <c r="Q15">
-        <v>-0.1592495656571429</v>
+        <v>-0.1814105212571429</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1826143351754492</v>
+        <v>0.1842051995379544</v>
       </c>
       <c r="T15">
-        <v>1.171922005843559</v>
+        <v>1.185549005911507</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.09355628614213293</v>
+        <v>0.08687369427483771</v>
       </c>
       <c r="W15">
-        <v>0.2137394277276851</v>
+        <v>0.2153151828899933</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3118542871404431</v>
+        <v>0.2895789809161257</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1885605972072399</v>
+        <v>0.1904605972072399</v>
       </c>
       <c r="C16">
-        <v>9.444936771572635</v>
+        <v>9.162160891777049</v>
       </c>
       <c r="D16">
-        <v>11.30757677157264</v>
+        <v>11.15906089177705</v>
       </c>
       <c r="E16">
-        <v>1.45364</v>
+        <v>1.587900000000001</v>
       </c>
       <c r="F16">
-        <v>1.87964</v>
+        <v>2.0139</v>
       </c>
       <c r="G16">
         <v>0.017</v>
@@ -2599,37 +2599,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M16">
-        <v>0.4432191120000001</v>
+        <v>0.4748776200000001</v>
       </c>
       <c r="N16">
-        <v>-0.3148721732244899</v>
+        <v>-0.3465306812244899</v>
       </c>
       <c r="O16">
-        <v>-0.09446165196734697</v>
+        <v>-0.103959204367347</v>
       </c>
       <c r="P16">
-        <v>-0.2204105212571429</v>
+        <v>-0.242571476857143</v>
       </c>
       <c r="Q16">
-        <v>-0.1814105212571429</v>
+        <v>-0.203571476857143</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1842051995379544</v>
+        <v>0.1858334960031068</v>
       </c>
       <c r="T16">
-        <v>1.185549005911507</v>
+        <v>1.199496641275172</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.08687369427483771</v>
+        <v>0.08108211465651519</v>
       </c>
       <c r="W16">
-        <v>0.2153151828899933</v>
+        <v>0.2166808373639937</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2895789809161257</v>
+        <v>0.2702737155217173</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1904605972072399</v>
+        <v>0.1923605972072399</v>
       </c>
       <c r="C17">
-        <v>9.162160891777051</v>
+        <v>8.883235708239379</v>
       </c>
       <c r="D17">
-        <v>11.15906089177705</v>
+        <v>11.01439570823938</v>
       </c>
       <c r="E17">
-        <v>1.5879</v>
+        <v>1.72216</v>
       </c>
       <c r="F17">
-        <v>2.0139</v>
+        <v>2.14816</v>
       </c>
       <c r="G17">
         <v>0.017</v>
@@ -2681,37 +2681,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M17">
-        <v>0.47487762</v>
+        <v>0.5065361280000001</v>
       </c>
       <c r="N17">
-        <v>-0.3465306812244898</v>
+        <v>-0.37818918922449</v>
       </c>
       <c r="O17">
-        <v>-0.1039592043673469</v>
+        <v>-0.113456756767347</v>
       </c>
       <c r="P17">
-        <v>-0.2425714768571429</v>
+        <v>-0.264732432457143</v>
       </c>
       <c r="Q17">
-        <v>-0.2035714768571429</v>
+        <v>-0.2257324324571429</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1858334960031068</v>
+        <v>0.1875005614317153</v>
       </c>
       <c r="T17">
-        <v>1.199496641275172</v>
+        <v>1.213776363195115</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.0810821146565152</v>
+        <v>0.076014482490483</v>
       </c>
       <c r="W17">
-        <v>0.2166808373639937</v>
+        <v>0.2178757850287441</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2702737155217173</v>
+        <v>0.2533816083016099</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1923605972072399</v>
+        <v>0.1942605972072399</v>
       </c>
       <c r="C18">
-        <v>8.883235708239379</v>
+        <v>8.608013377228128</v>
       </c>
       <c r="D18">
-        <v>11.01439570823938</v>
+        <v>10.87343337722813</v>
       </c>
       <c r="E18">
-        <v>1.72216</v>
+        <v>1.85642</v>
       </c>
       <c r="F18">
-        <v>2.14816</v>
+        <v>2.28242</v>
       </c>
       <c r="G18">
         <v>0.017</v>
@@ -2763,37 +2763,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M18">
-        <v>0.5065361280000001</v>
+        <v>0.5381946360000001</v>
       </c>
       <c r="N18">
-        <v>-0.37818918922449</v>
+        <v>-0.4098476972244899</v>
       </c>
       <c r="O18">
-        <v>-0.113456756767347</v>
+        <v>-0.122954309167347</v>
       </c>
       <c r="P18">
-        <v>-0.264732432457143</v>
+        <v>-0.2868933880571429</v>
       </c>
       <c r="Q18">
-        <v>-0.2257324324571429</v>
+        <v>-0.2478933880571429</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1875005614317153</v>
+        <v>0.1892077971116155</v>
       </c>
       <c r="T18">
-        <v>1.213776363195115</v>
+        <v>1.228400174799875</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.076014482490483</v>
+        <v>0.071543042343984</v>
       </c>
       <c r="W18">
-        <v>0.2178757850287441</v>
+        <v>0.2189301506152886</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2533816083016099</v>
+        <v>0.23847680781328</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1942605972072399</v>
+        <v>0.1961605972072399</v>
       </c>
       <c r="C19">
-        <v>8.608013377228128</v>
+        <v>8.33635352779644</v>
       </c>
       <c r="D19">
-        <v>10.87343337722813</v>
+        <v>10.73603352779644</v>
       </c>
       <c r="E19">
-        <v>1.85642</v>
+        <v>1.99068</v>
       </c>
       <c r="F19">
-        <v>2.28242</v>
+        <v>2.41668</v>
       </c>
       <c r="G19">
         <v>0.017</v>
@@ -2845,37 +2845,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M19">
-        <v>0.5381946360000001</v>
+        <v>0.5698531440000001</v>
       </c>
       <c r="N19">
-        <v>-0.4098476972244899</v>
+        <v>-0.4415062052244899</v>
       </c>
       <c r="O19">
-        <v>-0.122954309167347</v>
+        <v>-0.132451861567347</v>
       </c>
       <c r="P19">
-        <v>-0.2868933880571429</v>
+        <v>-0.3090543436571429</v>
       </c>
       <c r="Q19">
-        <v>-0.2478933880571429</v>
+        <v>-0.2700543436571429</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1892077971116155</v>
+        <v>0.1909566726861474</v>
       </c>
       <c r="T19">
-        <v>1.228400174799875</v>
+        <v>1.243380664736459</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.071543042343984</v>
+        <v>0.06756842888042933</v>
       </c>
       <c r="W19">
-        <v>0.2189301506152886</v>
+        <v>0.2198673644699948</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.23847680781328</v>
+        <v>0.2252280962680977</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1961605972072399</v>
+        <v>0.1980605972072398</v>
       </c>
       <c r="C20">
-        <v>8.33635352779644</v>
+        <v>8.068122795532405</v>
       </c>
       <c r="D20">
-        <v>10.73603352779644</v>
+        <v>10.60206279553241</v>
       </c>
       <c r="E20">
-        <v>1.99068</v>
+        <v>2.12494</v>
       </c>
       <c r="F20">
-        <v>2.41668</v>
+        <v>2.55094</v>
       </c>
       <c r="G20">
         <v>0.017</v>
@@ -2927,37 +2927,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M20">
-        <v>0.569853144</v>
+        <v>0.6015116520000001</v>
       </c>
       <c r="N20">
-        <v>-0.4415062052244898</v>
+        <v>-0.4731647132244899</v>
       </c>
       <c r="O20">
-        <v>-0.1324518615673469</v>
+        <v>-0.141949413967347</v>
       </c>
       <c r="P20">
-        <v>-0.3090543436571429</v>
+        <v>-0.331215299257143</v>
       </c>
       <c r="Q20">
-        <v>-0.2700543436571429</v>
+        <v>-0.292215299257143</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1909566726861473</v>
+        <v>0.1927487303736306</v>
       </c>
       <c r="T20">
-        <v>1.243380664736459</v>
+        <v>1.258731043313452</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.06756842888042934</v>
+        <v>0.06401219578145936</v>
       </c>
       <c r="W20">
-        <v>0.2198673644699948</v>
+        <v>0.2207059242347319</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2252280962680978</v>
+        <v>0.2133739859381978</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1980605972072398</v>
+        <v>0.1999605972072399</v>
       </c>
       <c r="C21">
-        <v>8.068122795532405</v>
+        <v>7.803194390788018</v>
       </c>
       <c r="D21">
-        <v>10.60206279553241</v>
+        <v>10.47139439078802</v>
       </c>
       <c r="E21">
-        <v>2.12494</v>
+        <v>2.2592</v>
       </c>
       <c r="F21">
-        <v>2.55094</v>
+        <v>2.6852</v>
       </c>
       <c r="G21">
         <v>0.017</v>
@@ -3009,37 +3009,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M21">
-        <v>0.6015116520000001</v>
+        <v>0.63317016</v>
       </c>
       <c r="N21">
-        <v>-0.4731647132244899</v>
+        <v>-0.5048232212244899</v>
       </c>
       <c r="O21">
-        <v>-0.141949413967347</v>
+        <v>-0.1514469663673469</v>
       </c>
       <c r="P21">
-        <v>-0.331215299257143</v>
+        <v>-0.3533762548571429</v>
       </c>
       <c r="Q21">
-        <v>-0.292215299257143</v>
+        <v>-0.3143762548571429</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1927487303736306</v>
+        <v>0.194585589503301</v>
       </c>
       <c r="T21">
-        <v>1.258731043313452</v>
+        <v>1.27446518135487</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.06401219578145936</v>
+        <v>0.0608115859923864</v>
       </c>
       <c r="W21">
-        <v>0.2207059242347319</v>
+        <v>0.2214606280229953</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2133739859381978</v>
+        <v>0.202705286641288</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1999605972072399</v>
+        <v>0.2018605972072399</v>
       </c>
       <c r="C22">
-        <v>7.803194390788018</v>
+        <v>7.541447698448395</v>
       </c>
       <c r="D22">
-        <v>10.47139439078802</v>
+        <v>10.3439076984484</v>
       </c>
       <c r="E22">
-        <v>2.2592</v>
+        <v>2.39346</v>
       </c>
       <c r="F22">
-        <v>2.6852</v>
+        <v>2.81946</v>
       </c>
       <c r="G22">
         <v>0.017</v>
@@ -3091,37 +3091,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M22">
-        <v>0.63317016</v>
+        <v>0.6648286680000001</v>
       </c>
       <c r="N22">
-        <v>-0.5048232212244899</v>
+        <v>-0.5364817292244899</v>
       </c>
       <c r="O22">
-        <v>-0.1514469663673469</v>
+        <v>-0.160944518767347</v>
       </c>
       <c r="P22">
-        <v>-0.3533762548571429</v>
+        <v>-0.3755372104571429</v>
       </c>
       <c r="Q22">
-        <v>-0.3143762548571429</v>
+        <v>-0.3365372104571429</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.194585589503301</v>
+        <v>0.1964689513957479</v>
       </c>
       <c r="T22">
-        <v>1.27446518135487</v>
+        <v>1.290597652004932</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.0608115859923864</v>
+        <v>0.05791579618322515</v>
       </c>
       <c r="W22">
-        <v>0.2214606280229953</v>
+        <v>0.2221434552599955</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.202705286641288</v>
+        <v>0.1930526539440838</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2018605972072399</v>
+        <v>0.2037605972072399</v>
       </c>
       <c r="C23">
-        <v>7.541447698448398</v>
+        <v>7.282767906585576</v>
       </c>
       <c r="D23">
-        <v>10.3439076984484</v>
+        <v>10.21948790658558</v>
       </c>
       <c r="E23">
-        <v>2.39346</v>
+        <v>2.52772</v>
       </c>
       <c r="F23">
-        <v>2.81946</v>
+        <v>2.95372</v>
       </c>
       <c r="G23">
         <v>0.017</v>
@@ -3173,37 +3173,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M23">
-        <v>0.664828668</v>
+        <v>0.6964871760000001</v>
       </c>
       <c r="N23">
-        <v>-0.5364817292244898</v>
+        <v>-0.5681402372244899</v>
       </c>
       <c r="O23">
-        <v>-0.1609445187673469</v>
+        <v>-0.170442071167347</v>
       </c>
       <c r="P23">
-        <v>-0.3755372104571428</v>
+        <v>-0.3976981660571429</v>
       </c>
       <c r="Q23">
-        <v>-0.3365372104571428</v>
+        <v>-0.3586981660571429</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1964689513957479</v>
+        <v>0.1984006046187703</v>
       </c>
       <c r="T23">
-        <v>1.290597652004932</v>
+        <v>1.307143775748585</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05791579618322516</v>
+        <v>0.05528325999307854</v>
       </c>
       <c r="W23">
-        <v>0.2221434552599955</v>
+        <v>0.2227642072936321</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1930526539440838</v>
+        <v>0.1842775333102618</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2037605972072399</v>
+        <v>0.2056605972072398</v>
       </c>
       <c r="C24">
-        <v>7.282767906585576</v>
+        <v>7.027045661593831</v>
       </c>
       <c r="D24">
-        <v>10.21948790658558</v>
+        <v>10.09802566159383</v>
       </c>
       <c r="E24">
-        <v>2.52772</v>
+        <v>2.66198</v>
       </c>
       <c r="F24">
-        <v>2.95372</v>
+        <v>3.08798</v>
       </c>
       <c r="G24">
         <v>0.017</v>
@@ -3255,37 +3255,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M24">
-        <v>0.6964871760000001</v>
+        <v>0.7281456840000001</v>
       </c>
       <c r="N24">
-        <v>-0.5681402372244899</v>
+        <v>-0.5997987452244899</v>
       </c>
       <c r="O24">
-        <v>-0.170442071167347</v>
+        <v>-0.179939623567347</v>
       </c>
       <c r="P24">
-        <v>-0.3976981660571429</v>
+        <v>-0.419859121657143</v>
       </c>
       <c r="Q24">
-        <v>-0.3586981660571429</v>
+        <v>-0.380859121657143</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1984006046187703</v>
+        <v>0.2003824306527802</v>
       </c>
       <c r="T24">
-        <v>1.307143775748585</v>
+        <v>1.324119668940125</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.05528325999307854</v>
+        <v>0.05287963999337948</v>
       </c>
       <c r="W24">
-        <v>0.2227642072936321</v>
+        <v>0.2233309808895611</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1842775333102618</v>
+        <v>0.1762654666445982</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2056605972072398</v>
+        <v>0.2075605972072399</v>
       </c>
       <c r="C25">
-        <v>7.027045661593831</v>
+        <v>6.774176747629149</v>
       </c>
       <c r="D25">
-        <v>10.09802566159383</v>
+        <v>9.97941674762915</v>
       </c>
       <c r="E25">
-        <v>2.66198</v>
+        <v>2.79624</v>
       </c>
       <c r="F25">
-        <v>3.08798</v>
+        <v>3.22224</v>
       </c>
       <c r="G25">
         <v>0.017</v>
@@ -3337,37 +3337,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M25">
-        <v>0.7281456840000001</v>
+        <v>0.759804192</v>
       </c>
       <c r="N25">
-        <v>-0.5997987452244899</v>
+        <v>-0.6314572532244899</v>
       </c>
       <c r="O25">
-        <v>-0.179939623567347</v>
+        <v>-0.189437175967347</v>
       </c>
       <c r="P25">
-        <v>-0.419859121657143</v>
+        <v>-0.4420200772571429</v>
       </c>
       <c r="Q25">
-        <v>-0.380859121657143</v>
+        <v>-0.4030200772571428</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2003824306527802</v>
+        <v>0.2024164100034748</v>
       </c>
       <c r="T25">
-        <v>1.324119668940125</v>
+        <v>1.341542296163021</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05287963999337948</v>
+        <v>0.05067632166032201</v>
       </c>
       <c r="W25">
-        <v>0.2233309808895611</v>
+        <v>0.2238505233524961</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1762654666445982</v>
+        <v>0.1689210722010733</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2075605972072398</v>
+        <v>0.2094605972072399</v>
       </c>
       <c r="C26">
-        <v>6.774176747629154</v>
+        <v>6.524061788377809</v>
       </c>
       <c r="D26">
-        <v>9.979416747629154</v>
+        <v>9.86356178837781</v>
       </c>
       <c r="E26">
-        <v>2.79624</v>
+        <v>2.9305</v>
       </c>
       <c r="F26">
-        <v>3.22224</v>
+        <v>3.3565</v>
       </c>
       <c r="G26">
         <v>0.017</v>
@@ -3419,37 +3419,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M26">
-        <v>0.7598041919999999</v>
+        <v>0.7914627000000001</v>
       </c>
       <c r="N26">
-        <v>-0.6314572532244898</v>
+        <v>-0.6631157612244899</v>
       </c>
       <c r="O26">
-        <v>-0.1894371759673469</v>
+        <v>-0.198934728367347</v>
       </c>
       <c r="P26">
-        <v>-0.4420200772571429</v>
+        <v>-0.464181032857143</v>
       </c>
       <c r="Q26">
-        <v>-0.4030200772571428</v>
+        <v>-0.4251810328571429</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2024164100034747</v>
+        <v>0.2045046288035211</v>
       </c>
       <c r="T26">
-        <v>1.341542296163021</v>
+        <v>1.359429526778528</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05067632166032202</v>
+        <v>0.04864926879390912</v>
       </c>
       <c r="W26">
-        <v>0.2238505233524961</v>
+        <v>0.2243285024183962</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1689210722010733</v>
+        <v>0.1621642293130304</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2094605972072399</v>
+        <v>0.2113605972072399</v>
       </c>
       <c r="C27">
-        <v>6.524061788377809</v>
+        <v>6.276605969360199</v>
       </c>
       <c r="D27">
-        <v>9.86356178837781</v>
+        <v>9.7503659693602</v>
       </c>
       <c r="E27">
-        <v>2.9305</v>
+        <v>3.06476</v>
       </c>
       <c r="F27">
-        <v>3.3565</v>
+        <v>3.49076</v>
       </c>
       <c r="G27">
         <v>0.017</v>
@@ -3501,37 +3501,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M27">
-        <v>0.7914627000000001</v>
+        <v>0.8231212080000001</v>
       </c>
       <c r="N27">
-        <v>-0.6631157612244899</v>
+        <v>-0.6947742692244899</v>
       </c>
       <c r="O27">
-        <v>-0.198934728367347</v>
+        <v>-0.208432280767347</v>
       </c>
       <c r="P27">
-        <v>-0.464181032857143</v>
+        <v>-0.4863419884571429</v>
       </c>
       <c r="Q27">
-        <v>-0.4251810328571429</v>
+        <v>-0.4473419884571429</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2045046288035211</v>
+        <v>0.2066492859495146</v>
       </c>
       <c r="T27">
-        <v>1.359429526778528</v>
+        <v>1.377800196059319</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04864926879390912</v>
+        <v>0.04677814307106647</v>
       </c>
       <c r="W27">
-        <v>0.2243285024183962</v>
+        <v>0.2247697138638425</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1621642293130304</v>
+        <v>0.1559271435702215</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2113605972072399</v>
+        <v>0.2132605972072399</v>
       </c>
       <c r="C28">
-        <v>6.276605969360199</v>
+        <v>6.031718779139097</v>
       </c>
       <c r="D28">
-        <v>9.7503659693602</v>
+        <v>9.639738779139098</v>
       </c>
       <c r="E28">
-        <v>3.06476</v>
+        <v>3.19902</v>
       </c>
       <c r="F28">
-        <v>3.49076</v>
+        <v>3.62502</v>
       </c>
       <c r="G28">
         <v>0.017</v>
@@ -3583,37 +3583,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M28">
-        <v>0.8231212080000001</v>
+        <v>0.854779716</v>
       </c>
       <c r="N28">
-        <v>-0.6947742692244899</v>
+        <v>-0.7264327772244898</v>
       </c>
       <c r="O28">
-        <v>-0.208432280767347</v>
+        <v>-0.217929833167347</v>
       </c>
       <c r="P28">
-        <v>-0.4863419884571429</v>
+        <v>-0.5085029440571429</v>
       </c>
       <c r="Q28">
-        <v>-0.4473419884571429</v>
+        <v>-0.4695029440571429</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2066492859495146</v>
+        <v>0.2088527008255354</v>
       </c>
       <c r="T28">
-        <v>1.377800196059319</v>
+        <v>1.396674171347803</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04677814307106647</v>
+        <v>0.04504561925361956</v>
       </c>
       <c r="W28">
-        <v>0.2247697138638425</v>
+        <v>0.2251782429799965</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1559271435702215</v>
+        <v>0.1501520641787318</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2132605972072399</v>
+        <v>0.2151605972072398</v>
       </c>
       <c r="C29">
-        <v>6.031718779139097</v>
+        <v>5.78931376794767</v>
       </c>
       <c r="D29">
-        <v>9.639738779139098</v>
+        <v>9.531593767947671</v>
       </c>
       <c r="E29">
-        <v>3.19902</v>
+        <v>3.33328</v>
       </c>
       <c r="F29">
-        <v>3.62502</v>
+        <v>3.75928</v>
       </c>
       <c r="G29">
         <v>0.017</v>
@@ -3665,37 +3665,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M29">
-        <v>0.854779716</v>
+        <v>0.8864382240000002</v>
       </c>
       <c r="N29">
-        <v>-0.7264327772244898</v>
+        <v>-0.75809128522449</v>
       </c>
       <c r="O29">
-        <v>-0.217929833167347</v>
+        <v>-0.227427385567347</v>
       </c>
       <c r="P29">
-        <v>-0.5085029440571429</v>
+        <v>-0.530663899657143</v>
       </c>
       <c r="Q29">
-        <v>-0.4695029440571429</v>
+        <v>-0.491663899657143</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2088527008255354</v>
+        <v>0.2111173216703345</v>
       </c>
       <c r="T29">
-        <v>1.396674171347803</v>
+        <v>1.416072423727633</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04504561925361956</v>
+        <v>0.04343684713741885</v>
       </c>
       <c r="W29">
-        <v>0.2251782429799965</v>
+        <v>0.2255575914449966</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1501520641787318</v>
+        <v>0.1447894904580628</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2151605972072398</v>
+        <v>0.2170605972072399</v>
       </c>
       <c r="C30">
-        <v>5.78931376794767</v>
+        <v>5.549308322384463</v>
       </c>
       <c r="D30">
-        <v>9.531593767947671</v>
+        <v>9.425848322384464</v>
       </c>
       <c r="E30">
-        <v>3.33328</v>
+        <v>3.467540000000001</v>
       </c>
       <c r="F30">
-        <v>3.75928</v>
+        <v>3.893540000000001</v>
       </c>
       <c r="G30">
         <v>0.017</v>
@@ -3747,37 +3747,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M30">
-        <v>0.8864382240000002</v>
+        <v>0.9180967320000002</v>
       </c>
       <c r="N30">
-        <v>-0.75809128522449</v>
+        <v>-0.78974979322449</v>
       </c>
       <c r="O30">
-        <v>-0.227427385567347</v>
+        <v>-0.236924937967347</v>
       </c>
       <c r="P30">
-        <v>-0.530663899657143</v>
+        <v>-0.5528248552571431</v>
       </c>
       <c r="Q30">
-        <v>-0.491663899657143</v>
+        <v>-0.5138248552571431</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2111173216703345</v>
+        <v>0.2134457346516068</v>
       </c>
       <c r="T30">
-        <v>1.416072423727633</v>
+        <v>1.436017105751967</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04343684713741885</v>
+        <v>0.04193902482233545</v>
       </c>
       <c r="W30">
-        <v>0.2255575914449966</v>
+        <v>0.2259107779468933</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1447894904580628</v>
+        <v>0.1397967494077847</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2170605972072399</v>
+        <v>0.2189605972072399</v>
       </c>
       <c r="C31">
-        <v>5.549308322384464</v>
+        <v>5.31162345494134</v>
       </c>
       <c r="D31">
-        <v>9.425848322384464</v>
+        <v>9.32242345494134</v>
       </c>
       <c r="E31">
-        <v>3.46754</v>
+        <v>3.6018</v>
       </c>
       <c r="F31">
-        <v>3.89354</v>
+        <v>4.0278</v>
       </c>
       <c r="G31">
         <v>0.017</v>
@@ -3829,37 +3829,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M31">
-        <v>0.918096732</v>
+        <v>0.94975524</v>
       </c>
       <c r="N31">
-        <v>-0.7897497932244898</v>
+        <v>-0.8214083012244898</v>
       </c>
       <c r="O31">
-        <v>-0.2369249379673469</v>
+        <v>-0.2464224903673469</v>
       </c>
       <c r="P31">
-        <v>-0.5528248552571429</v>
+        <v>-0.5749858108571428</v>
       </c>
       <c r="Q31">
-        <v>-0.5138248552571428</v>
+        <v>-0.5359858108571428</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2134457346516068</v>
+        <v>0.2158406737180583</v>
       </c>
       <c r="T31">
-        <v>1.436017105751967</v>
+        <v>1.456531635834138</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04193902482233546</v>
+        <v>0.0405410573282576</v>
       </c>
       <c r="W31">
-        <v>0.2259107779468933</v>
+        <v>0.2262404186819968</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1397967494077849</v>
+        <v>0.1351368577608587</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2189605972072399</v>
+        <v>0.2208605972072398</v>
       </c>
       <c r="C32">
-        <v>5.31162345494134</v>
+        <v>5.076183607237407</v>
       </c>
       <c r="D32">
-        <v>9.32242345494134</v>
+        <v>9.221243607237408</v>
       </c>
       <c r="E32">
-        <v>3.6018</v>
+        <v>3.73606</v>
       </c>
       <c r="F32">
-        <v>4.0278</v>
+        <v>4.16206</v>
       </c>
       <c r="G32">
         <v>0.017</v>
@@ -3911,37 +3911,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M32">
-        <v>0.94975524</v>
+        <v>0.9814137480000001</v>
       </c>
       <c r="N32">
-        <v>-0.8214083012244898</v>
+        <v>-0.85306680922449</v>
       </c>
       <c r="O32">
-        <v>-0.2464224903673469</v>
+        <v>-0.255920042767347</v>
       </c>
       <c r="P32">
-        <v>-0.5749858108571428</v>
+        <v>-0.597146766457143</v>
       </c>
       <c r="Q32">
-        <v>-0.5359858108571428</v>
+        <v>-0.558146766457143</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2158406737180583</v>
+        <v>0.2183050313081751</v>
       </c>
       <c r="T32">
-        <v>1.456531635834138</v>
+        <v>1.477640789976661</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0405410573282576</v>
+        <v>0.03923328128541059</v>
       </c>
       <c r="W32">
-        <v>0.2262404186819968</v>
+        <v>0.2265487922729002</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1351368577608587</v>
+        <v>0.1307776042847019</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2208605972072398</v>
+        <v>0.2227605972072399</v>
       </c>
       <c r="C33">
-        <v>5.076183607237407</v>
+        <v>4.842916465928806</v>
       </c>
       <c r="D33">
-        <v>9.221243607237408</v>
+        <v>9.122236465928808</v>
       </c>
       <c r="E33">
-        <v>3.73606</v>
+        <v>3.87032</v>
       </c>
       <c r="F33">
-        <v>4.16206</v>
+        <v>4.296320000000001</v>
       </c>
       <c r="G33">
         <v>0.017</v>
@@ -3993,37 +3993,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M33">
-        <v>0.9814137480000001</v>
+        <v>1.013072256</v>
       </c>
       <c r="N33">
-        <v>-0.85306680922449</v>
+        <v>-0.8847253172244901</v>
       </c>
       <c r="O33">
-        <v>-0.255920042767347</v>
+        <v>-0.265417595167347</v>
       </c>
       <c r="P33">
-        <v>-0.597146766457143</v>
+        <v>-0.619307722057143</v>
       </c>
       <c r="Q33">
-        <v>-0.558146766457143</v>
+        <v>-0.580307722057143</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2183050313081751</v>
+        <v>0.2208418700038836</v>
       </c>
       <c r="T33">
-        <v>1.477640789976661</v>
+        <v>1.499370801593965</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03923328128541059</v>
+        <v>0.0380072412452415</v>
       </c>
       <c r="W33">
-        <v>0.2265487922729002</v>
+        <v>0.2268378925143721</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1307776042847019</v>
+        <v>0.1266908041508049</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2227605972072399</v>
+        <v>0.2246605972072399</v>
       </c>
       <c r="C34">
-        <v>4.842916465928806</v>
+        <v>4.611752790351887</v>
       </c>
       <c r="D34">
-        <v>9.122236465928808</v>
+        <v>9.025332790351888</v>
       </c>
       <c r="E34">
-        <v>3.87032</v>
+        <v>4.00458</v>
       </c>
       <c r="F34">
-        <v>4.296320000000001</v>
+        <v>4.43058</v>
       </c>
       <c r="G34">
         <v>0.017</v>
@@ -4075,37 +4075,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M34">
-        <v>1.013072256</v>
+        <v>1.044730764</v>
       </c>
       <c r="N34">
-        <v>-0.8847253172244901</v>
+        <v>-0.9163838252244899</v>
       </c>
       <c r="O34">
-        <v>-0.265417595167347</v>
+        <v>-0.274915147567347</v>
       </c>
       <c r="P34">
-        <v>-0.619307722057143</v>
+        <v>-0.641468677657143</v>
       </c>
       <c r="Q34">
-        <v>-0.580307722057143</v>
+        <v>-0.602468677657143</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2208418700038836</v>
+        <v>0.2234544352278221</v>
       </c>
       <c r="T34">
-        <v>1.499370801593965</v>
+        <v>1.521749470274472</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.0380072412452415</v>
+        <v>0.03685550666205237</v>
       </c>
       <c r="W34">
-        <v>0.2268378925143721</v>
+        <v>0.2271094715290881</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1266908041508049</v>
+        <v>0.1228516888735078</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2246605972072399</v>
+        <v>0.2265605972072399</v>
       </c>
       <c r="C35">
-        <v>4.611752790351887</v>
+        <v>4.382626251036305</v>
       </c>
       <c r="D35">
-        <v>9.025332790351888</v>
+        <v>8.930466251036306</v>
       </c>
       <c r="E35">
-        <v>4.00458</v>
+        <v>4.13884</v>
       </c>
       <c r="F35">
-        <v>4.43058</v>
+        <v>4.56484</v>
       </c>
       <c r="G35">
         <v>0.017</v>
@@ -4157,37 +4157,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M35">
-        <v>1.044730764</v>
+        <v>1.076389272</v>
       </c>
       <c r="N35">
-        <v>-0.9163838252244899</v>
+        <v>-0.9480423332244899</v>
       </c>
       <c r="O35">
-        <v>-0.274915147567347</v>
+        <v>-0.284412699967347</v>
       </c>
       <c r="P35">
-        <v>-0.641468677657143</v>
+        <v>-0.663629633257143</v>
       </c>
       <c r="Q35">
-        <v>-0.602468677657143</v>
+        <v>-0.6246296332571429</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2234544352278221</v>
+        <v>0.2261461690949103</v>
       </c>
       <c r="T35">
-        <v>1.521749470274472</v>
+        <v>1.544806280430146</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03685550666205237</v>
+        <v>0.035771521171992</v>
       </c>
       <c r="W35">
-        <v>0.2271094715290881</v>
+        <v>0.2273650753076443</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1228516888735078</v>
+        <v>0.11923840390664</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2265605972072399</v>
+        <v>0.2284605972072399</v>
       </c>
       <c r="C36">
-        <v>4.382626251036305</v>
+        <v>4.155473278296715</v>
       </c>
       <c r="D36">
-        <v>8.930466251036306</v>
+        <v>8.837573278296716</v>
       </c>
       <c r="E36">
-        <v>4.13884</v>
+        <v>4.2731</v>
       </c>
       <c r="F36">
-        <v>4.56484</v>
+        <v>4.6991</v>
       </c>
       <c r="G36">
         <v>0.017</v>
@@ -4239,37 +4239,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M36">
-        <v>1.076389272</v>
+        <v>1.10804778</v>
       </c>
       <c r="N36">
-        <v>-0.9480423332244899</v>
+        <v>-0.97970084122449</v>
       </c>
       <c r="O36">
-        <v>-0.284412699967347</v>
+        <v>-0.293910252367347</v>
       </c>
       <c r="P36">
-        <v>-0.663629633257143</v>
+        <v>-0.6857905888571429</v>
       </c>
       <c r="Q36">
-        <v>-0.6246296332571429</v>
+        <v>-0.6467905888571429</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2261461690949103</v>
+        <v>0.2289207255425244</v>
       </c>
       <c r="T36">
-        <v>1.544806280430146</v>
+        <v>1.568572530898302</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.035771521171992</v>
+        <v>0.03474947770993508</v>
       </c>
       <c r="W36">
-        <v>0.2273650753076443</v>
+        <v>0.2276060731559973</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.11923840390664</v>
+        <v>0.1158315923664502</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2284605972072399</v>
+        <v>0.2303605972072399</v>
       </c>
       <c r="C37">
-        <v>4.155473278296715</v>
+        <v>3.930232920176673</v>
       </c>
       <c r="D37">
-        <v>8.837573278296716</v>
+        <v>8.746592920176674</v>
       </c>
       <c r="E37">
-        <v>4.2731</v>
+        <v>4.407360000000001</v>
       </c>
       <c r="F37">
-        <v>4.6991</v>
+        <v>4.833360000000001</v>
       </c>
       <c r="G37">
         <v>0.017</v>
@@ -4321,37 +4321,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M37">
-        <v>1.10804778</v>
+        <v>1.139706288</v>
       </c>
       <c r="N37">
-        <v>-0.97970084122449</v>
+        <v>-1.01135934922449</v>
       </c>
       <c r="O37">
-        <v>-0.293910252367347</v>
+        <v>-0.303407804767347</v>
       </c>
       <c r="P37">
-        <v>-0.6857905888571429</v>
+        <v>-0.7079515444571429</v>
       </c>
       <c r="Q37">
-        <v>-0.6467905888571429</v>
+        <v>-0.6689515444571429</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2289207255425244</v>
+        <v>0.2317819868791263</v>
       </c>
       <c r="T37">
-        <v>1.568572530898302</v>
+        <v>1.593081476693588</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03474947770993508</v>
+        <v>0.03378421444021466</v>
       </c>
       <c r="W37">
-        <v>0.2276060731559973</v>
+        <v>0.2278336822349974</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1158315923664502</v>
+        <v>0.112614048134049</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2303605972072399</v>
+        <v>0.2322605972072399</v>
       </c>
       <c r="C38">
-        <v>3.930232920176672</v>
+        <v>3.706846709077684</v>
       </c>
       <c r="D38">
-        <v>8.746592920176672</v>
+        <v>8.657466709077685</v>
       </c>
       <c r="E38">
-        <v>4.40736</v>
+        <v>4.54162</v>
       </c>
       <c r="F38">
-        <v>4.83336</v>
+        <v>4.96762</v>
       </c>
       <c r="G38">
         <v>0.017</v>
@@ -4403,37 +4403,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M38">
-        <v>1.139706288</v>
+        <v>1.171364796</v>
       </c>
       <c r="N38">
-        <v>-1.01135934922449</v>
+        <v>-1.04301785722449</v>
       </c>
       <c r="O38">
-        <v>-0.3034078047673469</v>
+        <v>-0.3129053571673469</v>
       </c>
       <c r="P38">
-        <v>-0.7079515444571427</v>
+        <v>-0.7301125000571428</v>
       </c>
       <c r="Q38">
-        <v>-0.6689515444571427</v>
+        <v>-0.6911125000571428</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2317819868791263</v>
+        <v>0.2347340819089537</v>
       </c>
       <c r="T38">
-        <v>1.593081476693588</v>
+        <v>1.618368484260153</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03378421444021467</v>
+        <v>0.03287112756345211</v>
       </c>
       <c r="W38">
-        <v>0.2278336822349974</v>
+        <v>0.228048988120538</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.112614048134049</v>
+        <v>0.1095704252115071</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2322605972072399</v>
+        <v>0.2341605972072399</v>
       </c>
       <c r="C39">
-        <v>3.706846709077684</v>
+        <v>3.485258536460194</v>
       </c>
       <c r="D39">
-        <v>8.657466709077685</v>
+        <v>8.570138536460195</v>
       </c>
       <c r="E39">
-        <v>4.54162</v>
+        <v>4.67588</v>
       </c>
       <c r="F39">
-        <v>4.96762</v>
+        <v>5.10188</v>
       </c>
       <c r="G39">
         <v>0.017</v>
@@ -4485,37 +4485,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M39">
-        <v>1.171364796</v>
+        <v>1.203023304</v>
       </c>
       <c r="N39">
-        <v>-1.04301785722449</v>
+        <v>-1.07467636522449</v>
       </c>
       <c r="O39">
-        <v>-0.3129053571673469</v>
+        <v>-0.322402909567347</v>
       </c>
       <c r="P39">
-        <v>-0.7301125000571428</v>
+        <v>-0.752273455657143</v>
       </c>
       <c r="Q39">
-        <v>-0.6911125000571428</v>
+        <v>-0.713273455657143</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2347340819089537</v>
+        <v>0.237781405810711</v>
       </c>
       <c r="T39">
-        <v>1.618368484260153</v>
+        <v>1.64447120174822</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03287112756345211</v>
+        <v>0.03200609789072968</v>
       </c>
       <c r="W39">
-        <v>0.228048988120538</v>
+        <v>0.228252962117366</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1095704252115071</v>
+        <v>0.106686992969099</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2341605972072399</v>
+        <v>0.2360605972072399</v>
       </c>
       <c r="C40">
-        <v>3.485258536460194</v>
+        <v>3.265414535052178</v>
       </c>
       <c r="D40">
-        <v>8.570138536460195</v>
+        <v>8.48455453505218</v>
       </c>
       <c r="E40">
-        <v>4.67588</v>
+        <v>4.810140000000001</v>
       </c>
       <c r="F40">
-        <v>5.10188</v>
+        <v>5.236140000000001</v>
       </c>
       <c r="G40">
         <v>0.017</v>
@@ -4567,37 +4567,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M40">
-        <v>1.203023304</v>
+        <v>1.234681812</v>
       </c>
       <c r="N40">
-        <v>-1.07467636522449</v>
+        <v>-1.10633487322449</v>
       </c>
       <c r="O40">
-        <v>-0.322402909567347</v>
+        <v>-0.331900461967347</v>
       </c>
       <c r="P40">
-        <v>-0.752273455657143</v>
+        <v>-0.7744344112571431</v>
       </c>
       <c r="Q40">
-        <v>-0.713273455657143</v>
+        <v>-0.735434411257143</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.237781405810711</v>
+        <v>0.2409286419715423</v>
       </c>
       <c r="T40">
-        <v>1.64447120174822</v>
+        <v>1.671429746039174</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03200609789072968</v>
+        <v>0.0311854287140443</v>
       </c>
       <c r="W40">
-        <v>0.228252962117366</v>
+        <v>0.2284464759092284</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.106686992969099</v>
+        <v>0.1039514290468144</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2360605972072399</v>
+        <v>0.2379605972072399</v>
       </c>
       <c r="C41">
-        <v>3.265414535052178</v>
+        <v>3.047262968045787</v>
       </c>
       <c r="D41">
-        <v>8.48455453505218</v>
+        <v>8.400662968045788</v>
       </c>
       <c r="E41">
-        <v>4.810140000000001</v>
+        <v>4.9444</v>
       </c>
       <c r="F41">
-        <v>5.236140000000001</v>
+        <v>5.3704</v>
       </c>
       <c r="G41">
         <v>0.017</v>
@@ -4649,37 +4649,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M41">
-        <v>1.234681812</v>
+        <v>1.26634032</v>
       </c>
       <c r="N41">
-        <v>-1.10633487322449</v>
+        <v>-1.13799338122449</v>
       </c>
       <c r="O41">
-        <v>-0.331900461967347</v>
+        <v>-0.3413980143673469</v>
       </c>
       <c r="P41">
-        <v>-0.7744344112571431</v>
+        <v>-0.7965953668571428</v>
       </c>
       <c r="Q41">
-        <v>-0.735434411257143</v>
+        <v>-0.7575953668571428</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2409286419715423</v>
+        <v>0.2441807860044014</v>
       </c>
       <c r="T41">
-        <v>1.671429746039174</v>
+        <v>1.699286908473161</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0311854287140443</v>
+        <v>0.0304057929961932</v>
       </c>
       <c r="W41">
-        <v>0.2284464759092284</v>
+        <v>0.2286303140114977</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1039514290468144</v>
+        <v>0.1013526433206441</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2379605972072399</v>
+        <v>0.2398605972072399</v>
       </c>
       <c r="C42">
-        <v>3.047262968045787</v>
+        <v>2.830754124803067</v>
       </c>
       <c r="D42">
-        <v>8.400662968045788</v>
+        <v>8.318414124803068</v>
       </c>
       <c r="E42">
-        <v>4.9444</v>
+        <v>5.07866</v>
       </c>
       <c r="F42">
-        <v>5.3704</v>
+        <v>5.50466</v>
       </c>
       <c r="G42">
         <v>0.017</v>
@@ -4731,37 +4731,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M42">
-        <v>1.26634032</v>
+        <v>1.297998828</v>
       </c>
       <c r="N42">
-        <v>-1.13799338122449</v>
+        <v>-1.16965188922449</v>
       </c>
       <c r="O42">
-        <v>-0.3413980143673469</v>
+        <v>-0.350895566767347</v>
       </c>
       <c r="P42">
-        <v>-0.7965953668571428</v>
+        <v>-0.8187563224571428</v>
       </c>
       <c r="Q42">
-        <v>-0.7575953668571428</v>
+        <v>-0.7797563224571428</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2441807860044014</v>
+        <v>0.2475431722078658</v>
       </c>
       <c r="T42">
-        <v>1.699286908473161</v>
+        <v>1.728088381498129</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0304057929961932</v>
+        <v>0.02966418828896897</v>
       </c>
       <c r="W42">
-        <v>0.2286303140114977</v>
+        <v>0.2288051844014611</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1013526433206441</v>
+        <v>0.09888062762989669</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2398605972072399</v>
+        <v>0.2417605972072399</v>
       </c>
       <c r="C43">
-        <v>2.830754124803067</v>
+        <v>2.615840222628995</v>
       </c>
       <c r="D43">
-        <v>8.318414124803068</v>
+        <v>8.237760222628996</v>
       </c>
       <c r="E43">
-        <v>5.07866</v>
+        <v>5.21292</v>
       </c>
       <c r="F43">
-        <v>5.50466</v>
+        <v>5.638920000000001</v>
       </c>
       <c r="G43">
         <v>0.017</v>
@@ -4813,37 +4813,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M43">
-        <v>1.297998828</v>
+        <v>1.329657336</v>
       </c>
       <c r="N43">
-        <v>-1.16965188922449</v>
+        <v>-1.20131039722449</v>
       </c>
       <c r="O43">
-        <v>-0.350895566767347</v>
+        <v>-0.360393119167347</v>
       </c>
       <c r="P43">
-        <v>-0.8187563224571428</v>
+        <v>-0.8409172780571429</v>
       </c>
       <c r="Q43">
-        <v>-0.7797563224571428</v>
+        <v>-0.8019172780571429</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2475431722078658</v>
+        <v>0.2510215027631738</v>
       </c>
       <c r="T43">
-        <v>1.728088381498129</v>
+        <v>1.757883008765338</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02966418828896897</v>
+        <v>0.02895789809161257</v>
       </c>
       <c r="W43">
-        <v>0.2288051844014611</v>
+        <v>0.2289717276299978</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.09888062762989669</v>
+        <v>0.096526326972042</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2417605972072399</v>
+        <v>0.2436605972072399</v>
       </c>
       <c r="C44">
-        <v>2.615840222628996</v>
+        <v>2.40247531420399</v>
       </c>
       <c r="D44">
-        <v>8.237760222628996</v>
+        <v>8.15865531420399</v>
       </c>
       <c r="E44">
-        <v>5.21292</v>
+        <v>5.34718</v>
       </c>
       <c r="F44">
-        <v>5.63892</v>
+        <v>5.77318</v>
       </c>
       <c r="G44">
         <v>0.017</v>
@@ -4895,37 +4895,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M44">
-        <v>1.329657336</v>
+        <v>1.361315844</v>
       </c>
       <c r="N44">
-        <v>-1.20131039722449</v>
+        <v>-1.23296890522449</v>
       </c>
       <c r="O44">
-        <v>-0.3603931191673469</v>
+        <v>-0.3698906715673469</v>
       </c>
       <c r="P44">
-        <v>-0.8409172780571428</v>
+        <v>-0.8630782336571428</v>
       </c>
       <c r="Q44">
-        <v>-0.8019172780571427</v>
+        <v>-0.8240782336571427</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2510215027631738</v>
+        <v>0.254621880004633</v>
       </c>
       <c r="T44">
-        <v>1.757883008765338</v>
+        <v>1.788723061550695</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02895789809161258</v>
+        <v>0.02828445860110996</v>
       </c>
       <c r="W44">
-        <v>0.2289717276299978</v>
+        <v>0.2291305246618583</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.096526326972042</v>
+        <v>0.09428152867036654</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2436605972072399</v>
+        <v>0.2455605972072399</v>
       </c>
       <c r="C45">
-        <v>2.40247531420399</v>
+        <v>2.190615200299116</v>
       </c>
       <c r="D45">
-        <v>8.15865531420399</v>
+        <v>8.081055200299117</v>
       </c>
       <c r="E45">
-        <v>5.34718</v>
+        <v>5.48144</v>
       </c>
       <c r="F45">
-        <v>5.77318</v>
+        <v>5.90744</v>
       </c>
       <c r="G45">
         <v>0.017</v>
@@ -4977,37 +4977,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M45">
-        <v>1.361315844</v>
+        <v>1.392974352</v>
       </c>
       <c r="N45">
-        <v>-1.23296890522449</v>
+        <v>-1.26462741322449</v>
       </c>
       <c r="O45">
-        <v>-0.3698906715673469</v>
+        <v>-0.3793882239673469</v>
       </c>
       <c r="P45">
-        <v>-0.8630782336571428</v>
+        <v>-0.885239189257143</v>
       </c>
       <c r="Q45">
-        <v>-0.8240782336571427</v>
+        <v>-0.8462391892571429</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.254621880004633</v>
+        <v>0.2583508421475729</v>
       </c>
       <c r="T45">
-        <v>1.788723061550695</v>
+        <v>1.820664544792672</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02828445860110996</v>
+        <v>0.02764162999653927</v>
       </c>
       <c r="W45">
-        <v>0.2291305246618583</v>
+        <v>0.229282103646816</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.09428152867036654</v>
+        <v>0.09213876665513099</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2455605972072399</v>
+        <v>0.2474605972072398</v>
       </c>
       <c r="C46">
-        <v>2.190615200299116</v>
+        <v>1.980217347425512</v>
       </c>
       <c r="D46">
-        <v>8.081055200299117</v>
+        <v>8.004917347425513</v>
       </c>
       <c r="E46">
-        <v>5.48144</v>
+        <v>5.6157</v>
       </c>
       <c r="F46">
-        <v>5.90744</v>
+        <v>6.041700000000001</v>
       </c>
       <c r="G46">
         <v>0.017</v>
@@ -5059,37 +5059,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M46">
-        <v>1.392974352</v>
+        <v>1.42463286</v>
       </c>
       <c r="N46">
-        <v>-1.26462741322449</v>
+        <v>-1.29628592122449</v>
       </c>
       <c r="O46">
-        <v>-0.3793882239673469</v>
+        <v>-0.3888857763673469</v>
       </c>
       <c r="P46">
-        <v>-0.885239189257143</v>
+        <v>-0.9074001448571429</v>
       </c>
       <c r="Q46">
-        <v>-0.8462391892571429</v>
+        <v>-0.8684001448571429</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2583508421475729</v>
+        <v>0.2622154029138923</v>
       </c>
       <c r="T46">
-        <v>1.820664544792672</v>
+        <v>1.853767536516175</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02764162999653927</v>
+        <v>0.02702737155217173</v>
       </c>
       <c r="W46">
-        <v>0.229282103646816</v>
+        <v>0.2294269457879979</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.09213876665513099</v>
+        <v>0.09009123850723921</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2474605972072398</v>
+        <v>0.2493605972072399</v>
       </c>
       <c r="C47">
-        <v>1.980217347425512</v>
+        <v>1.771240810095724</v>
       </c>
       <c r="D47">
-        <v>8.004917347425513</v>
+        <v>7.930200810095725</v>
       </c>
       <c r="E47">
-        <v>5.6157</v>
+        <v>5.749960000000001</v>
       </c>
       <c r="F47">
-        <v>6.041700000000001</v>
+        <v>6.175960000000001</v>
       </c>
       <c r="G47">
         <v>0.017</v>
@@ -5141,37 +5141,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M47">
-        <v>1.42463286</v>
+        <v>1.456291368</v>
       </c>
       <c r="N47">
-        <v>-1.29628592122449</v>
+        <v>-1.32794442922449</v>
       </c>
       <c r="O47">
-        <v>-0.3888857763673469</v>
+        <v>-0.398383328767347</v>
       </c>
       <c r="P47">
-        <v>-0.9074001448571429</v>
+        <v>-0.9295611004571429</v>
       </c>
       <c r="Q47">
-        <v>-0.8684001448571429</v>
+        <v>-0.8905611004571429</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2622154029138923</v>
+        <v>0.2662230955604459</v>
       </c>
       <c r="T47">
-        <v>1.853767536516175</v>
+        <v>1.888096564970178</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02702737155217173</v>
+        <v>0.02643981999668974</v>
       </c>
       <c r="W47">
-        <v>0.2294269457879979</v>
+        <v>0.2295654904447806</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.09009123850723921</v>
+        <v>0.08813273332229921</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2493605972072399</v>
+        <v>0.2512605972072399</v>
       </c>
       <c r="C48">
-        <v>1.771240810095724</v>
+        <v>1.56364615739838</v>
       </c>
       <c r="D48">
-        <v>7.930200810095725</v>
+        <v>7.85686615739838</v>
       </c>
       <c r="E48">
-        <v>5.749960000000001</v>
+        <v>5.88422</v>
       </c>
       <c r="F48">
-        <v>6.175960000000001</v>
+        <v>6.31022</v>
       </c>
       <c r="G48">
         <v>0.017</v>
@@ -5223,37 +5223,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M48">
-        <v>1.456291368</v>
+        <v>1.487949876</v>
       </c>
       <c r="N48">
-        <v>-1.32794442922449</v>
+        <v>-1.35960293722449</v>
       </c>
       <c r="O48">
-        <v>-0.398383328767347</v>
+        <v>-0.4078808811673469</v>
       </c>
       <c r="P48">
-        <v>-0.9295611004571429</v>
+        <v>-0.9517220560571429</v>
       </c>
       <c r="Q48">
-        <v>-0.8905611004571429</v>
+        <v>-0.9127220560571428</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2662230955604459</v>
+        <v>0.2703820218917751</v>
       </c>
       <c r="T48">
-        <v>1.888096564970178</v>
+        <v>1.923721028460182</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02643981999668974</v>
+        <v>0.02587727063505805</v>
       </c>
       <c r="W48">
-        <v>0.2295654904447806</v>
+        <v>0.2296981395842533</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.08813273332229921</v>
+        <v>0.08625756878352686</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2512605972072399</v>
+        <v>0.2531605972072399</v>
       </c>
       <c r="C49">
-        <v>1.56364615739838</v>
+        <v>1.357395403609522</v>
       </c>
       <c r="D49">
-        <v>7.85686615739838</v>
+        <v>7.784875403609522</v>
       </c>
       <c r="E49">
-        <v>5.88422</v>
+        <v>6.01848</v>
       </c>
       <c r="F49">
-        <v>6.31022</v>
+        <v>6.44448</v>
       </c>
       <c r="G49">
         <v>0.017</v>
@@ -5305,37 +5305,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M49">
-        <v>1.487949876</v>
+        <v>1.519608384</v>
       </c>
       <c r="N49">
-        <v>-1.35960293722449</v>
+        <v>-1.39126144522449</v>
       </c>
       <c r="O49">
-        <v>-0.4078808811673469</v>
+        <v>-0.4173784335673469</v>
       </c>
       <c r="P49">
-        <v>-0.9517220560571429</v>
+        <v>-0.9738830116571429</v>
       </c>
       <c r="Q49">
-        <v>-0.9127220560571428</v>
+        <v>-0.9348830116571428</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2703820218917751</v>
+        <v>0.2747009069281554</v>
       </c>
       <c r="T49">
-        <v>1.923721028460182</v>
+        <v>1.960715663622878</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02587727063505805</v>
+        <v>0.025338160830161</v>
       </c>
       <c r="W49">
-        <v>0.2296981395842533</v>
+        <v>0.229825261676248</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.08625756878352686</v>
+        <v>0.08446053610053672</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2531605972072399</v>
+        <v>0.2550605972072398</v>
       </c>
       <c r="C50">
-        <v>1.357395403609523</v>
+        <v>1.152451942584085</v>
       </c>
       <c r="D50">
-        <v>7.784875403609522</v>
+        <v>7.714191942584084</v>
       </c>
       <c r="E50">
-        <v>6.018479999999999</v>
+        <v>6.15274</v>
       </c>
       <c r="F50">
-        <v>6.44448</v>
+        <v>6.57874</v>
       </c>
       <c r="G50">
         <v>0.017</v>
@@ -5387,37 +5387,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M50">
-        <v>1.519608384</v>
+        <v>1.551266892</v>
       </c>
       <c r="N50">
-        <v>-1.39126144522449</v>
+        <v>-1.42291995322449</v>
       </c>
       <c r="O50">
-        <v>-0.4173784335673469</v>
+        <v>-0.4268759859673469</v>
       </c>
       <c r="P50">
-        <v>-0.9738830116571426</v>
+        <v>-0.9960439672571428</v>
       </c>
       <c r="Q50">
-        <v>-0.9348830116571426</v>
+        <v>-0.9570439672571428</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2747009069281554</v>
+        <v>0.279189160005178</v>
       </c>
       <c r="T50">
-        <v>1.960715663622877</v>
+        <v>1.999161068791953</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02533816083016101</v>
+        <v>0.02482105550709649</v>
       </c>
       <c r="W50">
-        <v>0.229825261676248</v>
+        <v>0.2299471951114267</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.08446053610053672</v>
+        <v>0.08273685169032174</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2550605972072398</v>
+        <v>0.2569605972072398</v>
       </c>
       <c r="C51">
-        <v>1.152451942584085</v>
+        <v>0.9487804856893822</v>
       </c>
       <c r="D51">
-        <v>7.714191942584084</v>
+        <v>7.644780485689382</v>
       </c>
       <c r="E51">
-        <v>6.15274</v>
+        <v>6.287</v>
       </c>
       <c r="F51">
-        <v>6.57874</v>
+        <v>6.713</v>
       </c>
       <c r="G51">
         <v>0.017</v>
@@ -5469,37 +5469,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M51">
-        <v>1.551266892</v>
+        <v>1.5829254</v>
       </c>
       <c r="N51">
-        <v>-1.42291995322449</v>
+        <v>-1.45457846122449</v>
       </c>
       <c r="O51">
-        <v>-0.4268759859673469</v>
+        <v>-0.4363735383673469</v>
       </c>
       <c r="P51">
-        <v>-0.9960439672571428</v>
+        <v>-1.018204922857143</v>
       </c>
       <c r="Q51">
-        <v>-0.9570439672571428</v>
+        <v>-0.979204922857143</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.279189160005178</v>
+        <v>0.2838569432052816</v>
       </c>
       <c r="T51">
-        <v>1.999161068791953</v>
+        <v>2.039144290167792</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02482105550709649</v>
+        <v>0.02432463439695456</v>
       </c>
       <c r="W51">
-        <v>0.2299471951114267</v>
+        <v>0.2300642512091981</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.08273685169032174</v>
+        <v>0.08108211465651527</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2569605972072398</v>
+        <v>0.2588605972072399</v>
       </c>
       <c r="C52">
-        <v>0.9487804856893822</v>
+        <v>0.7463470030595483</v>
       </c>
       <c r="D52">
-        <v>7.644780485689382</v>
+        <v>7.576607003059548</v>
       </c>
       <c r="E52">
-        <v>6.287</v>
+        <v>6.42126</v>
       </c>
       <c r="F52">
-        <v>6.713</v>
+        <v>6.84726</v>
       </c>
       <c r="G52">
         <v>0.017</v>
@@ -5551,37 +5551,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M52">
-        <v>1.5829254</v>
+        <v>1.614583908</v>
       </c>
       <c r="N52">
-        <v>-1.45457846122449</v>
+        <v>-1.48623696922449</v>
       </c>
       <c r="O52">
-        <v>-0.4363735383673469</v>
+        <v>-0.4458710907673469</v>
       </c>
       <c r="P52">
-        <v>-1.018204922857143</v>
+        <v>-1.040365878457143</v>
       </c>
       <c r="Q52">
-        <v>-0.979204922857143</v>
+        <v>-1.001365878457143</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2838569432052816</v>
+        <v>0.2887152481686547</v>
       </c>
       <c r="T52">
-        <v>2.039144290167792</v>
+        <v>2.080759479763054</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02432463439695456</v>
+        <v>0.023847680781328</v>
       </c>
       <c r="W52">
-        <v>0.2300642512091981</v>
+        <v>0.2301767168717629</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.08108211465651527</v>
+        <v>0.07949226927109343</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2588605972072399</v>
+        <v>0.2607605972072399</v>
       </c>
       <c r="C53">
-        <v>0.7463470030595483</v>
+        <v>0.5451186679653972</v>
       </c>
       <c r="D53">
-        <v>7.576607003059548</v>
+        <v>7.509638667965397</v>
       </c>
       <c r="E53">
-        <v>6.42126</v>
+        <v>6.55552</v>
       </c>
       <c r="F53">
-        <v>6.84726</v>
+        <v>6.981520000000001</v>
       </c>
       <c r="G53">
         <v>0.017</v>
@@ -5633,37 +5633,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M53">
-        <v>1.614583908</v>
+        <v>1.646242416</v>
       </c>
       <c r="N53">
-        <v>-1.48623696922449</v>
+        <v>-1.51789547722449</v>
       </c>
       <c r="O53">
-        <v>-0.4458710907673469</v>
+        <v>-0.4553686431673469</v>
       </c>
       <c r="P53">
-        <v>-1.040365878457143</v>
+        <v>-1.062526834057143</v>
       </c>
       <c r="Q53">
-        <v>-1.001365878457143</v>
+        <v>-1.023526834057143</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2887152481686547</v>
+        <v>0.2937759825055017</v>
       </c>
       <c r="T53">
-        <v>2.080759479763054</v>
+        <v>2.124108635591451</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.023847680781328</v>
+        <v>0.02338907153553323</v>
       </c>
       <c r="W53">
-        <v>0.2301767168717629</v>
+        <v>0.2302848569319213</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.07949226927109343</v>
+        <v>0.07796357178511082</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2607605972072399</v>
+        <v>0.2626605972072399</v>
       </c>
       <c r="C54">
-        <v>0.5451186679653972</v>
+        <v>0.3450638041086904</v>
       </c>
       <c r="D54">
-        <v>7.509638667965397</v>
+        <v>7.443843804108691</v>
       </c>
       <c r="E54">
-        <v>6.55552</v>
+        <v>6.689780000000001</v>
       </c>
       <c r="F54">
-        <v>6.981520000000001</v>
+        <v>7.115780000000001</v>
       </c>
       <c r="G54">
         <v>0.017</v>
@@ -5715,37 +5715,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M54">
-        <v>1.646242416</v>
+        <v>1.677900924</v>
       </c>
       <c r="N54">
-        <v>-1.51789547722449</v>
+        <v>-1.54955398522449</v>
       </c>
       <c r="O54">
-        <v>-0.4553686431673469</v>
+        <v>-0.464866195567347</v>
       </c>
       <c r="P54">
-        <v>-1.062526834057143</v>
+        <v>-1.084687789657143</v>
       </c>
       <c r="Q54">
-        <v>-1.023526834057143</v>
+        <v>-1.045687789657143</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2937759825055017</v>
+        <v>0.2990520672396613</v>
       </c>
       <c r="T54">
-        <v>2.124108635591451</v>
+        <v>2.169302436348715</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02338907153553323</v>
+        <v>0.02294776829901373</v>
       </c>
       <c r="W54">
-        <v>0.2302848569319213</v>
+        <v>0.2303889162350926</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.07796357178511082</v>
+        <v>0.07649256099671253</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2626605972072399</v>
+        <v>0.2645605972072399</v>
       </c>
       <c r="C55">
-        <v>0.3450638041086904</v>
+        <v>0.146151835662983</v>
       </c>
       <c r="D55">
-        <v>7.443843804108691</v>
+        <v>7.379191835662983</v>
       </c>
       <c r="E55">
-        <v>6.689780000000001</v>
+        <v>6.82404</v>
       </c>
       <c r="F55">
-        <v>7.115780000000001</v>
+        <v>7.25004</v>
       </c>
       <c r="G55">
         <v>0.017</v>
@@ -5797,37 +5797,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M55">
-        <v>1.677900924</v>
+        <v>1.709559432</v>
       </c>
       <c r="N55">
-        <v>-1.54955398522449</v>
+        <v>-1.58121249322449</v>
       </c>
       <c r="O55">
-        <v>-0.464866195567347</v>
+        <v>-0.4743637479673469</v>
       </c>
       <c r="P55">
-        <v>-1.084687789657143</v>
+        <v>-1.106848745257143</v>
       </c>
       <c r="Q55">
-        <v>-1.045687789657143</v>
+        <v>-1.067848745257143</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2990520672396613</v>
+        <v>0.3045575469622627</v>
       </c>
       <c r="T55">
-        <v>2.169302436348715</v>
+        <v>2.216461184964992</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02294776829901373</v>
+        <v>0.02252280962680978</v>
       </c>
       <c r="W55">
-        <v>0.2303889162350926</v>
+        <v>0.2304891214899983</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.07649256099671253</v>
+        <v>0.07507603208936597</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2645605972072399</v>
+        <v>0.2664605972072399</v>
       </c>
       <c r="C56">
-        <v>0.146151835662983</v>
+        <v>-0.05164676010448943</v>
       </c>
       <c r="D56">
-        <v>7.379191835662983</v>
+        <v>7.315653239895511</v>
       </c>
       <c r="E56">
-        <v>6.82404</v>
+        <v>6.9583</v>
       </c>
       <c r="F56">
-        <v>7.25004</v>
+        <v>7.384300000000001</v>
       </c>
       <c r="G56">
         <v>0.017</v>
@@ -5879,37 +5879,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M56">
-        <v>1.709559432</v>
+        <v>1.74121794</v>
       </c>
       <c r="N56">
-        <v>-1.58121249322449</v>
+        <v>-1.61287100122449</v>
       </c>
       <c r="O56">
-        <v>-0.4743637479673469</v>
+        <v>-0.483861300367347</v>
       </c>
       <c r="P56">
-        <v>-1.106848745257143</v>
+        <v>-1.129009700857143</v>
       </c>
       <c r="Q56">
-        <v>-1.067848745257143</v>
+        <v>-1.090009700857143</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3045575469622627</v>
+        <v>0.3103077146725352</v>
       </c>
       <c r="T56">
-        <v>2.216461184964992</v>
+        <v>2.265715877964214</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02252280962680978</v>
+        <v>0.02211330399723142</v>
       </c>
       <c r="W56">
-        <v>0.2304891214899983</v>
+        <v>0.2305856829174528</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.07507603208936597</v>
+        <v>0.07371101332410479</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2664605972072399</v>
+        <v>0.2683605972072399</v>
       </c>
       <c r="C57">
-        <v>-0.05164676010448943</v>
+        <v>-0.2483604977841116</v>
       </c>
       <c r="D57">
-        <v>7.315653239895511</v>
+        <v>7.253199502215889</v>
       </c>
       <c r="E57">
-        <v>6.9583</v>
+        <v>7.092560000000001</v>
       </c>
       <c r="F57">
-        <v>7.384300000000001</v>
+        <v>7.518560000000001</v>
       </c>
       <c r="G57">
         <v>0.017</v>
@@ -5961,37 +5961,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M57">
-        <v>1.74121794</v>
+        <v>1.772876448</v>
       </c>
       <c r="N57">
-        <v>-1.61287100122449</v>
+        <v>-1.64452950922449</v>
       </c>
       <c r="O57">
-        <v>-0.483861300367347</v>
+        <v>-0.493358852767347</v>
       </c>
       <c r="P57">
-        <v>-1.129009700857143</v>
+        <v>-1.151170656457143</v>
       </c>
       <c r="Q57">
-        <v>-1.090009700857143</v>
+        <v>-1.112170656457143</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3103077146725352</v>
+        <v>0.3163192536423655</v>
       </c>
       <c r="T57">
-        <v>2.265715877964214</v>
+        <v>2.317209420645219</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02211330399723142</v>
+        <v>0.02171842356870943</v>
       </c>
       <c r="W57">
-        <v>0.2305856829174528</v>
+        <v>0.2306787957224983</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.07371101332410479</v>
+        <v>0.07239474522903144</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2683605972072399</v>
+        <v>0.2702605972072399</v>
       </c>
       <c r="C58">
-        <v>-0.2483604977841116</v>
+        <v>-0.4440169264922051</v>
       </c>
       <c r="D58">
-        <v>7.253199502215889</v>
+        <v>7.191803073507796</v>
       </c>
       <c r="E58">
-        <v>7.092560000000001</v>
+        <v>7.226820000000001</v>
       </c>
       <c r="F58">
-        <v>7.518560000000001</v>
+        <v>7.652820000000001</v>
       </c>
       <c r="G58">
         <v>0.017</v>
@@ -6043,37 +6043,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M58">
-        <v>1.772876448</v>
+        <v>1.804534956</v>
       </c>
       <c r="N58">
-        <v>-1.64452950922449</v>
+        <v>-1.67618801722449</v>
       </c>
       <c r="O58">
-        <v>-0.493358852767347</v>
+        <v>-0.502856405167347</v>
       </c>
       <c r="P58">
-        <v>-1.151170656457143</v>
+        <v>-1.173331612057143</v>
       </c>
       <c r="Q58">
-        <v>-1.112170656457143</v>
+        <v>-1.134331612057143</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3163192536423655</v>
+        <v>0.3226103990759089</v>
       </c>
       <c r="T58">
-        <v>2.317209420645219</v>
+        <v>2.371098011823015</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02171842356870943</v>
+        <v>0.02133739859381979</v>
       </c>
       <c r="W58">
-        <v>0.2306787957224983</v>
+        <v>0.2307686414115773</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.07239474522903144</v>
+        <v>0.07112466197939937</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2702605972072399</v>
+        <v>0.2721605972072398</v>
       </c>
       <c r="C59">
-        <v>-0.4440169264922051</v>
+        <v>-0.6386426703904435</v>
       </c>
       <c r="D59">
-        <v>7.191803073507796</v>
+        <v>7.131437329609557</v>
       </c>
       <c r="E59">
-        <v>7.226820000000001</v>
+        <v>7.361080000000001</v>
       </c>
       <c r="F59">
-        <v>7.652820000000001</v>
+        <v>7.787080000000001</v>
       </c>
       <c r="G59">
         <v>0.017</v>
@@ -6125,37 +6125,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M59">
-        <v>1.804534956</v>
+        <v>1.836193464</v>
       </c>
       <c r="N59">
-        <v>-1.67618801722449</v>
+        <v>-1.70784652522449</v>
       </c>
       <c r="O59">
-        <v>-0.502856405167347</v>
+        <v>-0.512353957567347</v>
       </c>
       <c r="P59">
-        <v>-1.173331612057143</v>
+        <v>-1.195492567657143</v>
       </c>
       <c r="Q59">
-        <v>-1.134331612057143</v>
+        <v>-1.156492567657143</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3226103990759089</v>
+        <v>0.3292011228634305</v>
       </c>
       <c r="T59">
-        <v>2.371098011823015</v>
+        <v>2.427552726390229</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02133739859381979</v>
+        <v>0.02096951241116772</v>
       </c>
       <c r="W59">
-        <v>0.2307686414115773</v>
+        <v>0.2308553889734467</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.07112466197939937</v>
+        <v>0.06989837470389249</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2721605972072398</v>
+        <v>0.2740605972072399</v>
       </c>
       <c r="C60">
-        <v>-0.6386426703904418</v>
+        <v>-0.8322634671816473</v>
       </c>
       <c r="D60">
-        <v>7.131437329609557</v>
+        <v>7.072076532818352</v>
       </c>
       <c r="E60">
-        <v>7.361079999999999</v>
+        <v>7.49534</v>
       </c>
       <c r="F60">
-        <v>7.78708</v>
+        <v>7.92134</v>
       </c>
       <c r="G60">
         <v>0.017</v>
@@ -6207,37 +6207,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M60">
-        <v>1.836193464</v>
+        <v>1.867851972</v>
       </c>
       <c r="N60">
-        <v>-1.70784652522449</v>
+        <v>-1.73950503322449</v>
       </c>
       <c r="O60">
-        <v>-0.5123539575673469</v>
+        <v>-0.5218515099673469</v>
       </c>
       <c r="P60">
-        <v>-1.195492567657143</v>
+        <v>-1.217653523257143</v>
       </c>
       <c r="Q60">
-        <v>-1.156492567657143</v>
+        <v>-1.178653523257143</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3292011228634305</v>
+        <v>0.3361133453722946</v>
       </c>
       <c r="T60">
-        <v>2.427552726390229</v>
+        <v>2.486761329472917</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02096951241116773</v>
+        <v>0.02061409694657166</v>
       </c>
       <c r="W60">
-        <v>0.2308553889734467</v>
+        <v>0.2309391959399984</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.06989837470389249</v>
+        <v>0.06871365648857231</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2740605972072399</v>
+        <v>0.2759605972072399</v>
       </c>
       <c r="C61">
-        <v>-0.8322634671816473</v>
+        <v>-1.024904204698835</v>
       </c>
       <c r="D61">
-        <v>7.072076532818352</v>
+        <v>7.013695795301165</v>
       </c>
       <c r="E61">
-        <v>7.49534</v>
+        <v>7.6296</v>
       </c>
       <c r="F61">
-        <v>7.92134</v>
+        <v>8.0556</v>
       </c>
       <c r="G61">
         <v>0.017</v>
@@ -6289,37 +6289,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M61">
-        <v>1.867851972</v>
+        <v>1.89951048</v>
       </c>
       <c r="N61">
-        <v>-1.73950503322449</v>
+        <v>-1.77116354122449</v>
       </c>
       <c r="O61">
-        <v>-0.5218515099673469</v>
+        <v>-0.5313490623673469</v>
       </c>
       <c r="P61">
-        <v>-1.217653523257143</v>
+        <v>-1.239814478857143</v>
       </c>
       <c r="Q61">
-        <v>-1.178653523257143</v>
+        <v>-1.200814478857143</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3361133453722946</v>
+        <v>0.343371179006602</v>
       </c>
       <c r="T61">
-        <v>2.486761329472917</v>
+        <v>2.54893036270974</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02061409694657166</v>
+        <v>0.0202705286641288</v>
       </c>
       <c r="W61">
-        <v>0.2309391959399984</v>
+        <v>0.2310202093409984</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.06871365648857231</v>
+        <v>0.06756842888042935</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2759605972072399</v>
+        <v>0.2778605972072399</v>
       </c>
       <c r="C62">
-        <v>-1.024904204698835</v>
+        <v>-1.216588955696832</v>
       </c>
       <c r="D62">
-        <v>7.013695795301165</v>
+        <v>6.956271044303167</v>
       </c>
       <c r="E62">
-        <v>7.6296</v>
+        <v>7.763859999999999</v>
       </c>
       <c r="F62">
-        <v>8.0556</v>
+        <v>8.189859999999999</v>
       </c>
       <c r="G62">
         <v>0.017</v>
@@ -6371,37 +6371,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M62">
-        <v>1.89951048</v>
+        <v>1.931168988</v>
       </c>
       <c r="N62">
-        <v>-1.77116354122449</v>
+        <v>-1.80282204922449</v>
       </c>
       <c r="O62">
-        <v>-0.5313490623673469</v>
+        <v>-0.5408466147673469</v>
       </c>
       <c r="P62">
-        <v>-1.239814478857143</v>
+        <v>-1.261975434457143</v>
       </c>
       <c r="Q62">
-        <v>-1.200814478857143</v>
+        <v>-1.222975434457143</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.343371179006602</v>
+        <v>0.3510012092375405</v>
       </c>
       <c r="T62">
-        <v>2.54893036270974</v>
+        <v>2.61428755149717</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0202705286641288</v>
+        <v>0.01993822491553653</v>
       </c>
       <c r="W62">
-        <v>0.2310202093409984</v>
+        <v>0.2310985665649165</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.06756842888042935</v>
+        <v>0.06646074971845517</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2778605972072399</v>
+        <v>0.2797605972072399</v>
       </c>
       <c r="C63">
-        <v>-1.216588955696832</v>
+        <v>-1.407341010948636</v>
       </c>
       <c r="D63">
-        <v>6.956271044303167</v>
+        <v>6.899778989051364</v>
       </c>
       <c r="E63">
-        <v>7.763859999999999</v>
+        <v>7.89812</v>
       </c>
       <c r="F63">
-        <v>8.189859999999999</v>
+        <v>8.324120000000001</v>
       </c>
       <c r="G63">
         <v>0.017</v>
@@ -6453,37 +6453,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M63">
-        <v>1.931168988</v>
+        <v>1.962827496</v>
       </c>
       <c r="N63">
-        <v>-1.80282204922449</v>
+        <v>-1.83448055722449</v>
       </c>
       <c r="O63">
-        <v>-0.5408466147673469</v>
+        <v>-0.550344167167347</v>
       </c>
       <c r="P63">
-        <v>-1.261975434457143</v>
+        <v>-1.284136390057143</v>
       </c>
       <c r="Q63">
-        <v>-1.222975434457143</v>
+        <v>-1.245136390057143</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3510012092375405</v>
+        <v>0.3590328200069495</v>
       </c>
       <c r="T63">
-        <v>2.61428755149717</v>
+        <v>2.683084592326042</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01993822491553653</v>
+        <v>0.01961664064270529</v>
       </c>
       <c r="W63">
-        <v>0.2310985665649165</v>
+        <v>0.2311743961364501</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.06646074971845517</v>
+        <v>0.06538880214235099</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2797605972072399</v>
+        <v>0.2816605972072398</v>
       </c>
       <c r="C64">
-        <v>-1.407341010948636</v>
+        <v>-1.597182910742092</v>
       </c>
       <c r="D64">
-        <v>6.899778989051364</v>
+        <v>6.844197089257908</v>
       </c>
       <c r="E64">
-        <v>7.89812</v>
+        <v>8.03238</v>
       </c>
       <c r="F64">
-        <v>8.324120000000001</v>
+        <v>8.45838</v>
       </c>
       <c r="G64">
         <v>0.017</v>
@@ -6535,37 +6535,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M64">
-        <v>1.962827496</v>
+        <v>1.994486004</v>
       </c>
       <c r="N64">
-        <v>-1.83448055722449</v>
+        <v>-1.86613906522449</v>
       </c>
       <c r="O64">
-        <v>-0.550344167167347</v>
+        <v>-0.559841719567347</v>
       </c>
       <c r="P64">
-        <v>-1.284136390057143</v>
+        <v>-1.306297345657143</v>
       </c>
       <c r="Q64">
-        <v>-1.245136390057143</v>
+        <v>-1.267297345657143</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3590328200069495</v>
+        <v>0.3674985718990292</v>
       </c>
       <c r="T64">
-        <v>2.683084592326042</v>
+        <v>2.755600392118638</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01961664064270529</v>
+        <v>0.01930526539440838</v>
       </c>
       <c r="W64">
-        <v>0.2311743961364501</v>
+        <v>0.2312478184199985</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.06538880214235099</v>
+        <v>0.06435088464802796</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2816605972072398</v>
+        <v>0.2835605972072399</v>
       </c>
       <c r="C65">
-        <v>-1.597182910742092</v>
+        <v>-1.786136474866408</v>
       </c>
       <c r="D65">
-        <v>6.844197089257908</v>
+        <v>6.789503525133592</v>
       </c>
       <c r="E65">
-        <v>8.03238</v>
+        <v>8.166640000000001</v>
       </c>
       <c r="F65">
-        <v>8.45838</v>
+        <v>8.592640000000001</v>
       </c>
       <c r="G65">
         <v>0.017</v>
@@ -6617,37 +6617,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M65">
-        <v>1.994486004</v>
+        <v>2.026144512000001</v>
       </c>
       <c r="N65">
-        <v>-1.86613906522449</v>
+        <v>-1.89779757322449</v>
       </c>
       <c r="O65">
-        <v>-0.559841719567347</v>
+        <v>-0.569339271967347</v>
       </c>
       <c r="P65">
-        <v>-1.306297345657143</v>
+        <v>-1.328458301257143</v>
       </c>
       <c r="Q65">
-        <v>-1.267297345657143</v>
+        <v>-1.289458301257143</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3674985718990292</v>
+        <v>0.3764346433406689</v>
       </c>
       <c r="T65">
-        <v>2.755600392118638</v>
+        <v>2.832144847455267</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01930526539440838</v>
+        <v>0.01900362062262075</v>
       </c>
       <c r="W65">
-        <v>0.2312478184199985</v>
+        <v>0.231318946257186</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.06435088464802796</v>
+        <v>0.06334540207540251</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2835605972072399</v>
+        <v>0.2854605972072399</v>
       </c>
       <c r="C66">
-        <v>-1.786136474866408</v>
+        <v>-1.974222831172276</v>
       </c>
       <c r="D66">
-        <v>6.789503525133592</v>
+        <v>6.735677168827724</v>
       </c>
       <c r="E66">
-        <v>8.166640000000001</v>
+        <v>8.3009</v>
       </c>
       <c r="F66">
-        <v>8.592640000000001</v>
+        <v>8.726900000000001</v>
       </c>
       <c r="G66">
         <v>0.017</v>
@@ -6699,37 +6699,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M66">
-        <v>2.026144512000001</v>
+        <v>2.05780302</v>
       </c>
       <c r="N66">
-        <v>-1.89779757322449</v>
+        <v>-1.92945608122449</v>
       </c>
       <c r="O66">
-        <v>-0.569339271967347</v>
+        <v>-0.578836824367347</v>
       </c>
       <c r="P66">
-        <v>-1.328458301257143</v>
+        <v>-1.350619256857143</v>
       </c>
       <c r="Q66">
-        <v>-1.289458301257143</v>
+        <v>-1.311619256857143</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3764346433406689</v>
+        <v>0.3858813474361166</v>
       </c>
       <c r="T66">
-        <v>2.832144847455267</v>
+        <v>2.913063271668275</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01900362062262075</v>
+        <v>0.01871125722842659</v>
       </c>
       <c r="W66">
-        <v>0.231318946257186</v>
+        <v>0.231387885545537</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.06334540207540251</v>
+        <v>0.06237085742808868</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2854605972072399</v>
+        <v>0.2873605972072398</v>
       </c>
       <c r="C67">
-        <v>-1.974222831172276</v>
+        <v>-2.161462442784152</v>
       </c>
       <c r="D67">
-        <v>6.735677168827724</v>
+        <v>6.682697557215848</v>
       </c>
       <c r="E67">
-        <v>8.3009</v>
+        <v>8.43516</v>
       </c>
       <c r="F67">
-        <v>8.726900000000001</v>
+        <v>8.86116</v>
       </c>
       <c r="G67">
         <v>0.017</v>
@@ -6781,37 +6781,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M67">
-        <v>2.05780302</v>
+        <v>2.089461528</v>
       </c>
       <c r="N67">
-        <v>-1.92945608122449</v>
+        <v>-1.96111458922449</v>
       </c>
       <c r="O67">
-        <v>-0.578836824367347</v>
+        <v>-0.5883343767673469</v>
       </c>
       <c r="P67">
-        <v>-1.350619256857143</v>
+        <v>-1.372780212457143</v>
       </c>
       <c r="Q67">
-        <v>-1.311619256857143</v>
+        <v>-1.333780212457143</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3858813474361166</v>
+        <v>0.3958837400077671</v>
       </c>
       <c r="T67">
-        <v>2.913063271668275</v>
+        <v>2.99874160318793</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01871125722842659</v>
+        <v>0.01842775333102618</v>
       </c>
       <c r="W67">
-        <v>0.231387885545537</v>
+        <v>0.231454735764544</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.06237085742808868</v>
+        <v>0.06142584443675403</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2873605972072398</v>
+        <v>0.2892605972072399</v>
       </c>
       <c r="C68">
-        <v>-2.161462442784152</v>
+        <v>-2.347875134038346</v>
       </c>
       <c r="D68">
-        <v>6.682697557215848</v>
+        <v>6.630544865961655</v>
       </c>
       <c r="E68">
-        <v>8.43516</v>
+        <v>8.569420000000001</v>
       </c>
       <c r="F68">
-        <v>8.86116</v>
+        <v>8.995420000000001</v>
       </c>
       <c r="G68">
         <v>0.017</v>
@@ -6863,37 +6863,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M68">
-        <v>2.089461528</v>
+        <v>2.121120036</v>
       </c>
       <c r="N68">
-        <v>-1.96111458922449</v>
+        <v>-1.99277309722449</v>
       </c>
       <c r="O68">
-        <v>-0.5883343767673469</v>
+        <v>-0.597831929167347</v>
       </c>
       <c r="P68">
-        <v>-1.372780212457143</v>
+        <v>-1.394941168057143</v>
       </c>
       <c r="Q68">
-        <v>-1.333780212457143</v>
+        <v>-1.355941168057143</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3958837400077671</v>
+        <v>0.4064923381898207</v>
       </c>
       <c r="T68">
-        <v>2.99874160318793</v>
+        <v>3.089612560860292</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01842775333102618</v>
+        <v>0.01815271223653326</v>
       </c>
       <c r="W68">
-        <v>0.231454735764544</v>
+        <v>0.2315195904546255</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.06142584443675403</v>
+        <v>0.06050904078844421</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2892605972072399</v>
+        <v>0.2911605972072399</v>
       </c>
       <c r="C69">
-        <v>-2.347875134038346</v>
+        <v>-2.533480115215931</v>
       </c>
       <c r="D69">
-        <v>6.630544865961655</v>
+        <v>6.579199884784069</v>
       </c>
       <c r="E69">
-        <v>8.569420000000001</v>
+        <v>8.70368</v>
       </c>
       <c r="F69">
-        <v>8.995420000000001</v>
+        <v>9.12968</v>
       </c>
       <c r="G69">
         <v>0.017</v>
@@ -6945,37 +6945,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M69">
-        <v>2.121120036</v>
+        <v>2.152778544</v>
       </c>
       <c r="N69">
-        <v>-1.99277309722449</v>
+        <v>-2.02443160522449</v>
       </c>
       <c r="O69">
-        <v>-0.597831929167347</v>
+        <v>-0.607329481567347</v>
       </c>
       <c r="P69">
-        <v>-1.394941168057143</v>
+        <v>-1.417102123657143</v>
       </c>
       <c r="Q69">
-        <v>-1.355941168057143</v>
+        <v>-1.378102123657143</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4064923381898207</v>
+        <v>0.4177639737582526</v>
       </c>
       <c r="T69">
-        <v>3.089612560860292</v>
+        <v>3.186162953387176</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01815271223653326</v>
+        <v>0.017885760585996</v>
       </c>
       <c r="W69">
-        <v>0.2315195904546255</v>
+        <v>0.2315825376538221</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.06050904078844421</v>
+        <v>0.05961920195332004</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2911605972072399</v>
+        <v>0.2930605972072399</v>
       </c>
       <c r="C70">
-        <v>-2.533480115215931</v>
+        <v>-2.718296006135391</v>
       </c>
       <c r="D70">
-        <v>6.579199884784069</v>
+        <v>6.52864399386461</v>
       </c>
       <c r="E70">
-        <v>8.70368</v>
+        <v>8.837940000000001</v>
       </c>
       <c r="F70">
-        <v>9.12968</v>
+        <v>9.263940000000002</v>
       </c>
       <c r="G70">
         <v>0.017</v>
@@ -7027,37 +7027,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M70">
-        <v>2.152778544</v>
+        <v>2.184437052</v>
       </c>
       <c r="N70">
-        <v>-2.02443160522449</v>
+        <v>-2.05609011322449</v>
       </c>
       <c r="O70">
-        <v>-0.607329481567347</v>
+        <v>-0.6168270339673469</v>
       </c>
       <c r="P70">
-        <v>-1.417102123657143</v>
+        <v>-1.439263079257143</v>
       </c>
       <c r="Q70">
-        <v>-1.378102123657143</v>
+        <v>-1.400263079257143</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4177639737582526</v>
+        <v>0.429762811621422</v>
       </c>
       <c r="T70">
-        <v>3.186162953387176</v>
+        <v>3.28894240349644</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.017885760585996</v>
+        <v>0.01762654666445982</v>
       </c>
       <c r="W70">
-        <v>0.2315825376538221</v>
+        <v>0.2316436602965204</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.05961920195332004</v>
+        <v>0.05875515554819943</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2930605972072399</v>
+        <v>0.2949605972072399</v>
       </c>
       <c r="C71">
-        <v>-2.718296006135391</v>
+        <v>-2.902340858665767</v>
       </c>
       <c r="D71">
-        <v>6.52864399386461</v>
+        <v>6.478859141334234</v>
       </c>
       <c r="E71">
-        <v>8.837940000000001</v>
+        <v>8.972200000000001</v>
       </c>
       <c r="F71">
-        <v>9.263940000000002</v>
+        <v>9.398200000000001</v>
       </c>
       <c r="G71">
         <v>0.017</v>
@@ -7109,37 +7109,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M71">
-        <v>2.184437052</v>
+        <v>2.21609556</v>
       </c>
       <c r="N71">
-        <v>-2.05609011322449</v>
+        <v>-2.08774862122449</v>
       </c>
       <c r="O71">
-        <v>-0.6168270339673469</v>
+        <v>-0.626324586367347</v>
       </c>
       <c r="P71">
-        <v>-1.439263079257143</v>
+        <v>-1.461424034857143</v>
       </c>
       <c r="Q71">
-        <v>-1.400263079257143</v>
+        <v>-1.422424034857143</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.429762811621422</v>
+        <v>0.4425615720088028</v>
       </c>
       <c r="T71">
-        <v>3.28894240349644</v>
+        <v>3.398573816946322</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01762654666445982</v>
+        <v>0.01737473885496754</v>
       </c>
       <c r="W71">
-        <v>0.2316436602965204</v>
+        <v>0.2317030365779987</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.05875515554819943</v>
+        <v>0.05791579618322518</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2949605972072399</v>
+        <v>0.2968605972072399</v>
       </c>
       <c r="C72">
-        <v>-2.902340858665767</v>
+        <v>-3.085632178217571</v>
       </c>
       <c r="D72">
-        <v>6.478859141334234</v>
+        <v>6.429827821782429</v>
       </c>
       <c r="E72">
-        <v>8.972200000000001</v>
+        <v>9.10646</v>
       </c>
       <c r="F72">
-        <v>9.398200000000001</v>
+        <v>9.53246</v>
       </c>
       <c r="G72">
         <v>0.017</v>
@@ -7191,37 +7191,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M72">
-        <v>2.21609556</v>
+        <v>2.247754068</v>
       </c>
       <c r="N72">
-        <v>-2.08774862122449</v>
+        <v>-2.11940712922449</v>
       </c>
       <c r="O72">
-        <v>-0.626324586367347</v>
+        <v>-0.6358221387673469</v>
       </c>
       <c r="P72">
-        <v>-1.461424034857143</v>
+        <v>-1.483584990457143</v>
       </c>
       <c r="Q72">
-        <v>-1.422424034857143</v>
+        <v>-1.444584990457143</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4425615720088028</v>
+        <v>0.4562430055263477</v>
       </c>
       <c r="T72">
-        <v>3.398573816946322</v>
+        <v>3.515766017530678</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01737473885496754</v>
+        <v>0.01713002422320744</v>
       </c>
       <c r="W72">
-        <v>0.2317030365779987</v>
+        <v>0.2317607402881677</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.05791579618322518</v>
+        <v>0.05710008074402484</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2968605972072399</v>
+        <v>0.2987605972072399</v>
       </c>
       <c r="C73">
-        <v>-3.085632178217571</v>
+        <v>-3.268186944265177</v>
       </c>
       <c r="D73">
-        <v>6.429827821782429</v>
+        <v>6.381533055734822</v>
       </c>
       <c r="E73">
-        <v>9.10646</v>
+        <v>9.24072</v>
       </c>
       <c r="F73">
-        <v>9.53246</v>
+        <v>9.66672</v>
       </c>
       <c r="G73">
         <v>0.017</v>
@@ -7273,37 +7273,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M73">
-        <v>2.247754068</v>
+        <v>2.279412576</v>
       </c>
       <c r="N73">
-        <v>-2.11940712922449</v>
+        <v>-2.15106563722449</v>
       </c>
       <c r="O73">
-        <v>-0.6358221387673469</v>
+        <v>-0.6453196911673469</v>
       </c>
       <c r="P73">
-        <v>-1.483584990457143</v>
+        <v>-1.505745946057143</v>
       </c>
       <c r="Q73">
-        <v>-1.444584990457143</v>
+        <v>-1.466745946057143</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4562430055263476</v>
+        <v>0.4709016842951457</v>
       </c>
       <c r="T73">
-        <v>3.515766017530676</v>
+        <v>3.641329089585343</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01713002422320744</v>
+        <v>0.01689210722010734</v>
       </c>
       <c r="W73">
-        <v>0.2317607402881677</v>
+        <v>0.2318168411174987</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.05710008074402484</v>
+        <v>0.05630702406702448</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2987605972072399</v>
+        <v>0.3006605972072399</v>
       </c>
       <c r="C74">
-        <v>-3.268186944265177</v>
+        <v>-3.450021629951237</v>
       </c>
       <c r="D74">
-        <v>6.381533055734822</v>
+        <v>6.333958370048761</v>
       </c>
       <c r="E74">
-        <v>9.24072</v>
+        <v>9.374979999999999</v>
       </c>
       <c r="F74">
-        <v>9.66672</v>
+        <v>9.800979999999999</v>
       </c>
       <c r="G74">
         <v>0.017</v>
@@ -7355,37 +7355,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M74">
-        <v>2.279412576</v>
+        <v>2.311071084</v>
       </c>
       <c r="N74">
-        <v>-2.15106563722449</v>
+        <v>-2.18272414522449</v>
       </c>
       <c r="O74">
-        <v>-0.6453196911673469</v>
+        <v>-0.6548172435673468</v>
       </c>
       <c r="P74">
-        <v>-1.505745946057143</v>
+        <v>-1.527906901657143</v>
       </c>
       <c r="Q74">
-        <v>-1.466745946057143</v>
+        <v>-1.488906901657143</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4709016842951457</v>
+        <v>0.4866461911208919</v>
       </c>
       <c r="T74">
-        <v>3.641329089585343</v>
+        <v>3.776193129940356</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01689210722010734</v>
+        <v>0.01666070849106477</v>
       </c>
       <c r="W74">
-        <v>0.2318168411174987</v>
+        <v>0.2318714049378069</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.05630702406702448</v>
+        <v>0.05553569497021593</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3006605972072399</v>
+        <v>0.3025605972072398</v>
       </c>
       <c r="C75">
-        <v>-3.450021629951237</v>
+        <v>-3.631152220820672</v>
       </c>
       <c r="D75">
-        <v>6.333958370048761</v>
+        <v>6.287087779179328</v>
       </c>
       <c r="E75">
-        <v>9.374979999999999</v>
+        <v>9.50924</v>
       </c>
       <c r="F75">
-        <v>9.800979999999999</v>
+        <v>9.93524</v>
       </c>
       <c r="G75">
         <v>0.017</v>
@@ -7437,37 +7437,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M75">
-        <v>2.311071084</v>
+        <v>2.342729592</v>
       </c>
       <c r="N75">
-        <v>-2.18272414522449</v>
+        <v>-2.21438265322449</v>
       </c>
       <c r="O75">
-        <v>-0.6548172435673468</v>
+        <v>-0.6643147959673469</v>
       </c>
       <c r="P75">
-        <v>-1.527906901657143</v>
+        <v>-1.550067857257143</v>
       </c>
       <c r="Q75">
-        <v>-1.488906901657143</v>
+        <v>-1.511067857257143</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4866461911208919</v>
+        <v>0.5036018138563108</v>
       </c>
       <c r="T75">
-        <v>3.776193129940356</v>
+        <v>3.921431327245755</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01666070849106477</v>
+        <v>0.01643556378172606</v>
       </c>
       <c r="W75">
-        <v>0.2318714049378069</v>
+        <v>0.231924494060269</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.05553569497021593</v>
+        <v>0.05478521260575353</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3025605972072398</v>
+        <v>0.3044605972072398</v>
       </c>
       <c r="C76">
-        <v>-3.631152220820672</v>
+        <v>-3.811594232729004</v>
       </c>
       <c r="D76">
-        <v>6.287087779179328</v>
+        <v>6.240905767270995</v>
       </c>
       <c r="E76">
-        <v>9.50924</v>
+        <v>9.6435</v>
       </c>
       <c r="F76">
-        <v>9.93524</v>
+        <v>10.0695</v>
       </c>
       <c r="G76">
         <v>0.017</v>
@@ -7519,37 +7519,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M76">
-        <v>2.342729592</v>
+        <v>2.3743881</v>
       </c>
       <c r="N76">
-        <v>-2.21438265322449</v>
+        <v>-2.24604116122449</v>
       </c>
       <c r="O76">
-        <v>-0.6643147959673469</v>
+        <v>-0.6738123483673469</v>
       </c>
       <c r="P76">
-        <v>-1.550067857257143</v>
+        <v>-1.572228812857143</v>
       </c>
       <c r="Q76">
-        <v>-1.511067857257143</v>
+        <v>-1.533228812857143</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5036018138563108</v>
+        <v>0.5219138864105631</v>
       </c>
       <c r="T76">
-        <v>3.921431327245755</v>
+        <v>4.078288580335585</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01643556378172606</v>
+        <v>0.01621642293130304</v>
       </c>
       <c r="W76">
-        <v>0.231924494060269</v>
+        <v>0.2319761674727987</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.05478521260575353</v>
+        <v>0.05405474310434355</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3044605972072398</v>
+        <v>0.3063605972072399</v>
       </c>
       <c r="C77">
-        <v>-3.811594232729004</v>
+        <v>-3.991362728967154</v>
       </c>
       <c r="D77">
-        <v>6.240905767270995</v>
+        <v>6.195397271032847</v>
       </c>
       <c r="E77">
-        <v>9.6435</v>
+        <v>9.777760000000001</v>
       </c>
       <c r="F77">
-        <v>10.0695</v>
+        <v>10.20376</v>
       </c>
       <c r="G77">
         <v>0.017</v>
@@ -7601,37 +7601,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M77">
-        <v>2.3743881</v>
+        <v>2.406046608</v>
       </c>
       <c r="N77">
-        <v>-2.24604116122449</v>
+        <v>-2.27769966922449</v>
       </c>
       <c r="O77">
-        <v>-0.6738123483673469</v>
+        <v>-0.683309900767347</v>
       </c>
       <c r="P77">
-        <v>-1.572228812857143</v>
+        <v>-1.594389768457143</v>
       </c>
       <c r="Q77">
-        <v>-1.533228812857143</v>
+        <v>-1.555389768457143</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5219138864105631</v>
+        <v>0.5417519650110034</v>
       </c>
       <c r="T77">
-        <v>4.078288580335585</v>
+        <v>4.248217271182901</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01621642293130304</v>
+        <v>0.01600304894536484</v>
       </c>
       <c r="W77">
-        <v>0.2319761674727987</v>
+        <v>0.232026481058683</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.05405474310434355</v>
+        <v>0.0533434964845495</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3063605972072399</v>
+        <v>0.3082605972072399</v>
       </c>
       <c r="C78">
-        <v>-3.991362728967154</v>
+        <v>-4.170472336642424</v>
       </c>
       <c r="D78">
-        <v>6.195397271032847</v>
+        <v>6.150547663357576</v>
       </c>
       <c r="E78">
-        <v>9.777760000000001</v>
+        <v>9.91202</v>
       </c>
       <c r="F78">
-        <v>10.20376</v>
+        <v>10.33802</v>
       </c>
       <c r="G78">
         <v>0.017</v>
@@ -7683,37 +7683,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M78">
-        <v>2.406046608</v>
+        <v>2.437705116</v>
       </c>
       <c r="N78">
-        <v>-2.27769966922449</v>
+        <v>-2.30935817722449</v>
       </c>
       <c r="O78">
-        <v>-0.683309900767347</v>
+        <v>-0.6928074531673469</v>
       </c>
       <c r="P78">
-        <v>-1.594389768457143</v>
+        <v>-1.616550724057143</v>
       </c>
       <c r="Q78">
-        <v>-1.555389768457143</v>
+        <v>-1.577550724057143</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5417519650110034</v>
+        <v>0.5633150939245253</v>
       </c>
       <c r="T78">
-        <v>4.248217271182901</v>
+        <v>4.432922369929984</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01600304894536484</v>
+        <v>0.01579521714087959</v>
       </c>
       <c r="W78">
-        <v>0.232026481058683</v>
+        <v>0.2320754877981806</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0533434964845495</v>
+        <v>0.05265072380293201</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3082605972072399</v>
+        <v>0.3101605972072399</v>
       </c>
       <c r="C79">
-        <v>-4.170472336642424</v>
+        <v>-4.348937262353114</v>
       </c>
       <c r="D79">
-        <v>6.150547663357576</v>
+        <v>6.106342737646887</v>
       </c>
       <c r="E79">
-        <v>9.91202</v>
+        <v>10.04628</v>
       </c>
       <c r="F79">
-        <v>10.33802</v>
+        <v>10.47228</v>
       </c>
       <c r="G79">
         <v>0.017</v>
@@ -7765,37 +7765,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M79">
-        <v>2.437705116</v>
+        <v>2.469363624000001</v>
       </c>
       <c r="N79">
-        <v>-2.30935817722449</v>
+        <v>-2.34101668522449</v>
       </c>
       <c r="O79">
-        <v>-0.6928074531673469</v>
+        <v>-0.7023050055673471</v>
       </c>
       <c r="P79">
-        <v>-1.616550724057143</v>
+        <v>-1.638711679657143</v>
       </c>
       <c r="Q79">
-        <v>-1.577550724057143</v>
+        <v>-1.599711679657143</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5633150939245253</v>
+        <v>0.586838507284731</v>
       </c>
       <c r="T79">
-        <v>4.432922369929984</v>
+        <v>4.634418841290438</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01579521714087959</v>
+        <v>0.01559271435702215</v>
       </c>
       <c r="W79">
-        <v>0.2320754877981806</v>
+        <v>0.2321232379546142</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.05265072380293201</v>
+        <v>0.05197571452340721</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3101605972072399</v>
+        <v>0.3120605972072399</v>
       </c>
       <c r="C80">
-        <v>-4.348937262353114</v>
+        <v>-4.526771307191972</v>
       </c>
       <c r="D80">
-        <v>6.106342737646887</v>
+        <v>6.062768692808029</v>
       </c>
       <c r="E80">
-        <v>10.04628</v>
+        <v>10.18054</v>
       </c>
       <c r="F80">
-        <v>10.47228</v>
+        <v>10.60654</v>
       </c>
       <c r="G80">
         <v>0.017</v>
@@ -7847,37 +7847,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M80">
-        <v>2.469363624000001</v>
+        <v>2.501022132</v>
       </c>
       <c r="N80">
-        <v>-2.34101668522449</v>
+        <v>-2.37267519322449</v>
       </c>
       <c r="O80">
-        <v>-0.7023050055673471</v>
+        <v>-0.7118025579673469</v>
       </c>
       <c r="P80">
-        <v>-1.638711679657143</v>
+        <v>-1.660872635257143</v>
       </c>
       <c r="Q80">
-        <v>-1.599711679657143</v>
+        <v>-1.621872635257143</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.586838507284731</v>
+        <v>0.612602245726861</v>
       </c>
       <c r="T80">
-        <v>4.634418841290438</v>
+        <v>4.855105452780458</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01559271435702215</v>
+        <v>0.01539533822592061</v>
       </c>
       <c r="W80">
-        <v>0.2321232379546142</v>
+        <v>0.2321697792463279</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.05197571452340721</v>
+        <v>0.05131779408640202</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3120605972072399</v>
+        <v>0.3139605972072399</v>
       </c>
       <c r="C81">
-        <v>-4.526771307191972</v>
+        <v>-4.703987881111863</v>
       </c>
       <c r="D81">
-        <v>6.062768692808029</v>
+        <v>6.019812118888137</v>
       </c>
       <c r="E81">
-        <v>10.18054</v>
+        <v>10.3148</v>
       </c>
       <c r="F81">
-        <v>10.60654</v>
+        <v>10.7408</v>
       </c>
       <c r="G81">
         <v>0.017</v>
@@ -7929,37 +7929,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M81">
-        <v>2.501022132</v>
+        <v>2.53268064</v>
       </c>
       <c r="N81">
-        <v>-2.37267519322449</v>
+        <v>-2.40433370122449</v>
       </c>
       <c r="O81">
-        <v>-0.7118025579673469</v>
+        <v>-0.721300110367347</v>
       </c>
       <c r="P81">
-        <v>-1.660872635257143</v>
+        <v>-1.683033590857143</v>
       </c>
       <c r="Q81">
-        <v>-1.621872635257143</v>
+        <v>-1.644033590857143</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.612602245726861</v>
+        <v>0.6409423580132041</v>
       </c>
       <c r="T81">
-        <v>4.855105452780458</v>
+        <v>5.097860725419482</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01539533822592061</v>
+        <v>0.0152028964980966</v>
       </c>
       <c r="W81">
-        <v>0.2321697792463279</v>
+        <v>0.2322151570057488</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.05131779408640202</v>
+        <v>0.05067632166032199</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3139605972072399</v>
+        <v>0.3158605972072399</v>
       </c>
       <c r="C82">
-        <v>-4.703987881111863</v>
+        <v>-4.880600016685015</v>
       </c>
       <c r="D82">
-        <v>6.019812118888137</v>
+        <v>5.977459983314986</v>
       </c>
       <c r="E82">
-        <v>10.3148</v>
+        <v>10.44906</v>
       </c>
       <c r="F82">
-        <v>10.7408</v>
+        <v>10.87506</v>
       </c>
       <c r="G82">
         <v>0.017</v>
@@ -8011,37 +8011,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M82">
-        <v>2.53268064</v>
+        <v>2.564339148000001</v>
       </c>
       <c r="N82">
-        <v>-2.40433370122449</v>
+        <v>-2.43599220922449</v>
       </c>
       <c r="O82">
-        <v>-0.721300110367347</v>
+        <v>-0.730797662767347</v>
       </c>
       <c r="P82">
-        <v>-1.683033590857143</v>
+        <v>-1.705194546457143</v>
       </c>
       <c r="Q82">
-        <v>-1.644033590857143</v>
+        <v>-1.666194546457143</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6409423580132041</v>
+        <v>0.6722656400138991</v>
       </c>
       <c r="T82">
-        <v>5.097860725419482</v>
+        <v>5.366169184652087</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0152028964980966</v>
+        <v>0.01501520641787318</v>
       </c>
       <c r="W82">
-        <v>0.2322151570057488</v>
+        <v>0.2322594143266655</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.05067632166032199</v>
+        <v>0.05005068805957735</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3158605972072399</v>
+        <v>0.3177605972072399</v>
       </c>
       <c r="C83">
-        <v>-4.880600016685015</v>
+        <v>-5.056620382285492</v>
       </c>
       <c r="D83">
-        <v>5.977459983314986</v>
+        <v>5.935699617714508</v>
       </c>
       <c r="E83">
-        <v>10.44906</v>
+        <v>10.58332</v>
       </c>
       <c r="F83">
-        <v>10.87506</v>
+        <v>11.00932</v>
       </c>
       <c r="G83">
         <v>0.017</v>
@@ -8093,37 +8093,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M83">
-        <v>2.564339148000001</v>
+        <v>2.595997656</v>
       </c>
       <c r="N83">
-        <v>-2.43599220922449</v>
+        <v>-2.46765071722449</v>
       </c>
       <c r="O83">
-        <v>-0.730797662767347</v>
+        <v>-0.740295215167347</v>
       </c>
       <c r="P83">
-        <v>-1.705194546457143</v>
+        <v>-1.727355502057143</v>
       </c>
       <c r="Q83">
-        <v>-1.666194546457143</v>
+        <v>-1.688355502057143</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6722656400138991</v>
+        <v>0.7070692866813379</v>
       </c>
       <c r="T83">
-        <v>5.366169184652087</v>
+        <v>5.664289694910536</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01501520641787318</v>
+        <v>0.01483209414448449</v>
       </c>
       <c r="W83">
-        <v>0.2322594143266655</v>
+        <v>0.2323025922007306</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.05005068805957735</v>
+        <v>0.04944031381494829</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3177605972072399</v>
+        <v>0.3196605972072398</v>
       </c>
       <c r="C84">
-        <v>-5.056620382285492</v>
+        <v>-5.232061294722936</v>
       </c>
       <c r="D84">
-        <v>5.935699617714508</v>
+        <v>5.894518705277066</v>
       </c>
       <c r="E84">
-        <v>10.58332</v>
+        <v>10.71758</v>
       </c>
       <c r="F84">
-        <v>11.00932</v>
+        <v>11.14358</v>
       </c>
       <c r="G84">
         <v>0.017</v>
@@ -8175,37 +8175,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M84">
-        <v>2.595997656</v>
+        <v>2.627656164000001</v>
       </c>
       <c r="N84">
-        <v>-2.46765071722449</v>
+        <v>-2.49930922522449</v>
       </c>
       <c r="O84">
-        <v>-0.740295215167347</v>
+        <v>-0.7497927675673471</v>
       </c>
       <c r="P84">
-        <v>-1.727355502057143</v>
+        <v>-1.749516457657143</v>
       </c>
       <c r="Q84">
-        <v>-1.688355502057143</v>
+        <v>-1.710516457657143</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7070692866813379</v>
+        <v>0.7459674800155344</v>
       </c>
       <c r="T84">
-        <v>5.664289694910536</v>
+        <v>5.997483206375862</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01483209414448449</v>
+        <v>0.01465339421503286</v>
       </c>
       <c r="W84">
-        <v>0.2323025922007306</v>
+        <v>0.2323447296440952</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.04944031381494829</v>
+        <v>0.04884464738344296</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3196605972072398</v>
+        <v>0.3215605972072399</v>
       </c>
       <c r="C85">
-        <v>-5.232061294722936</v>
+        <v>-5.406934731354022</v>
       </c>
       <c r="D85">
-        <v>5.894518705277066</v>
+        <v>5.853905268645978</v>
       </c>
       <c r="E85">
-        <v>10.71758</v>
+        <v>10.85184</v>
       </c>
       <c r="F85">
-        <v>11.14358</v>
+        <v>11.27784</v>
       </c>
       <c r="G85">
         <v>0.017</v>
@@ -8257,37 +8257,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M85">
-        <v>2.627656164000001</v>
+        <v>2.659314672</v>
       </c>
       <c r="N85">
-        <v>-2.49930922522449</v>
+        <v>-2.53096773322449</v>
       </c>
       <c r="O85">
-        <v>-0.7497927675673471</v>
+        <v>-0.759290319967347</v>
       </c>
       <c r="P85">
-        <v>-1.749516457657143</v>
+        <v>-1.771677413257143</v>
       </c>
       <c r="Q85">
-        <v>-1.710516457657143</v>
+        <v>-1.732677413257143</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7459674800155344</v>
+        <v>0.7897279475165054</v>
       </c>
       <c r="T85">
-        <v>5.997483206375862</v>
+        <v>6.372325906774355</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01465339421503286</v>
+        <v>0.01447894904580629</v>
       </c>
       <c r="W85">
-        <v>0.2323447296440952</v>
+        <v>0.2323858638149989</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.04884464738344296</v>
+        <v>0.048263163486021</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3215605972072398</v>
+        <v>0.3234605972072399</v>
       </c>
       <c r="C86">
-        <v>-5.406934731354019</v>
+        <v>-5.581252341696644</v>
       </c>
       <c r="D86">
-        <v>5.85390526864598</v>
+        <v>5.813847658303357</v>
       </c>
       <c r="E86">
-        <v>10.85184</v>
+        <v>10.9861</v>
       </c>
       <c r="F86">
-        <v>11.27784</v>
+        <v>11.4121</v>
       </c>
       <c r="G86">
         <v>0.017</v>
@@ -8339,37 +8339,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M86">
-        <v>2.659314672</v>
+        <v>2.69097318</v>
       </c>
       <c r="N86">
-        <v>-2.53096773322449</v>
+        <v>-2.56262624122449</v>
       </c>
       <c r="O86">
-        <v>-0.7592903199673469</v>
+        <v>-0.768787872367347</v>
       </c>
       <c r="P86">
-        <v>-1.771677413257143</v>
+        <v>-1.793838368857143</v>
       </c>
       <c r="Q86">
-        <v>-1.732677413257143</v>
+        <v>-1.754838368857143</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7897279475165049</v>
+        <v>0.8393231440176053</v>
       </c>
       <c r="T86">
-        <v>6.372325906774351</v>
+        <v>6.797147633892641</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01447894904580629</v>
+        <v>0.0143086084687968</v>
       </c>
       <c r="W86">
-        <v>0.2323858638149989</v>
+        <v>0.2324260301230577</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.048263163486021</v>
+        <v>0.04769536156265608</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3234605972072399</v>
+        <v>0.3253605972072399</v>
       </c>
       <c r="C87">
-        <v>-5.581252341696644</v>
+        <v>-5.755025458570505</v>
       </c>
       <c r="D87">
-        <v>5.813847658303357</v>
+        <v>5.774334541429495</v>
       </c>
       <c r="E87">
-        <v>10.9861</v>
+        <v>11.12036</v>
       </c>
       <c r="F87">
-        <v>11.4121</v>
+        <v>11.54636</v>
       </c>
       <c r="G87">
         <v>0.017</v>
@@ -8421,37 +8421,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M87">
-        <v>2.69097318</v>
+        <v>2.722631688</v>
       </c>
       <c r="N87">
-        <v>-2.56262624122449</v>
+        <v>-2.59428474922449</v>
       </c>
       <c r="O87">
-        <v>-0.768787872367347</v>
+        <v>-0.7782854247673469</v>
       </c>
       <c r="P87">
-        <v>-1.793838368857143</v>
+        <v>-1.815999324457143</v>
       </c>
       <c r="Q87">
-        <v>-1.754838368857143</v>
+        <v>-1.776999324457143</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8393231440176053</v>
+        <v>0.8960033685902914</v>
       </c>
       <c r="T87">
-        <v>6.797147633892641</v>
+        <v>7.282658179170687</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0143086084687968</v>
+        <v>0.01414222930055498</v>
       </c>
       <c r="W87">
-        <v>0.2324260301230577</v>
+        <v>0.2324652623309292</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.04769536156265608</v>
+        <v>0.04714076433518333</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3253605972072399</v>
+        <v>0.3272605972072399</v>
       </c>
       <c r="C88">
-        <v>-5.755025458570505</v>
+        <v>-5.928265108786474</v>
       </c>
       <c r="D88">
-        <v>5.774334541429495</v>
+        <v>5.735354891213525</v>
       </c>
       <c r="E88">
-        <v>11.12036</v>
+        <v>11.25462</v>
       </c>
       <c r="F88">
-        <v>11.54636</v>
+        <v>11.68062</v>
       </c>
       <c r="G88">
         <v>0.017</v>
@@ -8503,37 +8503,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M88">
-        <v>2.722631688</v>
+        <v>2.754290196</v>
       </c>
       <c r="N88">
-        <v>-2.59428474922449</v>
+        <v>-2.62594325722449</v>
       </c>
       <c r="O88">
-        <v>-0.7782854247673469</v>
+        <v>-0.7877829771673469</v>
       </c>
       <c r="P88">
-        <v>-1.815999324457143</v>
+        <v>-1.838160280057143</v>
       </c>
       <c r="Q88">
-        <v>-1.776999324457143</v>
+        <v>-1.799160280057143</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8960033685902914</v>
+        <v>0.9614036277126216</v>
       </c>
       <c r="T88">
-        <v>7.282658179170687</v>
+        <v>7.842862654491509</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01414222930055498</v>
+        <v>0.01397967494077849</v>
       </c>
       <c r="W88">
-        <v>0.2324652623309292</v>
+        <v>0.2325035926489644</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.04714076433518333</v>
+        <v>0.04659891646926162</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3272605972072399</v>
+        <v>0.3291605972072399</v>
       </c>
       <c r="C89">
-        <v>-5.928265108786474</v>
+        <v>-6.100982023405892</v>
       </c>
       <c r="D89">
-        <v>5.735354891213525</v>
+        <v>5.696897976594108</v>
       </c>
       <c r="E89">
-        <v>11.25462</v>
+        <v>11.38888</v>
       </c>
       <c r="F89">
-        <v>11.68062</v>
+        <v>11.81488</v>
       </c>
       <c r="G89">
         <v>0.017</v>
@@ -8585,37 +8585,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M89">
-        <v>2.754290196</v>
+        <v>2.785948704</v>
       </c>
       <c r="N89">
-        <v>-2.62594325722449</v>
+        <v>-2.65760176522449</v>
       </c>
       <c r="O89">
-        <v>-0.7877829771673469</v>
+        <v>-0.797280529567347</v>
       </c>
       <c r="P89">
-        <v>-1.838160280057143</v>
+        <v>-1.860321235657143</v>
       </c>
       <c r="Q89">
-        <v>-1.799160280057143</v>
+        <v>-1.821321235657143</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9614036277126216</v>
+        <v>1.037703930022007</v>
       </c>
       <c r="T89">
-        <v>7.842862654491509</v>
+        <v>8.496434542365803</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01397967494077849</v>
+        <v>0.01382081499826964</v>
       </c>
       <c r="W89">
-        <v>0.2325035926489644</v>
+        <v>0.232541051823408</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.04659891646926162</v>
+        <v>0.04606938332756549</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3291605972072399</v>
+        <v>0.3310605972072399</v>
       </c>
       <c r="C90">
-        <v>-6.100982023405892</v>
+        <v>-6.27318664758988</v>
       </c>
       <c r="D90">
-        <v>5.696897976594108</v>
+        <v>5.658953352410119</v>
       </c>
       <c r="E90">
-        <v>11.38888</v>
+        <v>11.52314</v>
       </c>
       <c r="F90">
-        <v>11.81488</v>
+        <v>11.94914</v>
       </c>
       <c r="G90">
         <v>0.017</v>
@@ -8667,37 +8667,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M90">
-        <v>2.785948704</v>
+        <v>2.817607212</v>
       </c>
       <c r="N90">
-        <v>-2.65760176522449</v>
+        <v>-2.68926027322449</v>
       </c>
       <c r="O90">
-        <v>-0.797280529567347</v>
+        <v>-0.8067780819673469</v>
       </c>
       <c r="P90">
-        <v>-1.860321235657143</v>
+        <v>-1.882482191257143</v>
       </c>
       <c r="Q90">
-        <v>-1.821321235657143</v>
+        <v>-1.843482191257143</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.037703930022007</v>
+        <v>1.127877014569462</v>
       </c>
       <c r="T90">
-        <v>8.496434542365803</v>
+        <v>9.268837682580877</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01382081499826964</v>
+        <v>0.01366552494210931</v>
       </c>
       <c r="W90">
-        <v>0.232541051823408</v>
+        <v>0.2325776692186506</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.04606938332756549</v>
+        <v>0.04555174980703103</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3310605972072399</v>
+        <v>0.3329605972072399</v>
       </c>
       <c r="C91">
-        <v>-6.27318664758988</v>
+        <v>-6.444889150057652</v>
       </c>
       <c r="D91">
-        <v>5.658953352410119</v>
+        <v>5.621510849942348</v>
       </c>
       <c r="E91">
-        <v>11.52314</v>
+        <v>11.6574</v>
       </c>
       <c r="F91">
-        <v>11.94914</v>
+        <v>12.0834</v>
       </c>
       <c r="G91">
         <v>0.017</v>
@@ -8749,37 +8749,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M91">
-        <v>2.817607212</v>
+        <v>2.84926572</v>
       </c>
       <c r="N91">
-        <v>-2.68926027322449</v>
+        <v>-2.72091878122449</v>
       </c>
       <c r="O91">
-        <v>-0.8067780819673469</v>
+        <v>-0.8162756343673471</v>
       </c>
       <c r="P91">
-        <v>-1.882482191257143</v>
+        <v>-1.904643146857143</v>
       </c>
       <c r="Q91">
-        <v>-1.843482191257143</v>
+        <v>-1.865643146857143</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.127877014569462</v>
+        <v>1.236084716026408</v>
       </c>
       <c r="T91">
-        <v>9.268837682580877</v>
+        <v>10.19572145083896</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01366552494210931</v>
+        <v>0.01351368577608587</v>
       </c>
       <c r="W91">
-        <v>0.2325776692186506</v>
+        <v>0.2326134728939989</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.04555174980703103</v>
+        <v>0.04504561925361961</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3329605972072399</v>
+        <v>0.3348605972072399</v>
       </c>
       <c r="C92">
-        <v>-6.444889150057652</v>
+        <v>-6.616099432171797</v>
       </c>
       <c r="D92">
-        <v>5.621510849942348</v>
+        <v>5.584560567828203</v>
       </c>
       <c r="E92">
-        <v>11.6574</v>
+        <v>11.79166</v>
       </c>
       <c r="F92">
-        <v>12.0834</v>
+        <v>12.21766</v>
       </c>
       <c r="G92">
         <v>0.017</v>
@@ -8831,37 +8831,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M92">
-        <v>2.84926572</v>
+        <v>2.880924228</v>
       </c>
       <c r="N92">
-        <v>-2.72091878122449</v>
+        <v>-2.75257728922449</v>
       </c>
       <c r="O92">
-        <v>-0.8162756343673471</v>
+        <v>-0.8257731867673469</v>
       </c>
       <c r="P92">
-        <v>-1.904643146857143</v>
+        <v>-1.926804102457143</v>
       </c>
       <c r="Q92">
-        <v>-1.865643146857143</v>
+        <v>-1.887804102457143</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.236084716026408</v>
+        <v>1.368338573362676</v>
       </c>
       <c r="T92">
-        <v>10.19572145083896</v>
+        <v>11.32857938982107</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01351368577608587</v>
+        <v>0.01336518373459042</v>
       </c>
       <c r="W92">
-        <v>0.2326134728939989</v>
+        <v>0.2326484896753836</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.04504561925361961</v>
+        <v>0.04455061244863479</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3348605972072399</v>
+        <v>0.3367605972072399</v>
       </c>
       <c r="C93">
-        <v>-6.616099432171797</v>
+        <v>-6.786827136667594</v>
       </c>
       <c r="D93">
-        <v>5.584560567828203</v>
+        <v>5.548092863332407</v>
       </c>
       <c r="E93">
-        <v>11.79166</v>
+        <v>11.92592</v>
       </c>
       <c r="F93">
-        <v>12.21766</v>
+        <v>12.35192</v>
       </c>
       <c r="G93">
         <v>0.017</v>
@@ -8913,37 +8913,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M93">
-        <v>2.880924228</v>
+        <v>2.912582736000001</v>
       </c>
       <c r="N93">
-        <v>-2.75257728922449</v>
+        <v>-2.78423579722449</v>
       </c>
       <c r="O93">
-        <v>-0.8257731867673469</v>
+        <v>-0.8352707391673471</v>
       </c>
       <c r="P93">
-        <v>-1.926804102457143</v>
+        <v>-1.948965058057143</v>
       </c>
       <c r="Q93">
-        <v>-1.887804102457143</v>
+        <v>-1.909965058057143</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.368338573362676</v>
+        <v>1.533655895033011</v>
       </c>
       <c r="T93">
-        <v>11.32857938982107</v>
+        <v>12.74465181354871</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01336518373459042</v>
+        <v>0.01321990999834487</v>
       </c>
       <c r="W93">
-        <v>0.2326484896753836</v>
+        <v>0.2326827452223903</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.04455061244863479</v>
+        <v>0.0440663666611496</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3367605972072399</v>
+        <v>0.3386605972072399</v>
       </c>
       <c r="C94">
-        <v>-6.786827136667594</v>
+        <v>-6.95708165604253</v>
       </c>
       <c r="D94">
-        <v>5.548092863332407</v>
+        <v>5.51209834395747</v>
       </c>
       <c r="E94">
-        <v>11.92592</v>
+        <v>12.06018</v>
       </c>
       <c r="F94">
-        <v>12.35192</v>
+        <v>12.48618</v>
       </c>
       <c r="G94">
         <v>0.017</v>
@@ -8995,37 +8995,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M94">
-        <v>2.912582736000001</v>
+        <v>2.944241244000001</v>
       </c>
       <c r="N94">
-        <v>-2.78423579722449</v>
+        <v>-2.81589430522449</v>
       </c>
       <c r="O94">
-        <v>-0.8352707391673471</v>
+        <v>-0.844768291567347</v>
       </c>
       <c r="P94">
-        <v>-1.948965058057143</v>
+        <v>-1.971126013657143</v>
       </c>
       <c r="Q94">
-        <v>-1.909965058057143</v>
+        <v>-1.932126013657143</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.533655895033011</v>
+        <v>1.746206737180584</v>
       </c>
       <c r="T94">
-        <v>12.74465181354871</v>
+        <v>14.56531635834138</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01321990999834487</v>
+        <v>0.01307776042847019</v>
       </c>
       <c r="W94">
-        <v>0.2326827452223903</v>
+        <v>0.2327162640909667</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.0440663666611496</v>
+        <v>0.04359253476156733</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3386605972072399</v>
+        <v>0.3405605972072399</v>
       </c>
       <c r="C95">
-        <v>-6.95708165604253</v>
+        <v>-7.126872140621361</v>
       </c>
       <c r="D95">
-        <v>5.51209834395747</v>
+        <v>5.476567859378639</v>
       </c>
       <c r="E95">
-        <v>12.06018</v>
+        <v>12.19444</v>
       </c>
       <c r="F95">
-        <v>12.48618</v>
+        <v>12.62044</v>
       </c>
       <c r="G95">
         <v>0.017</v>
@@ -9077,37 +9077,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M95">
-        <v>2.944241244000001</v>
+        <v>2.975899752</v>
       </c>
       <c r="N95">
-        <v>-2.81589430522449</v>
+        <v>-2.84755281322449</v>
       </c>
       <c r="O95">
-        <v>-0.844768291567347</v>
+        <v>-0.8542658439673469</v>
       </c>
       <c r="P95">
-        <v>-1.971126013657143</v>
+        <v>-1.993286969257143</v>
       </c>
       <c r="Q95">
-        <v>-1.932126013657143</v>
+        <v>-1.954286969257143</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.746206737180584</v>
+        <v>2.029607860044015</v>
       </c>
       <c r="T95">
-        <v>14.56531635834138</v>
+        <v>16.99286908473162</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01307776042847019</v>
+        <v>0.01293863531752902</v>
       </c>
       <c r="W95">
-        <v>0.2327162640909667</v>
+        <v>0.2327490697921267</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.04359253476156733</v>
+        <v>0.04312878439176349</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3405605972072399</v>
+        <v>0.3424605972072399</v>
       </c>
       <c r="C96">
-        <v>-7.126872140621361</v>
+        <v>-7.296207506311232</v>
       </c>
       <c r="D96">
-        <v>5.476567859378639</v>
+        <v>5.441492493688769</v>
       </c>
       <c r="E96">
-        <v>12.19444</v>
+        <v>12.3287</v>
       </c>
       <c r="F96">
-        <v>12.62044</v>
+        <v>12.7547</v>
       </c>
       <c r="G96">
         <v>0.017</v>
@@ -9159,37 +9159,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M96">
-        <v>2.975899752</v>
+        <v>3.007558260000001</v>
       </c>
       <c r="N96">
-        <v>-2.84755281322449</v>
+        <v>-2.87921132122449</v>
       </c>
       <c r="O96">
-        <v>-0.8542658439673469</v>
+        <v>-0.8637633963673471</v>
       </c>
       <c r="P96">
-        <v>-1.993286969257143</v>
+        <v>-2.015447924857143</v>
       </c>
       <c r="Q96">
-        <v>-1.954286969257143</v>
+        <v>-1.976447924857143</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.029607860044015</v>
+        <v>2.42636943205282</v>
       </c>
       <c r="T96">
-        <v>16.99286908473162</v>
+        <v>20.39144290167796</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01293863531752902</v>
+        <v>0.01280243915629187</v>
       </c>
       <c r="W96">
-        <v>0.2327490697921267</v>
+        <v>0.2327811848469464</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.04312878439176349</v>
+        <v>0.04267479718763956</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3424605972072399</v>
+        <v>0.3443605972072399</v>
       </c>
       <c r="C97">
-        <v>-7.296207506311232</v>
+        <v>-7.465096442060688</v>
       </c>
       <c r="D97">
-        <v>5.441492493688769</v>
+        <v>5.406863557939313</v>
       </c>
       <c r="E97">
-        <v>12.3287</v>
+        <v>12.46296</v>
       </c>
       <c r="F97">
-        <v>12.7547</v>
+        <v>12.88896</v>
       </c>
       <c r="G97">
         <v>0.017</v>
@@ -9241,37 +9241,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M97">
-        <v>3.007558260000001</v>
+        <v>3.039216768</v>
       </c>
       <c r="N97">
-        <v>-2.87921132122449</v>
+        <v>-2.91086982922449</v>
       </c>
       <c r="O97">
-        <v>-0.8637633963673471</v>
+        <v>-0.8732609487673469</v>
       </c>
       <c r="P97">
-        <v>-2.015447924857143</v>
+        <v>-2.037608880457143</v>
       </c>
       <c r="Q97">
-        <v>-1.976447924857143</v>
+        <v>-1.998608880457143</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.42636943205282</v>
+        <v>3.021511790066026</v>
       </c>
       <c r="T97">
-        <v>20.39144290167796</v>
+        <v>25.48930362709745</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01280243915629187</v>
+        <v>0.0126690804150805</v>
       </c>
       <c r="W97">
-        <v>0.2327811848469464</v>
+        <v>0.232812630838124</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.04267479718763956</v>
+        <v>0.04223026805026842</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3443605972072399</v>
+        <v>0.3462605972072399</v>
       </c>
       <c r="C98">
-        <v>-7.465096442060686</v>
+        <v>-7.633547417035683</v>
       </c>
       <c r="D98">
-        <v>5.406863557939313</v>
+        <v>5.372672582964317</v>
       </c>
       <c r="E98">
-        <v>12.46296</v>
+        <v>12.59722</v>
       </c>
       <c r="F98">
-        <v>12.88896</v>
+        <v>13.02322</v>
       </c>
       <c r="G98">
         <v>0.017</v>
@@ -9323,37 +9323,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M98">
-        <v>3.039216768</v>
+        <v>3.070875276</v>
       </c>
       <c r="N98">
-        <v>-2.910869829224489</v>
+        <v>-2.94252833722449</v>
       </c>
       <c r="O98">
-        <v>-0.8732609487673468</v>
+        <v>-0.882758501167347</v>
       </c>
       <c r="P98">
-        <v>-2.037608880457142</v>
+        <v>-2.059769836057143</v>
       </c>
       <c r="Q98">
-        <v>-1.998608880457142</v>
+        <v>-2.020769836057143</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.021511790066017</v>
+        <v>4.013415720088024</v>
       </c>
       <c r="T98">
-        <v>25.48930362709738</v>
+        <v>33.98573816946318</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0126690804150805</v>
+        <v>0.01253847133863637</v>
       </c>
       <c r="W98">
-        <v>0.232812630838124</v>
+        <v>0.2328434284583495</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04223026805026842</v>
+        <v>0.04179490446212131</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3462605972072399</v>
+        <v>0.3481605972072399</v>
       </c>
       <c r="C99">
-        <v>-7.633547417035683</v>
+        <v>-7.801568687525021</v>
       </c>
       <c r="D99">
-        <v>5.372672582964317</v>
+        <v>5.338911312474978</v>
       </c>
       <c r="E99">
-        <v>12.59722</v>
+        <v>12.73148</v>
       </c>
       <c r="F99">
-        <v>13.02322</v>
+        <v>13.15748</v>
       </c>
       <c r="G99">
         <v>0.017</v>
@@ -9405,37 +9405,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M99">
-        <v>3.070875276</v>
+        <v>3.102533784</v>
       </c>
       <c r="N99">
-        <v>-2.94252833722449</v>
+        <v>-2.97418684522449</v>
       </c>
       <c r="O99">
-        <v>-0.882758501167347</v>
+        <v>-0.8922560535673469</v>
       </c>
       <c r="P99">
-        <v>-2.059769836057143</v>
+        <v>-2.081930791657143</v>
       </c>
       <c r="Q99">
-        <v>-2.020769836057143</v>
+        <v>-2.042930791657143</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.013415720088024</v>
+        <v>5.997223580132035</v>
       </c>
       <c r="T99">
-        <v>33.98573816946318</v>
+        <v>50.97860725419476</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01253847133863637</v>
+        <v>0.01241052775354824</v>
       </c>
       <c r="W99">
-        <v>0.2328434284583495</v>
+        <v>0.2328735975557133</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04179490446212131</v>
+        <v>0.04136842584516087</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3481605972072399</v>
+        <v>0.3500605972072399</v>
       </c>
       <c r="C100">
-        <v>-7.801568687525021</v>
+        <v>-7.969168303587084</v>
       </c>
       <c r="D100">
-        <v>5.338911312474978</v>
+        <v>5.305571696412916</v>
       </c>
       <c r="E100">
-        <v>12.73148</v>
+        <v>12.86574</v>
       </c>
       <c r="F100">
-        <v>13.15748</v>
+        <v>13.29174</v>
       </c>
       <c r="G100">
         <v>0.017</v>
@@ -9487,37 +9487,37 @@
         <v>0.1283469387755102</v>
       </c>
       <c r="M100">
-        <v>3.102533784</v>
+        <v>3.134192292</v>
       </c>
       <c r="N100">
-        <v>-2.97418684522449</v>
+        <v>-3.00584535322449</v>
       </c>
       <c r="O100">
-        <v>-0.8922560535673469</v>
+        <v>-0.901753605967347</v>
       </c>
       <c r="P100">
-        <v>-2.081930791657143</v>
+        <v>-2.104091747257143</v>
       </c>
       <c r="Q100">
-        <v>-2.042930791657143</v>
+        <v>-2.065091747257143</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.997223580132035</v>
+        <v>11.94864716026407</v>
       </c>
       <c r="T100">
-        <v>50.97860725419476</v>
+        <v>101.9572145083895</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01241052775354824</v>
+        <v>0.01228516888735079</v>
       </c>
       <c r="W100">
-        <v>0.2328735975557133</v>
+        <v>0.2329031571763627</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04136842584516087</v>
+        <v>0.04095056295783595</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3500605972072399</v>
-      </c>
-      <c r="C101">
-        <v>-7.969168303587084</v>
-      </c>
-      <c r="D101">
-        <v>5.305571696412916</v>
-      </c>
-      <c r="E101">
-        <v>12.86574</v>
-      </c>
-      <c r="F101">
-        <v>13.29174</v>
-      </c>
-      <c r="G101">
-        <v>0.017</v>
-      </c>
-      <c r="H101">
-        <v>13</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.1673469387755102</v>
-      </c>
-      <c r="K101">
-        <v>0.03900000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0.1283469387755102</v>
-      </c>
-      <c r="M101">
-        <v>3.134192292</v>
-      </c>
-      <c r="N101">
-        <v>-3.00584535322449</v>
-      </c>
-      <c r="O101">
-        <v>-0.901753605967347</v>
-      </c>
-      <c r="P101">
-        <v>-2.104091747257143</v>
-      </c>
-      <c r="Q101">
-        <v>-2.065091747257143</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.94864716026407</v>
-      </c>
-      <c r="T101">
-        <v>101.9572145083895</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01228516888735079</v>
-      </c>
-      <c r="W101">
-        <v>0.2329031571763627</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04095056295783595</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
